--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.53327969907</v>
+        <v>46073.69994636574</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55202717593</v>
+        <v>46092.71869384259</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.61572028935</v>
+        <v>46118.78238695602</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1697,13 +1697,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.53328005787</v>
+        <v>46073.69994672453</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55211712963</v>
+        <v>46092.7187837963</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55213513889</v>
+        <v>46092.71880180556</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1762,13 +1762,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.53328034723</v>
+        <v>46073.69994701388</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55214392361</v>
+        <v>46092.718810590275</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55215846065</v>
+        <v>46092.71882512732</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1827,13 +1827,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.53328063658</v>
+        <v>46073.69994730324</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.552157488426</v>
+        <v>46092.71882415509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.552175069446</v>
+        <v>46092.71884173611</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1892,13 +1892,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.53328091435</v>
+        <v>46073.699947581015</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55216664352</v>
+        <v>46092.71883331018</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.58784101852</v>
+        <v>46093.75450768518</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1957,13 +1957,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55218392361</v>
+        <v>46092.718850590274</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.552198634265</v>
+        <v>46092.71886530092</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2022,11 +2022,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.53328145834</v>
+        <v>46073.699948124995</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.72635736111</v>
+        <v>46127.89302402778</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2069,13 +2069,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.53328171297</v>
+        <v>46073.699948379624</v>
       </c>
       <c r="C11" s="8">
-        <v>46093.69488967593</v>
+        <v>46093.86155634259</v>
       </c>
       <c r="D11" s="8">
-        <v>46093.694909328704</v>
+        <v>46093.86157599537</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2134,11 +2134,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46134.52718547454</v>
+        <v>46134.69385214121</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2197,13 +2197,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C13" s="8">
-        <v>46093.58815574074</v>
+        <v>46093.75482240741</v>
       </c>
       <c r="D13" s="8">
-        <v>46093.58816989583</v>
+        <v>46093.7548365625</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2250,13 +2250,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.533279560186</v>
+        <v>46073.69994622685</v>
       </c>
       <c r="C14" s="5">
-        <v>46093.58800283565</v>
+        <v>46093.75466950232</v>
       </c>
       <c r="D14" s="5">
-        <v>46093.58802418981</v>
+        <v>46093.754690856484</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2315,13 +2315,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.53327989583</v>
+        <v>46073.6999465625</v>
       </c>
       <c r="C15" s="8">
-        <v>46093.58801493056</v>
+        <v>46093.754681597224</v>
       </c>
       <c r="D15" s="8">
-        <v>46093.588031527775</v>
+        <v>46093.75469819445</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2380,13 +2380,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.533280185184</v>
+        <v>46073.69994685185</v>
       </c>
       <c r="C16" s="5">
-        <v>46093.58802552083</v>
+        <v>46093.754692187504</v>
       </c>
       <c r="D16" s="5">
-        <v>46093.58804537037</v>
+        <v>46093.75471203704</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2445,13 +2445,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.53328045139</v>
+        <v>46073.69994711806</v>
       </c>
       <c r="C17" s="8">
-        <v>46093.58803587963</v>
+        <v>46093.7547025463</v>
       </c>
       <c r="D17" s="8">
-        <v>46093.58805561342</v>
+        <v>46093.75472228009</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2510,13 +2510,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.41097503473</v>
+        <v>46077.577641701384</v>
       </c>
       <c r="C18" s="5">
-        <v>46093.58804545139</v>
+        <v>46093.754712118054</v>
       </c>
       <c r="D18" s="5">
-        <v>46093.588064895834</v>
+        <v>46093.7547315625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2575,13 +2575,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.41106642361</v>
+        <v>46077.57773309028</v>
       </c>
       <c r="C19" s="8">
-        <v>46093.58805770833</v>
+        <v>46093.754724375</v>
       </c>
       <c r="D19" s="8">
-        <v>46093.588074803236</v>
+        <v>46093.75474146991</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2640,13 +2640,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.53328070602</v>
+        <v>46073.69994737269</v>
       </c>
       <c r="C20" s="5">
-        <v>46093.588138356485</v>
+        <v>46093.75480502315</v>
       </c>
       <c r="D20" s="5">
-        <v>46093.588156875005</v>
+        <v>46093.75482354166</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2705,13 +2705,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.533280972224</v>
+        <v>46073.69994763889</v>
       </c>
       <c r="C21" s="8">
-        <v>46093.70787949074</v>
+        <v>46093.87454615741</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.37611355324</v>
+        <v>46139.54278021991</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2758,13 +2758,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.53328150463</v>
+        <v>46073.6999481713</v>
       </c>
       <c r="C22" s="5">
-        <v>46093.58810327546</v>
+        <v>46093.75476994213</v>
       </c>
       <c r="D22" s="5">
-        <v>46093.58811964121</v>
+        <v>46093.754786307865</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2823,13 +2823,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.53328122685</v>
+        <v>46073.69994789352</v>
       </c>
       <c r="C23" s="8">
-        <v>46093.588114375</v>
+        <v>46093.754781041665</v>
       </c>
       <c r="D23" s="8">
-        <v>46093.5881318287</v>
+        <v>46093.75479849537</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2888,13 +2888,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.533281875</v>
+        <v>46073.69994854167</v>
       </c>
       <c r="C24" s="5">
-        <v>46093.707863171294</v>
+        <v>46093.874529837965</v>
       </c>
       <c r="D24" s="5">
-        <v>46093.707880625</v>
+        <v>46093.87454729166</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2953,13 +2953,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.53328215278</v>
+        <v>46073.69994881944</v>
       </c>
       <c r="C25" s="8">
-        <v>46093.588160694446</v>
+        <v>46093.75482736111</v>
       </c>
       <c r="D25" s="8">
-        <v>46093.5881780787</v>
+        <v>46093.754844745374</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -3018,13 +3018,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.53327965278</v>
+        <v>46073.699946319444</v>
       </c>
       <c r="C26" s="5">
-        <v>46093.588169571754</v>
+        <v>46093.754836238426</v>
       </c>
       <c r="D26" s="5">
-        <v>46093.58818924769</v>
+        <v>46093.75485591435</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3083,13 +3083,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46076.71435710648</v>
+        <v>46076.88102377315</v>
       </c>
       <c r="C27" s="8">
-        <v>46093.58817870371</v>
+        <v>46093.75484537037</v>
       </c>
       <c r="D27" s="8">
-        <v>46093.58820009259</v>
+        <v>46093.754866759264</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3148,13 +3148,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.41262609954</v>
+        <v>46077.579292766204</v>
       </c>
       <c r="C28" s="5">
-        <v>46093.5881874537</v>
+        <v>46093.75485412037</v>
       </c>
       <c r="D28" s="5">
-        <v>46093.5882078588</v>
+        <v>46093.75487452546</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>78</v>
@@ -3213,13 +3213,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.4126985301</v>
+        <v>46077.579365196754</v>
       </c>
       <c r="C29" s="8">
-        <v>46093.58819627315</v>
+        <v>46093.754862939815</v>
       </c>
       <c r="D29" s="8">
-        <v>46093.58821469908</v>
+        <v>46093.75488136574</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>81</v>
@@ -3278,13 +3278,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="5">
-        <v>46139.37604528935</v>
+        <v>46139.54271195602</v>
       </c>
       <c r="C30" s="5">
-        <v>46139.37662927083</v>
+        <v>46139.5432959375</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.3815103125</v>
+        <v>46139.548176979166</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3343,11 +3343,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.533280081014</v>
+        <v>46073.699946747685</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46139.37674895833</v>
+        <v>46139.543415625</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3390,11 +3390,11 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.53328038195</v>
+        <v>46073.69994704861</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46182.51697045139</v>
+        <v>46182.683637118054</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3453,13 +3453,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.53328071759</v>
+        <v>46073.69994738426</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.516964062495</v>
+        <v>46182.68363072917</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.51746700231</v>
+        <v>46182.68413366898</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3514,11 +3514,11 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.53328103009</v>
+        <v>46073.69994769676</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.516969930555</v>
+        <v>46182.68363659723</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3573,11 +3573,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.533281365744</v>
+        <v>46073.69994803241</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.48607194444</v>
+        <v>46174.65273861111</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3636,13 +3636,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.53328166666</v>
+        <v>46073.699948333335</v>
       </c>
       <c r="C36" s="5">
-        <v>46174.48606336805</v>
+        <v>46174.65273003472</v>
       </c>
       <c r="D36" s="5">
-        <v>46174.48606505787</v>
+        <v>46174.652731724535</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3697,11 +3697,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.53328195601</v>
+        <v>46073.699948622685</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46174.48607142361</v>
+        <v>46174.65273809028</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3756,11 +3756,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46182.509005092594</v>
+        <v>46182.67567175926</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3819,13 +3819,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.53328253472</v>
+        <v>46073.699949201386</v>
       </c>
       <c r="C39" s="8">
-        <v>46174.482631631945</v>
+        <v>46174.64929829861</v>
       </c>
       <c r="D39" s="8">
-        <v>46174.48263331018</v>
+        <v>46174.64929997685</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3880,13 +3880,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.53327918981</v>
+        <v>46073.69994585648</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.50899928241</v>
+        <v>46182.67566594908</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.50900143519</v>
+        <v>46182.67566810185</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3941,13 +3941,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.53327961806</v>
+        <v>46073.69994628472</v>
       </c>
       <c r="C41" s="8">
-        <v>46127.61676586806</v>
+        <v>46127.78343253472</v>
       </c>
       <c r="D41" s="8">
-        <v>46127.61677946759</v>
+        <v>46127.78344613426</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4006,13 +4006,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.53327987269</v>
+        <v>46073.69994653935</v>
       </c>
       <c r="C42" s="5">
-        <v>46120.52588439814</v>
+        <v>46120.692551064814</v>
       </c>
       <c r="D42" s="5">
-        <v>46120.52588638889</v>
+        <v>46120.69255305556</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4067,13 +4067,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.53328013889</v>
+        <v>46073.69994680556</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.616739375</v>
+        <v>46127.783406041664</v>
       </c>
       <c r="D43" s="8">
-        <v>46127.61674059028</v>
+        <v>46127.783407256946</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4128,13 +4128,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.53328040509</v>
+        <v>46073.69994707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.616750057874</v>
+        <v>46127.78341672454</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.616751388894</v>
+        <v>46127.78341805555</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4189,13 +4189,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C45" s="8">
-        <v>46112.323915127316</v>
+        <v>46112.49058179398</v>
       </c>
       <c r="D45" s="8">
-        <v>46139.38124505787</v>
+        <v>46139.54791172454</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4254,13 +4254,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C46" s="5">
-        <v>46104.66087769676</v>
+        <v>46104.82754436343</v>
       </c>
       <c r="D46" s="5">
-        <v>46104.66087959491</v>
+        <v>46104.82754626157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4315,13 +4315,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.53328120371</v>
+        <v>46073.699947870366</v>
       </c>
       <c r="C47" s="8">
-        <v>46132.4119659375</v>
+        <v>46132.57863260417</v>
       </c>
       <c r="D47" s="8">
-        <v>46132.4119678125</v>
+        <v>46132.57863447917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4376,13 +4376,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46076.71443853009</v>
+        <v>46076.881105196764</v>
       </c>
       <c r="C48" s="5">
-        <v>46112.32145986111</v>
+        <v>46112.48812652778</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.38121825231</v>
+        <v>46139.54788491898</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4441,13 +4441,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46076.72251572917</v>
+        <v>46076.88918239583</v>
       </c>
       <c r="C49" s="8">
-        <v>46112.32517975694</v>
+        <v>46112.49184642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46112.325181504624</v>
+        <v>46112.491848171296</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4496,13 +4496,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46076.72264325232</v>
+        <v>46076.88930991898</v>
       </c>
       <c r="C50" s="5">
-        <v>46112.339374965275</v>
+        <v>46112.50604163195</v>
       </c>
       <c r="D50" s="5">
-        <v>46112.33942322917</v>
+        <v>46112.50608989583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4551,11 +4551,11 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.41282131945</v>
+        <v>46077.579487986106</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46182.51671280093</v>
+        <v>46182.68337946759</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4614,13 +4614,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.42056212963</v>
+        <v>46077.5872287963</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.516705381946</v>
+        <v>46182.68337204861</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.51670674769</v>
+        <v>46182.68337341435</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4669,13 +4669,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.42074568287</v>
+        <v>46077.58741234954</v>
       </c>
       <c r="C53" s="8">
-        <v>46182.52543858797</v>
+        <v>46182.69210525463</v>
       </c>
       <c r="D53" s="8">
-        <v>46182.525440046295</v>
+        <v>46182.69210671296</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -4724,13 +4724,13 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.412874525464</v>
+        <v>46077.57954119213</v>
       </c>
       <c r="C54" s="5">
-        <v>46174.48518971065</v>
+        <v>46174.65185637731</v>
       </c>
       <c r="D54" s="5">
-        <v>46174.48519119213</v>
+        <v>46174.6518578588</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4789,13 +4789,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.420889166664</v>
+        <v>46077.587555833336</v>
       </c>
       <c r="C55" s="8">
-        <v>46094.59207417824</v>
+        <v>46094.7587408449</v>
       </c>
       <c r="D55" s="8">
-        <v>46169.673257800925</v>
+        <v>46169.8399244676</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>110</v>
@@ -4844,13 +4844,13 @@
         <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.42099605324</v>
+        <v>46077.5876627199</v>
       </c>
       <c r="C56" s="5">
-        <v>46174.48506333333</v>
+        <v>46174.65173</v>
       </c>
       <c r="D56" s="5">
-        <v>46174.48506471065</v>
+        <v>46174.651731377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -4899,11 +4899,11 @@
         <v>197</v>
       </c>
       <c r="B57" s="8">
-        <v>46139.37674723379</v>
+        <v>46139.543413900465</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46185.55454030093</v>
+        <v>46185.72120696759</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4962,11 +4962,11 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46139.37703415509</v>
+        <v>46139.543700821756</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46177.40211376158</v>
+        <v>46177.56878042824</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -5015,11 +5015,11 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46139.377118125005</v>
+        <v>46139.54378479166</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46177.0020609375</v>
+        <v>46177.16872760416</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5068,11 +5068,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.53328149306</v>
+        <v>46073.69994815972</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46129.41975893518</v>
+        <v>46129.586425601854</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5115,13 +5115,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.53328177083</v>
+        <v>46073.6999484375</v>
       </c>
       <c r="C61" s="8">
-        <v>46099.37575439815</v>
+        <v>46099.54242106482</v>
       </c>
       <c r="D61" s="8">
-        <v>46099.37575601852</v>
+        <v>46099.54242268519</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5180,13 +5180,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.53327958334</v>
+        <v>46073.699946249995</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.41958724537</v>
+        <v>46129.586253912035</v>
       </c>
       <c r="D62" s="5">
-        <v>46129.41960146991</v>
+        <v>46129.58626813657</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5245,13 +5245,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46092.327575069445</v>
+        <v>46092.494241736116</v>
       </c>
       <c r="C63" s="8">
-        <v>46129.41975123843</v>
+        <v>46129.58641790509</v>
       </c>
       <c r="D63" s="8">
-        <v>46139.38151048611</v>
+        <v>46139.54817715278</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>115</v>
@@ -5308,11 +5308,11 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.32761923611</v>
+        <v>46092.49428590278</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46154.00145138889</v>
+        <v>46154.16811805556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5371,11 +5371,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.5332799537</v>
+        <v>46073.69994662037</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46077.460896805555</v>
+        <v>46077.627563472226</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5418,11 +5418,11 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.53328023148</v>
+        <v>46073.69994689815</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46132.41198376157</v>
+        <v>46132.578650428244</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5481,11 +5481,11 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.53328053241</v>
+        <v>46073.69994719907</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46092.33724482638</v>
+        <v>46092.503911493055</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5544,11 +5544,11 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.533280821764</v>
+        <v>46073.69994748842</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46077.4624950463</v>
+        <v>46077.62916171296</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5591,11 +5591,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.533281111115</v>
+        <v>46073.69994777778</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46092.337323750005</v>
+        <v>46092.50399041666</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5654,11 +5654,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.533281446755</v>
+        <v>46073.699948113426</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46129.419755625</v>
+        <v>46129.58642229167</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5717,11 +5717,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.53328179398</v>
+        <v>46073.69994846065</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46129.419756724536</v>
+        <v>46129.5864233912</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5780,11 +5780,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.533282199074</v>
+        <v>46073.699948865746</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46077.464394027775</v>
+        <v>46077.631060694446</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5827,11 +5827,11 @@
         <v>258</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.53328430555</v>
+        <v>46073.69995097222</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.50900709491</v>
+        <v>46182.67567376157</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5890,11 +5890,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.5332797338</v>
+        <v>46073.69994640046</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46121.0211115162</v>
+        <v>46121.187778182866</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>56</v>
@@ -5953,11 +5953,11 @@
         <v>263</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.53328011574</v>
+        <v>46073.699946782406</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46134.005887060186</v>
+        <v>46134.17255372685</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>
@@ -6016,11 +6016,11 @@
         <v>266</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.53328041667</v>
+        <v>46073.69994708333</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46148.083779837965</v>
+        <v>46148.25044650463</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6079,11 +6079,11 @@
         <v>269</v>
       </c>
       <c r="B77" s="8">
-        <v>46076.71461256944</v>
+        <v>46076.88127923611</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46128.494822187495</v>
+        <v>46128.661488854166</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>270</v>
@@ -6142,11 +6142,11 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.41294417824</v>
+        <v>46077.57961084491</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46174.48507292824</v>
+        <v>46174.651739594905</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6205,11 +6205,11 @@
         <v>275</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.412987372685</v>
+        <v>46077.57965403935</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.52544603009</v>
+        <v>46182.692112696765</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>188</v>
@@ -6268,11 +6268,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46078.45457047454</v>
+        <v>46078.621237141204</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>277</v>
@@ -6315,11 +6315,11 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46128.00154921296</v>
+        <v>46128.16821587963</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6378,11 +6378,11 @@
         <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46150.00217104166</v>
+        <v>46150.168837708334</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6441,11 +6441,11 @@
         <v>287</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.53328146991</v>
+        <v>46073.69994813658</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46136.041621435186</v>
+        <v>46136.20828810185</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>288</v>
@@ -6504,11 +6504,11 @@
         <v>290</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.533281701384</v>
+        <v>46073.699948368056</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46139.00162658565</v>
+        <v>46139.16829325231</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>291</v>
@@ -6567,11 +6567,11 @@
         <v>294</v>
       </c>
       <c r="B85" s="8">
-        <v>46076.71470601852</v>
+        <v>46076.88137268518</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46133.01733604167</v>
+        <v>46133.18400270834</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>295</v>
@@ -6630,11 +6630,11 @@
         <v>298</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46153.00145027778</v>
+        <v>46153.16811694445</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>225</v>
@@ -6693,11 +6693,11 @@
         <v>301</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.53328224537</v>
+        <v>46073.699948912035</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46154.00118898148</v>
+        <v>46154.16785564815</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>302</v>
@@ -6756,11 +6756,11 @@
         <v>304</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.533279062496</v>
+        <v>46073.69994572917</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46077.4716805787</v>
+        <v>46077.638347245374</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>305</v>
@@ -6803,11 +6803,11 @@
         <v>307</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.53327943287</v>
+        <v>46073.699946099536</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.00127768518</v>
+        <v>46155.16794435185</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>308</v>
@@ -6866,11 +6866,11 @@
         <v>310</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.53327972222</v>
+        <v>46073.69994638889</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46160.083854375</v>
+        <v>46160.25052104167</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>274</v>
@@ -6929,11 +6929,11 @@
         <v>313</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.53328002315</v>
+        <v>46073.69994668981</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46161.083654560185</v>
+        <v>46161.25032122685</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>314</v>
@@ -6992,11 +6992,11 @@
         <v>316</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.53328028935</v>
+        <v>46073.69994695602</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.083743298615</v>
+        <v>46162.25040996527</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>317</v>
@@ -7055,11 +7055,11 @@
         <v>319</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.533280578704</v>
+        <v>46073.699947245375</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46077.47213016204</v>
+        <v>46077.6387968287</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>320</v>
@@ -7102,11 +7102,11 @@
         <v>322</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.53328083333</v>
+        <v>46073.699947500005</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.0016708912</v>
+        <v>46174.16833755787</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>323</v>
@@ -7165,11 +7165,11 @@
         <v>326</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.53328112268</v>
+        <v>46073.699947789355</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46174.00167351852</v>
+        <v>46174.168340185184</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>327</v>
@@ -7228,11 +7228,11 @@
         <v>329</v>
       </c>
       <c r="B96" s="5">
-        <v>46092.3230471875</v>
+        <v>46092.48971385417</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46092.33039228009</v>
+        <v>46092.497058946756</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>330</v>
@@ -7281,11 +7281,11 @@
         <v>332</v>
       </c>
       <c r="B97" s="8">
-        <v>46092.32494825231</v>
+        <v>46092.49161491898</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46171.00207628473</v>
+        <v>46171.168742951384</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>333</v>
@@ -7344,11 +7344,11 @@
         <v>335</v>
       </c>
       <c r="B98" s="5">
-        <v>46092.32499508101</v>
+        <v>46092.491661747685</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46181.001539502315</v>
+        <v>46181.16820616898</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>336</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -3347,7 +3347,7 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46139.543415625</v>
+        <v>46191.83935533564</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3392,9 +3392,11 @@
       <c r="B32" s="5">
         <v>46073.69994704861</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46191.839348587964</v>
+      </c>
       <c r="D32" s="5">
-        <v>46182.683637118054</v>
+        <v>46191.83935060185</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3516,9 +3518,11 @@
       <c r="B34" s="5">
         <v>46073.69994769676</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46191.83755203703</v>
+      </c>
       <c r="D34" s="5">
-        <v>46182.68363659723</v>
+        <v>46191.83755358796</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3758,9 +3762,11 @@
       <c r="B38" s="5">
         <v>46073.69994892361</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46191.836712743054</v>
+      </c>
       <c r="D38" s="5">
-        <v>46182.67567175926</v>
+        <v>46191.83671528935</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -4553,9 +4559,11 @@
       <c r="B51" s="8">
         <v>46077.579487986106</v>
       </c>
-      <c r="C51" s="9"/>
+      <c r="C51" s="8">
+        <v>46191.83738681713</v>
+      </c>
       <c r="D51" s="8">
-        <v>46182.68337946759</v>
+        <v>46191.83738863426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4901,9 +4909,11 @@
       <c r="B57" s="8">
         <v>46139.543413900465</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46191.840089791665</v>
+      </c>
       <c r="D57" s="8">
-        <v>46185.72120696759</v>
+        <v>46191.84009155093</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4964,9 +4974,11 @@
       <c r="B58" s="5">
         <v>46139.543700821756</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46191.839869421296</v>
+      </c>
       <c r="D58" s="5">
-        <v>46177.56878042824</v>
+        <v>46191.83987099537</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -5017,9 +5029,11 @@
       <c r="B59" s="8">
         <v>46139.54378479166</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46191.83995417824</v>
+      </c>
       <c r="D59" s="8">
-        <v>46177.16872760416</v>
+        <v>46191.83995613426</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5957,7 +5971,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46134.17255372685</v>
+        <v>46191.8375600463</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46077.627563472226</v>
+        <v>46195.6020638426</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5434,9 +5434,11 @@
       <c r="B66" s="5">
         <v>46073.69994689815</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46195.60205410879</v>
+      </c>
       <c r="D66" s="5">
-        <v>46132.578650428244</v>
+        <v>46195.60205646991</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5499,7 +5501,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46092.503911493055</v>
+        <v>46195.60206259259</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5798,7 +5800,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46077.631060694446</v>
+        <v>46195.604225717594</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -6032,9 +6034,11 @@
       <c r="B76" s="5">
         <v>46073.69994708333</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46195.603957824074</v>
+      </c>
       <c r="D76" s="5">
-        <v>46148.25044650463</v>
+        <v>46195.603959687505</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6095,9 +6099,11 @@
       <c r="B77" s="8">
         <v>46076.88127923611</v>
       </c>
-      <c r="C77" s="9"/>
+      <c r="C77" s="8">
+        <v>46195.60421921297</v>
+      </c>
       <c r="D77" s="8">
-        <v>46128.661488854166</v>
+        <v>46195.60422127315</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>270</v>
@@ -6158,9 +6164,11 @@
       <c r="B78" s="5">
         <v>46077.57961084491</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46195.60466336805</v>
+      </c>
       <c r="D78" s="5">
-        <v>46174.651739594905</v>
+        <v>46195.60466490741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6396,7 +6404,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46150.168837708334</v>
+        <v>46195.60396552083</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6585,7 +6593,7 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46133.18400270834</v>
+        <v>46195.60422616898</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>295</v>
@@ -6884,7 +6892,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46160.25052104167</v>
+        <v>46195.604670092594</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>274</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -6404,7 +6404,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.60396552083</v>
+        <v>46197.58394950231</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46136.20828810185</v>
+        <v>46197.583529641204</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>288</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46139.16829325231</v>
+        <v>46197.583207523145</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>291</v>
@@ -6578,7 +6578,7 @@
         <v>293</v>
       </c>
       <c r="T84" s="6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U84" s="10" t="s">
         <v>58</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.69994636574</v>
+        <v>46073.53327969907</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.71869384259</v>
+        <v>46092.55202717593</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.78238695602</v>
+        <v>46118.61572028935</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1697,13 +1697,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.69994672453</v>
+        <v>46073.53328005787</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.7187837963</v>
+        <v>46092.55211712963</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.71880180556</v>
+        <v>46092.55213513889</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1762,13 +1762,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.69994701388</v>
+        <v>46073.53328034723</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.718810590275</v>
+        <v>46092.55214392361</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71882512732</v>
+        <v>46092.55215846065</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1827,13 +1827,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.69994730324</v>
+        <v>46073.53328063658</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71882415509</v>
+        <v>46092.552157488426</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71884173611</v>
+        <v>46092.552175069446</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1892,13 +1892,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.699947581015</v>
+        <v>46073.53328091435</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71883331018</v>
+        <v>46092.55216664352</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.75450768518</v>
+        <v>46093.58784101852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1957,13 +1957,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.69994784722</v>
+        <v>46073.53328118056</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.718850590274</v>
+        <v>46092.55218392361</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71886530092</v>
+        <v>46092.552198634265</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2022,11 +2022,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.699948124995</v>
+        <v>46073.53328145834</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.89302402778</v>
+        <v>46127.72635736111</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2069,13 +2069,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.699948379624</v>
+        <v>46073.53328171297</v>
       </c>
       <c r="C11" s="8">
-        <v>46093.86155634259</v>
+        <v>46093.69488967593</v>
       </c>
       <c r="D11" s="8">
-        <v>46093.86157599537</v>
+        <v>46093.694909328704</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2134,11 +2134,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.69994864584</v>
+        <v>46073.533281979166</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46134.69385214121</v>
+        <v>46134.52718547454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2197,13 +2197,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.69994892361</v>
+        <v>46073.53328225695</v>
       </c>
       <c r="C13" s="8">
-        <v>46093.75482240741</v>
+        <v>46093.58815574074</v>
       </c>
       <c r="D13" s="8">
-        <v>46093.7548365625</v>
+        <v>46093.58816989583</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2250,13 +2250,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.69994622685</v>
+        <v>46073.533279560186</v>
       </c>
       <c r="C14" s="5">
-        <v>46093.75466950232</v>
+        <v>46093.58800283565</v>
       </c>
       <c r="D14" s="5">
-        <v>46093.754690856484</v>
+        <v>46093.58802418981</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2315,13 +2315,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.6999465625</v>
+        <v>46073.53327989583</v>
       </c>
       <c r="C15" s="8">
-        <v>46093.754681597224</v>
+        <v>46093.58801493056</v>
       </c>
       <c r="D15" s="8">
-        <v>46093.75469819445</v>
+        <v>46093.588031527775</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2380,13 +2380,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.69994685185</v>
+        <v>46073.533280185184</v>
       </c>
       <c r="C16" s="5">
-        <v>46093.754692187504</v>
+        <v>46093.58802552083</v>
       </c>
       <c r="D16" s="5">
-        <v>46093.75471203704</v>
+        <v>46093.58804537037</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2445,13 +2445,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.69994711806</v>
+        <v>46073.53328045139</v>
       </c>
       <c r="C17" s="8">
-        <v>46093.7547025463</v>
+        <v>46093.58803587963</v>
       </c>
       <c r="D17" s="8">
-        <v>46093.75472228009</v>
+        <v>46093.58805561342</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2510,13 +2510,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.577641701384</v>
+        <v>46077.41097503473</v>
       </c>
       <c r="C18" s="5">
-        <v>46093.754712118054</v>
+        <v>46093.58804545139</v>
       </c>
       <c r="D18" s="5">
-        <v>46093.7547315625</v>
+        <v>46093.588064895834</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2575,13 +2575,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.57773309028</v>
+        <v>46077.41106642361</v>
       </c>
       <c r="C19" s="8">
-        <v>46093.754724375</v>
+        <v>46093.58805770833</v>
       </c>
       <c r="D19" s="8">
-        <v>46093.75474146991</v>
+        <v>46093.588074803236</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2640,13 +2640,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.69994737269</v>
+        <v>46073.53328070602</v>
       </c>
       <c r="C20" s="5">
-        <v>46093.75480502315</v>
+        <v>46093.588138356485</v>
       </c>
       <c r="D20" s="5">
-        <v>46093.75482354166</v>
+        <v>46093.588156875005</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2705,13 +2705,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.69994763889</v>
+        <v>46073.533280972224</v>
       </c>
       <c r="C21" s="8">
-        <v>46093.87454615741</v>
+        <v>46093.70787949074</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.54278021991</v>
+        <v>46139.37611355324</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2758,13 +2758,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.6999481713</v>
+        <v>46073.53328150463</v>
       </c>
       <c r="C22" s="5">
-        <v>46093.75476994213</v>
+        <v>46093.58810327546</v>
       </c>
       <c r="D22" s="5">
-        <v>46093.754786307865</v>
+        <v>46093.58811964121</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2823,13 +2823,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.69994789352</v>
+        <v>46073.53328122685</v>
       </c>
       <c r="C23" s="8">
-        <v>46093.754781041665</v>
+        <v>46093.588114375</v>
       </c>
       <c r="D23" s="8">
-        <v>46093.75479849537</v>
+        <v>46093.5881318287</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2888,13 +2888,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.69994854167</v>
+        <v>46073.533281875</v>
       </c>
       <c r="C24" s="5">
-        <v>46093.874529837965</v>
+        <v>46093.707863171294</v>
       </c>
       <c r="D24" s="5">
-        <v>46093.87454729166</v>
+        <v>46093.707880625</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2953,13 +2953,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.69994881944</v>
+        <v>46073.53328215278</v>
       </c>
       <c r="C25" s="8">
-        <v>46093.75482736111</v>
+        <v>46093.588160694446</v>
       </c>
       <c r="D25" s="8">
-        <v>46093.754844745374</v>
+        <v>46093.5881780787</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -3018,13 +3018,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.699946319444</v>
+        <v>46073.53327965278</v>
       </c>
       <c r="C26" s="5">
-        <v>46093.754836238426</v>
+        <v>46093.588169571754</v>
       </c>
       <c r="D26" s="5">
-        <v>46093.75485591435</v>
+        <v>46093.58818924769</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3083,13 +3083,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46076.88102377315</v>
+        <v>46076.71435710648</v>
       </c>
       <c r="C27" s="8">
-        <v>46093.75484537037</v>
+        <v>46093.58817870371</v>
       </c>
       <c r="D27" s="8">
-        <v>46093.754866759264</v>
+        <v>46093.58820009259</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3148,13 +3148,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.579292766204</v>
+        <v>46077.41262609954</v>
       </c>
       <c r="C28" s="5">
-        <v>46093.75485412037</v>
+        <v>46093.5881874537</v>
       </c>
       <c r="D28" s="5">
-        <v>46093.75487452546</v>
+        <v>46093.5882078588</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>78</v>
@@ -3213,13 +3213,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.579365196754</v>
+        <v>46077.4126985301</v>
       </c>
       <c r="C29" s="8">
-        <v>46093.754862939815</v>
+        <v>46093.58819627315</v>
       </c>
       <c r="D29" s="8">
-        <v>46093.75488136574</v>
+        <v>46093.58821469908</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>81</v>
@@ -3278,13 +3278,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="5">
-        <v>46139.54271195602</v>
+        <v>46139.37604528935</v>
       </c>
       <c r="C30" s="5">
-        <v>46139.5432959375</v>
+        <v>46139.37662927083</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.548176979166</v>
+        <v>46139.3815103125</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3343,11 +3343,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.699946747685</v>
+        <v>46073.533280081014</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46191.83935533564</v>
+        <v>46191.67268866899</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3390,13 +3390,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.69994704861</v>
+        <v>46073.53328038195</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.839348587964</v>
+        <v>46191.67268192129</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.83935060185</v>
+        <v>46191.67268393519</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3455,13 +3455,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.69994738426</v>
+        <v>46073.53328071759</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.68363072917</v>
+        <v>46182.516964062495</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.68413366898</v>
+        <v>46182.51746700231</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3516,13 +3516,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.69994769676</v>
+        <v>46073.53328103009</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.83755203703</v>
+        <v>46191.670885370375</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.83755358796</v>
+        <v>46191.670886921296</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3577,11 +3577,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.69994803241</v>
+        <v>46073.533281365744</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.65273861111</v>
+        <v>46174.48607194444</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3640,13 +3640,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.699948333335</v>
+        <v>46073.53328166666</v>
       </c>
       <c r="C36" s="5">
-        <v>46174.65273003472</v>
+        <v>46174.48606336805</v>
       </c>
       <c r="D36" s="5">
-        <v>46174.652731724535</v>
+        <v>46174.48606505787</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3701,11 +3701,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.699948622685</v>
+        <v>46073.53328195601</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46174.65273809028</v>
+        <v>46174.48607142361</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3760,13 +3760,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.69994892361</v>
+        <v>46073.53328225695</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.836712743054</v>
+        <v>46191.67004607639</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.83671528935</v>
+        <v>46191.670048622684</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3825,13 +3825,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.699949201386</v>
+        <v>46073.53328253472</v>
       </c>
       <c r="C39" s="8">
-        <v>46174.64929829861</v>
+        <v>46174.482631631945</v>
       </c>
       <c r="D39" s="8">
-        <v>46174.64929997685</v>
+        <v>46174.48263331018</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3886,13 +3886,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.69994585648</v>
+        <v>46073.53327918981</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.67566594908</v>
+        <v>46182.50899928241</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.67566810185</v>
+        <v>46182.50900143519</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3947,13 +3947,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.69994628472</v>
+        <v>46073.53327961806</v>
       </c>
       <c r="C41" s="8">
-        <v>46127.78343253472</v>
+        <v>46127.61676586806</v>
       </c>
       <c r="D41" s="8">
-        <v>46127.78344613426</v>
+        <v>46127.61677946759</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4012,13 +4012,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.69994653935</v>
+        <v>46073.53327987269</v>
       </c>
       <c r="C42" s="5">
-        <v>46120.692551064814</v>
+        <v>46120.52588439814</v>
       </c>
       <c r="D42" s="5">
-        <v>46120.69255305556</v>
+        <v>46120.52588638889</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4073,13 +4073,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.69994680556</v>
+        <v>46073.53328013889</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.783406041664</v>
+        <v>46127.616739375</v>
       </c>
       <c r="D43" s="8">
-        <v>46127.783407256946</v>
+        <v>46127.61674059028</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4134,13 +4134,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.69994707176</v>
+        <v>46073.53328040509</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.78341672454</v>
+        <v>46127.616750057874</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.78341805555</v>
+        <v>46127.616751388894</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4195,13 +4195,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.69994733796</v>
+        <v>46073.5332806713</v>
       </c>
       <c r="C45" s="8">
-        <v>46112.49058179398</v>
+        <v>46112.323915127316</v>
       </c>
       <c r="D45" s="8">
-        <v>46139.54791172454</v>
+        <v>46139.38124505787</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4260,13 +4260,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.69994759259</v>
+        <v>46073.53328092593</v>
       </c>
       <c r="C46" s="5">
-        <v>46104.82754436343</v>
+        <v>46104.66087769676</v>
       </c>
       <c r="D46" s="5">
-        <v>46104.82754626157</v>
+        <v>46104.66087959491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4321,13 +4321,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.699947870366</v>
+        <v>46073.53328120371</v>
       </c>
       <c r="C47" s="8">
-        <v>46132.57863260417</v>
+        <v>46132.4119659375</v>
       </c>
       <c r="D47" s="8">
-        <v>46132.57863447917</v>
+        <v>46132.4119678125</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4382,13 +4382,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46076.881105196764</v>
+        <v>46076.71443853009</v>
       </c>
       <c r="C48" s="5">
-        <v>46112.48812652778</v>
+        <v>46112.32145986111</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.54788491898</v>
+        <v>46139.38121825231</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4447,13 +4447,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46076.88918239583</v>
+        <v>46076.72251572917</v>
       </c>
       <c r="C49" s="8">
-        <v>46112.49184642361</v>
+        <v>46112.32517975694</v>
       </c>
       <c r="D49" s="8">
-        <v>46112.491848171296</v>
+        <v>46112.325181504624</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4502,13 +4502,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46076.88930991898</v>
+        <v>46076.72264325232</v>
       </c>
       <c r="C50" s="5">
-        <v>46112.50604163195</v>
+        <v>46112.339374965275</v>
       </c>
       <c r="D50" s="5">
-        <v>46112.50608989583</v>
+        <v>46112.33942322917</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4557,13 +4557,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.579487986106</v>
+        <v>46077.41282131945</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.83738681713</v>
+        <v>46191.67072015046</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.83738863426</v>
+        <v>46191.67072196759</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4622,13 +4622,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.5872287963</v>
+        <v>46077.42056212963</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.68337204861</v>
+        <v>46182.516705381946</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.68337341435</v>
+        <v>46182.51670674769</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4677,13 +4677,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.58741234954</v>
+        <v>46077.42074568287</v>
       </c>
       <c r="C53" s="8">
-        <v>46182.69210525463</v>
+        <v>46182.52543858797</v>
       </c>
       <c r="D53" s="8">
-        <v>46182.69210671296</v>
+        <v>46182.525440046295</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -4732,13 +4732,13 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.57954119213</v>
+        <v>46077.412874525464</v>
       </c>
       <c r="C54" s="5">
-        <v>46174.65185637731</v>
+        <v>46174.48518971065</v>
       </c>
       <c r="D54" s="5">
-        <v>46174.6518578588</v>
+        <v>46174.48519119213</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4797,13 +4797,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.587555833336</v>
+        <v>46077.420889166664</v>
       </c>
       <c r="C55" s="8">
-        <v>46094.7587408449</v>
+        <v>46094.59207417824</v>
       </c>
       <c r="D55" s="8">
-        <v>46169.8399244676</v>
+        <v>46169.673257800925</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>110</v>
@@ -4852,13 +4852,13 @@
         <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.5876627199</v>
+        <v>46077.42099605324</v>
       </c>
       <c r="C56" s="5">
-        <v>46174.65173</v>
+        <v>46174.48506333333</v>
       </c>
       <c r="D56" s="5">
-        <v>46174.651731377315</v>
+        <v>46174.48506471065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -4907,13 +4907,13 @@
         <v>197</v>
       </c>
       <c r="B57" s="8">
-        <v>46139.543413900465</v>
+        <v>46139.37674723379</v>
       </c>
       <c r="C57" s="8">
-        <v>46191.840089791665</v>
+        <v>46191.673423125</v>
       </c>
       <c r="D57" s="8">
-        <v>46191.84009155093</v>
+        <v>46191.673424884255</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4972,13 +4972,13 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46139.543700821756</v>
+        <v>46139.37703415509</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.839869421296</v>
+        <v>46191.67320275463</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.83987099537</v>
+        <v>46191.673204328705</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -5027,13 +5027,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46139.54378479166</v>
+        <v>46139.377118125005</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.83995417824</v>
+        <v>46191.67328751157</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.83995613426</v>
+        <v>46191.673289467595</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5082,11 +5082,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.69994815972</v>
+        <v>46073.53328149306</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46129.586425601854</v>
+        <v>46129.41975893518</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5129,13 +5129,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.6999484375</v>
+        <v>46073.53328177083</v>
       </c>
       <c r="C61" s="8">
-        <v>46099.54242106482</v>
+        <v>46099.37575439815</v>
       </c>
       <c r="D61" s="8">
-        <v>46099.54242268519</v>
+        <v>46099.37575601852</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5194,13 +5194,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.699946249995</v>
+        <v>46073.53327958334</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.586253912035</v>
+        <v>46129.41958724537</v>
       </c>
       <c r="D62" s="5">
-        <v>46129.58626813657</v>
+        <v>46129.41960146991</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5259,13 +5259,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46092.494241736116</v>
+        <v>46092.327575069445</v>
       </c>
       <c r="C63" s="8">
-        <v>46129.58641790509</v>
+        <v>46129.41975123843</v>
       </c>
       <c r="D63" s="8">
-        <v>46139.54817715278</v>
+        <v>46139.38151048611</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>115</v>
@@ -5322,11 +5322,11 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.49428590278</v>
+        <v>46092.32761923611</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46154.16811805556</v>
+        <v>46154.00145138889</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5385,11 +5385,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.69994662037</v>
+        <v>46073.5332799537</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46195.6020638426</v>
+        <v>46195.43539717593</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5432,13 +5432,13 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.69994689815</v>
+        <v>46073.53328023148</v>
       </c>
       <c r="C66" s="5">
-        <v>46195.60205410879</v>
+        <v>46195.43538744213</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.60205646991</v>
+        <v>46195.43538980324</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5497,11 +5497,11 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.69994719907</v>
+        <v>46073.53328053241</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.60206259259</v>
+        <v>46195.435395925924</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5560,11 +5560,11 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.69994748842</v>
+        <v>46073.533280821764</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46077.62916171296</v>
+        <v>46077.4624950463</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5607,11 +5607,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.69994777778</v>
+        <v>46073.533281111115</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46092.50399041666</v>
+        <v>46092.337323750005</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5670,11 +5670,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.699948113426</v>
+        <v>46073.533281446755</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46129.58642229167</v>
+        <v>46129.419755625</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5733,11 +5733,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.69994846065</v>
+        <v>46073.53328179398</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46129.5864233912</v>
+        <v>46129.419756724536</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5796,11 +5796,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.699948865746</v>
+        <v>46073.533282199074</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.604225717594</v>
+        <v>46195.43755905093</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5843,11 +5843,11 @@
         <v>258</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.69995097222</v>
+        <v>46073.53328430555</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.67567376157</v>
+        <v>46182.50900709491</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5906,11 +5906,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.69994640046</v>
+        <v>46073.5332797338</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46121.187778182866</v>
+        <v>46121.0211115162</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>56</v>
@@ -5969,11 +5969,11 @@
         <v>263</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.699946782406</v>
+        <v>46073.53328011574</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.8375600463</v>
+        <v>46191.67089337963</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>
@@ -6032,13 +6032,13 @@
         <v>266</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.69994708333</v>
+        <v>46073.53328041667</v>
       </c>
       <c r="C76" s="5">
-        <v>46195.603957824074</v>
+        <v>46195.4372911574</v>
       </c>
       <c r="D76" s="5">
-        <v>46195.603959687505</v>
+        <v>46195.437293020834</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6097,13 +6097,13 @@
         <v>269</v>
       </c>
       <c r="B77" s="8">
-        <v>46076.88127923611</v>
+        <v>46076.71461256944</v>
       </c>
       <c r="C77" s="8">
-        <v>46195.60421921297</v>
+        <v>46195.4375525463</v>
       </c>
       <c r="D77" s="8">
-        <v>46195.60422127315</v>
+        <v>46195.437554606484</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>270</v>
@@ -6162,13 +6162,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.57961084491</v>
+        <v>46077.41294417824</v>
       </c>
       <c r="C78" s="5">
-        <v>46195.60466336805</v>
+        <v>46195.43799670139</v>
       </c>
       <c r="D78" s="5">
-        <v>46195.60466490741</v>
+        <v>46195.43799824074</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6227,11 +6227,11 @@
         <v>275</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.57965403935</v>
+        <v>46077.412987372685</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.692112696765</v>
+        <v>46182.52544603009</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>188</v>
@@ -6290,11 +6290,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.69994733796</v>
+        <v>46073.5332806713</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46078.621237141204</v>
+        <v>46078.45457047454</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>277</v>
@@ -6337,11 +6337,11 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.69994759259</v>
+        <v>46073.53328092593</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46128.16821587963</v>
+        <v>46128.00154921296</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6400,11 +6400,11 @@
         <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.69994784722</v>
+        <v>46073.53328118056</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46197.58394950231</v>
+        <v>46197.41728283565</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6463,11 +6463,11 @@
         <v>287</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.69994813658</v>
+        <v>46073.53328146991</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46197.583529641204</v>
+        <v>46197.41686297454</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>288</v>
@@ -6526,11 +6526,11 @@
         <v>290</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.699948368056</v>
+        <v>46073.533281701384</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.583207523145</v>
+        <v>46197.41654085648</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>291</v>
@@ -6589,11 +6589,11 @@
         <v>294</v>
       </c>
       <c r="B85" s="8">
-        <v>46076.88137268518</v>
+        <v>46076.71470601852</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.60422616898</v>
+        <v>46195.437559502316</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>295</v>
@@ -6652,11 +6652,11 @@
         <v>298</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.69994864584</v>
+        <v>46073.533281979166</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46153.16811694445</v>
+        <v>46153.00145027778</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>225</v>
@@ -6715,11 +6715,11 @@
         <v>301</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.699948912035</v>
+        <v>46073.53328224537</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46154.16785564815</v>
+        <v>46154.00118898148</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>302</v>
@@ -6778,11 +6778,11 @@
         <v>304</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.69994572917</v>
+        <v>46073.533279062496</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46077.638347245374</v>
+        <v>46077.4716805787</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>305</v>
@@ -6825,11 +6825,11 @@
         <v>307</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.699946099536</v>
+        <v>46073.53327943287</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.16794435185</v>
+        <v>46155.00127768518</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>308</v>
@@ -6888,11 +6888,11 @@
         <v>310</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.69994638889</v>
+        <v>46073.53327972222</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.604670092594</v>
+        <v>46195.43800342592</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>274</v>
@@ -6951,11 +6951,11 @@
         <v>313</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.69994668981</v>
+        <v>46073.53328002315</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46161.25032122685</v>
+        <v>46161.083654560185</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>314</v>
@@ -7014,11 +7014,11 @@
         <v>316</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.69994695602</v>
+        <v>46073.53328028935</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.25040996527</v>
+        <v>46162.083743298615</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>317</v>
@@ -7077,11 +7077,11 @@
         <v>319</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.699947245375</v>
+        <v>46073.533280578704</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46077.6387968287</v>
+        <v>46077.47213016204</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>320</v>
@@ -7124,11 +7124,11 @@
         <v>322</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.699947500005</v>
+        <v>46073.53328083333</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.16833755787</v>
+        <v>46174.0016708912</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>323</v>
@@ -7187,11 +7187,11 @@
         <v>326</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.699947789355</v>
+        <v>46073.53328112268</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46174.168340185184</v>
+        <v>46174.00167351852</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>327</v>
@@ -7250,11 +7250,11 @@
         <v>329</v>
       </c>
       <c r="B96" s="5">
-        <v>46092.48971385417</v>
+        <v>46092.3230471875</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46092.497058946756</v>
+        <v>46092.33039228009</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>330</v>
@@ -7303,11 +7303,11 @@
         <v>332</v>
       </c>
       <c r="B97" s="8">
-        <v>46092.49161491898</v>
+        <v>46092.32494825231</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46171.168742951384</v>
+        <v>46171.00207628473</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>333</v>
@@ -7366,11 +7366,11 @@
         <v>335</v>
       </c>
       <c r="B98" s="5">
-        <v>46092.491661747685</v>
+        <v>46092.32499508101</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46181.16820616898</v>
+        <v>46181.001539502315</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>336</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.53327969907</v>
+        <v>46073.69994636574</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55202717593</v>
+        <v>46092.71869384259</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.61572028935</v>
+        <v>46118.78238695602</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1697,13 +1697,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.53328005787</v>
+        <v>46073.69994672453</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55211712963</v>
+        <v>46092.7187837963</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55213513889</v>
+        <v>46092.71880180556</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1762,13 +1762,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.53328034723</v>
+        <v>46073.69994701388</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55214392361</v>
+        <v>46092.718810590275</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55215846065</v>
+        <v>46092.71882512732</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1827,13 +1827,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.53328063658</v>
+        <v>46073.69994730324</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.552157488426</v>
+        <v>46092.71882415509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.552175069446</v>
+        <v>46092.71884173611</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1892,13 +1892,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.53328091435</v>
+        <v>46073.699947581015</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55216664352</v>
+        <v>46092.71883331018</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.58784101852</v>
+        <v>46093.75450768518</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1957,13 +1957,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55218392361</v>
+        <v>46092.718850590274</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.552198634265</v>
+        <v>46092.71886530092</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2022,11 +2022,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.53328145834</v>
+        <v>46073.699948124995</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.72635736111</v>
+        <v>46127.89302402778</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2069,13 +2069,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.53328171297</v>
+        <v>46073.699948379624</v>
       </c>
       <c r="C11" s="8">
-        <v>46093.69488967593</v>
+        <v>46093.86155634259</v>
       </c>
       <c r="D11" s="8">
-        <v>46093.694909328704</v>
+        <v>46093.86157599537</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2134,11 +2134,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46134.52718547454</v>
+        <v>46134.69385214121</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2197,13 +2197,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C13" s="8">
-        <v>46093.58815574074</v>
+        <v>46093.75482240741</v>
       </c>
       <c r="D13" s="8">
-        <v>46093.58816989583</v>
+        <v>46093.7548365625</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2250,13 +2250,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.533279560186</v>
+        <v>46073.69994622685</v>
       </c>
       <c r="C14" s="5">
-        <v>46093.58800283565</v>
+        <v>46093.75466950232</v>
       </c>
       <c r="D14" s="5">
-        <v>46093.58802418981</v>
+        <v>46093.754690856484</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2315,13 +2315,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.53327989583</v>
+        <v>46073.6999465625</v>
       </c>
       <c r="C15" s="8">
-        <v>46093.58801493056</v>
+        <v>46093.754681597224</v>
       </c>
       <c r="D15" s="8">
-        <v>46093.588031527775</v>
+        <v>46093.75469819445</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2380,13 +2380,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.533280185184</v>
+        <v>46073.69994685185</v>
       </c>
       <c r="C16" s="5">
-        <v>46093.58802552083</v>
+        <v>46093.754692187504</v>
       </c>
       <c r="D16" s="5">
-        <v>46093.58804537037</v>
+        <v>46093.75471203704</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2445,13 +2445,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.53328045139</v>
+        <v>46073.69994711806</v>
       </c>
       <c r="C17" s="8">
-        <v>46093.58803587963</v>
+        <v>46093.7547025463</v>
       </c>
       <c r="D17" s="8">
-        <v>46093.58805561342</v>
+        <v>46093.75472228009</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2510,13 +2510,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.41097503473</v>
+        <v>46077.577641701384</v>
       </c>
       <c r="C18" s="5">
-        <v>46093.58804545139</v>
+        <v>46093.754712118054</v>
       </c>
       <c r="D18" s="5">
-        <v>46093.588064895834</v>
+        <v>46093.7547315625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2575,13 +2575,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.41106642361</v>
+        <v>46077.57773309028</v>
       </c>
       <c r="C19" s="8">
-        <v>46093.58805770833</v>
+        <v>46093.754724375</v>
       </c>
       <c r="D19" s="8">
-        <v>46093.588074803236</v>
+        <v>46093.75474146991</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2640,13 +2640,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.53328070602</v>
+        <v>46073.69994737269</v>
       </c>
       <c r="C20" s="5">
-        <v>46093.588138356485</v>
+        <v>46093.75480502315</v>
       </c>
       <c r="D20" s="5">
-        <v>46093.588156875005</v>
+        <v>46093.75482354166</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2705,13 +2705,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.533280972224</v>
+        <v>46073.69994763889</v>
       </c>
       <c r="C21" s="8">
-        <v>46093.70787949074</v>
+        <v>46093.87454615741</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.37611355324</v>
+        <v>46139.54278021991</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2758,13 +2758,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.53328150463</v>
+        <v>46073.6999481713</v>
       </c>
       <c r="C22" s="5">
-        <v>46093.58810327546</v>
+        <v>46093.75476994213</v>
       </c>
       <c r="D22" s="5">
-        <v>46093.58811964121</v>
+        <v>46093.754786307865</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2823,13 +2823,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.53328122685</v>
+        <v>46073.69994789352</v>
       </c>
       <c r="C23" s="8">
-        <v>46093.588114375</v>
+        <v>46093.754781041665</v>
       </c>
       <c r="D23" s="8">
-        <v>46093.5881318287</v>
+        <v>46093.75479849537</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2888,13 +2888,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.533281875</v>
+        <v>46073.69994854167</v>
       </c>
       <c r="C24" s="5">
-        <v>46093.707863171294</v>
+        <v>46093.874529837965</v>
       </c>
       <c r="D24" s="5">
-        <v>46093.707880625</v>
+        <v>46093.87454729166</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2953,13 +2953,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.53328215278</v>
+        <v>46073.69994881944</v>
       </c>
       <c r="C25" s="8">
-        <v>46093.588160694446</v>
+        <v>46093.75482736111</v>
       </c>
       <c r="D25" s="8">
-        <v>46093.5881780787</v>
+        <v>46093.754844745374</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -3018,13 +3018,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.53327965278</v>
+        <v>46073.699946319444</v>
       </c>
       <c r="C26" s="5">
-        <v>46093.588169571754</v>
+        <v>46093.754836238426</v>
       </c>
       <c r="D26" s="5">
-        <v>46093.58818924769</v>
+        <v>46093.75485591435</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3083,13 +3083,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46076.71435710648</v>
+        <v>46076.88102377315</v>
       </c>
       <c r="C27" s="8">
-        <v>46093.58817870371</v>
+        <v>46093.75484537037</v>
       </c>
       <c r="D27" s="8">
-        <v>46093.58820009259</v>
+        <v>46093.754866759264</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3148,13 +3148,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.41262609954</v>
+        <v>46077.579292766204</v>
       </c>
       <c r="C28" s="5">
-        <v>46093.5881874537</v>
+        <v>46093.75485412037</v>
       </c>
       <c r="D28" s="5">
-        <v>46093.5882078588</v>
+        <v>46093.75487452546</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>78</v>
@@ -3213,13 +3213,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.4126985301</v>
+        <v>46077.579365196754</v>
       </c>
       <c r="C29" s="8">
-        <v>46093.58819627315</v>
+        <v>46093.754862939815</v>
       </c>
       <c r="D29" s="8">
-        <v>46093.58821469908</v>
+        <v>46093.75488136574</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>81</v>
@@ -3278,13 +3278,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="5">
-        <v>46139.37604528935</v>
+        <v>46139.54271195602</v>
       </c>
       <c r="C30" s="5">
-        <v>46139.37662927083</v>
+        <v>46139.5432959375</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.3815103125</v>
+        <v>46139.548176979166</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3343,11 +3343,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.533280081014</v>
+        <v>46073.699946747685</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46191.67268866899</v>
+        <v>46191.83935533564</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3390,13 +3390,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.53328038195</v>
+        <v>46073.69994704861</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.67268192129</v>
+        <v>46191.839348587964</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.67268393519</v>
+        <v>46191.83935060185</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3455,13 +3455,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.53328071759</v>
+        <v>46073.69994738426</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.516964062495</v>
+        <v>46182.68363072917</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.51746700231</v>
+        <v>46182.68413366898</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3516,13 +3516,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.53328103009</v>
+        <v>46073.69994769676</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.670885370375</v>
+        <v>46191.83755203703</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.670886921296</v>
+        <v>46191.83755358796</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3577,11 +3577,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.533281365744</v>
+        <v>46073.69994803241</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.48607194444</v>
+        <v>46174.65273861111</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3640,13 +3640,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.53328166666</v>
+        <v>46073.699948333335</v>
       </c>
       <c r="C36" s="5">
-        <v>46174.48606336805</v>
+        <v>46174.65273003472</v>
       </c>
       <c r="D36" s="5">
-        <v>46174.48606505787</v>
+        <v>46174.652731724535</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3701,11 +3701,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.53328195601</v>
+        <v>46073.699948622685</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46174.48607142361</v>
+        <v>46174.65273809028</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3760,13 +3760,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.67004607639</v>
+        <v>46191.836712743054</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.670048622684</v>
+        <v>46191.83671528935</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3825,13 +3825,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.53328253472</v>
+        <v>46073.699949201386</v>
       </c>
       <c r="C39" s="8">
-        <v>46174.482631631945</v>
+        <v>46174.64929829861</v>
       </c>
       <c r="D39" s="8">
-        <v>46174.48263331018</v>
+        <v>46174.64929997685</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3886,13 +3886,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.53327918981</v>
+        <v>46073.69994585648</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.50899928241</v>
+        <v>46182.67566594908</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.50900143519</v>
+        <v>46182.67566810185</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3947,13 +3947,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.53327961806</v>
+        <v>46073.69994628472</v>
       </c>
       <c r="C41" s="8">
-        <v>46127.61676586806</v>
+        <v>46127.78343253472</v>
       </c>
       <c r="D41" s="8">
-        <v>46127.61677946759</v>
+        <v>46127.78344613426</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4012,13 +4012,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.53327987269</v>
+        <v>46073.69994653935</v>
       </c>
       <c r="C42" s="5">
-        <v>46120.52588439814</v>
+        <v>46120.692551064814</v>
       </c>
       <c r="D42" s="5">
-        <v>46120.52588638889</v>
+        <v>46120.69255305556</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4073,13 +4073,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.53328013889</v>
+        <v>46073.69994680556</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.616739375</v>
+        <v>46127.783406041664</v>
       </c>
       <c r="D43" s="8">
-        <v>46127.61674059028</v>
+        <v>46127.783407256946</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4134,13 +4134,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.53328040509</v>
+        <v>46073.69994707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.616750057874</v>
+        <v>46127.78341672454</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.616751388894</v>
+        <v>46127.78341805555</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4195,13 +4195,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C45" s="8">
-        <v>46112.323915127316</v>
+        <v>46112.49058179398</v>
       </c>
       <c r="D45" s="8">
-        <v>46139.38124505787</v>
+        <v>46139.54791172454</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4260,13 +4260,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C46" s="5">
-        <v>46104.66087769676</v>
+        <v>46104.82754436343</v>
       </c>
       <c r="D46" s="5">
-        <v>46104.66087959491</v>
+        <v>46104.82754626157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4321,13 +4321,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.53328120371</v>
+        <v>46073.699947870366</v>
       </c>
       <c r="C47" s="8">
-        <v>46132.4119659375</v>
+        <v>46132.57863260417</v>
       </c>
       <c r="D47" s="8">
-        <v>46132.4119678125</v>
+        <v>46132.57863447917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4382,13 +4382,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46076.71443853009</v>
+        <v>46076.881105196764</v>
       </c>
       <c r="C48" s="5">
-        <v>46112.32145986111</v>
+        <v>46112.48812652778</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.38121825231</v>
+        <v>46139.54788491898</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4447,13 +4447,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46076.72251572917</v>
+        <v>46076.88918239583</v>
       </c>
       <c r="C49" s="8">
-        <v>46112.32517975694</v>
+        <v>46112.49184642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46112.325181504624</v>
+        <v>46112.491848171296</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4502,13 +4502,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46076.72264325232</v>
+        <v>46076.88930991898</v>
       </c>
       <c r="C50" s="5">
-        <v>46112.339374965275</v>
+        <v>46112.50604163195</v>
       </c>
       <c r="D50" s="5">
-        <v>46112.33942322917</v>
+        <v>46112.50608989583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4557,13 +4557,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.41282131945</v>
+        <v>46077.579487986106</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.67072015046</v>
+        <v>46191.83738681713</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.67072196759</v>
+        <v>46191.83738863426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4622,13 +4622,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.42056212963</v>
+        <v>46077.5872287963</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.516705381946</v>
+        <v>46182.68337204861</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.51670674769</v>
+        <v>46182.68337341435</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4677,13 +4677,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.42074568287</v>
+        <v>46077.58741234954</v>
       </c>
       <c r="C53" s="8">
-        <v>46182.52543858797</v>
+        <v>46182.69210525463</v>
       </c>
       <c r="D53" s="8">
-        <v>46182.525440046295</v>
+        <v>46182.69210671296</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -4732,13 +4732,13 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.412874525464</v>
+        <v>46077.57954119213</v>
       </c>
       <c r="C54" s="5">
-        <v>46174.48518971065</v>
+        <v>46174.65185637731</v>
       </c>
       <c r="D54" s="5">
-        <v>46174.48519119213</v>
+        <v>46174.6518578588</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4797,13 +4797,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.420889166664</v>
+        <v>46077.587555833336</v>
       </c>
       <c r="C55" s="8">
-        <v>46094.59207417824</v>
+        <v>46094.7587408449</v>
       </c>
       <c r="D55" s="8">
-        <v>46169.673257800925</v>
+        <v>46169.8399244676</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>110</v>
@@ -4852,13 +4852,13 @@
         <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.42099605324</v>
+        <v>46077.5876627199</v>
       </c>
       <c r="C56" s="5">
-        <v>46174.48506333333</v>
+        <v>46174.65173</v>
       </c>
       <c r="D56" s="5">
-        <v>46174.48506471065</v>
+        <v>46174.651731377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -4907,13 +4907,13 @@
         <v>197</v>
       </c>
       <c r="B57" s="8">
-        <v>46139.37674723379</v>
+        <v>46139.543413900465</v>
       </c>
       <c r="C57" s="8">
-        <v>46191.673423125</v>
+        <v>46191.840089791665</v>
       </c>
       <c r="D57" s="8">
-        <v>46191.673424884255</v>
+        <v>46191.84009155093</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4972,13 +4972,13 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46139.37703415509</v>
+        <v>46139.543700821756</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.67320275463</v>
+        <v>46191.839869421296</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.673204328705</v>
+        <v>46191.83987099537</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -5027,13 +5027,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46139.377118125005</v>
+        <v>46139.54378479166</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.67328751157</v>
+        <v>46191.83995417824</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.673289467595</v>
+        <v>46191.83995613426</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5082,11 +5082,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.53328149306</v>
+        <v>46073.69994815972</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46129.41975893518</v>
+        <v>46129.586425601854</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5129,13 +5129,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.53328177083</v>
+        <v>46073.6999484375</v>
       </c>
       <c r="C61" s="8">
-        <v>46099.37575439815</v>
+        <v>46099.54242106482</v>
       </c>
       <c r="D61" s="8">
-        <v>46099.37575601852</v>
+        <v>46099.54242268519</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5194,13 +5194,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.53327958334</v>
+        <v>46073.699946249995</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.41958724537</v>
+        <v>46129.586253912035</v>
       </c>
       <c r="D62" s="5">
-        <v>46129.41960146991</v>
+        <v>46129.58626813657</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5259,13 +5259,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46092.327575069445</v>
+        <v>46092.494241736116</v>
       </c>
       <c r="C63" s="8">
-        <v>46129.41975123843</v>
+        <v>46129.58641790509</v>
       </c>
       <c r="D63" s="8">
-        <v>46139.38151048611</v>
+        <v>46139.54817715278</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>115</v>
@@ -5322,11 +5322,11 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.32761923611</v>
+        <v>46092.49428590278</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46154.00145138889</v>
+        <v>46154.16811805556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5385,11 +5385,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.5332799537</v>
+        <v>46073.69994662037</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46195.43539717593</v>
+        <v>46195.6020638426</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5432,13 +5432,13 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.53328023148</v>
+        <v>46073.69994689815</v>
       </c>
       <c r="C66" s="5">
-        <v>46195.43538744213</v>
+        <v>46195.60205410879</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.43538980324</v>
+        <v>46195.60205646991</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5497,11 +5497,11 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.53328053241</v>
+        <v>46073.69994719907</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.435395925924</v>
+        <v>46195.60206259259</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5560,11 +5560,11 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.533280821764</v>
+        <v>46073.69994748842</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46077.4624950463</v>
+        <v>46077.62916171296</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5607,11 +5607,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.533281111115</v>
+        <v>46073.69994777778</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46092.337323750005</v>
+        <v>46092.50399041666</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5670,11 +5670,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.533281446755</v>
+        <v>46073.699948113426</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46129.419755625</v>
+        <v>46129.58642229167</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5733,11 +5733,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.53328179398</v>
+        <v>46073.69994846065</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46129.419756724536</v>
+        <v>46129.5864233912</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5796,11 +5796,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.533282199074</v>
+        <v>46073.699948865746</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.43755905093</v>
+        <v>46195.604225717594</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5843,11 +5843,11 @@
         <v>258</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.53328430555</v>
+        <v>46073.69995097222</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.50900709491</v>
+        <v>46182.67567376157</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5906,11 +5906,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.5332797338</v>
+        <v>46073.69994640046</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46121.0211115162</v>
+        <v>46121.187778182866</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>56</v>
@@ -5969,11 +5969,11 @@
         <v>263</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.53328011574</v>
+        <v>46073.699946782406</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.67089337963</v>
+        <v>46191.8375600463</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>
@@ -6032,13 +6032,13 @@
         <v>266</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.53328041667</v>
+        <v>46073.69994708333</v>
       </c>
       <c r="C76" s="5">
-        <v>46195.4372911574</v>
+        <v>46195.603957824074</v>
       </c>
       <c r="D76" s="5">
-        <v>46195.437293020834</v>
+        <v>46195.603959687505</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6097,13 +6097,13 @@
         <v>269</v>
       </c>
       <c r="B77" s="8">
-        <v>46076.71461256944</v>
+        <v>46076.88127923611</v>
       </c>
       <c r="C77" s="8">
-        <v>46195.4375525463</v>
+        <v>46195.60421921297</v>
       </c>
       <c r="D77" s="8">
-        <v>46195.437554606484</v>
+        <v>46195.60422127315</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>270</v>
@@ -6162,13 +6162,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.41294417824</v>
+        <v>46077.57961084491</v>
       </c>
       <c r="C78" s="5">
-        <v>46195.43799670139</v>
+        <v>46195.60466336805</v>
       </c>
       <c r="D78" s="5">
-        <v>46195.43799824074</v>
+        <v>46195.60466490741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6227,11 +6227,11 @@
         <v>275</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.412987372685</v>
+        <v>46077.57965403935</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.52544603009</v>
+        <v>46182.692112696765</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>188</v>
@@ -6290,11 +6290,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46078.45457047454</v>
+        <v>46078.621237141204</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>277</v>
@@ -6337,11 +6337,11 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46128.00154921296</v>
+        <v>46128.16821587963</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6400,11 +6400,11 @@
         <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46197.41728283565</v>
+        <v>46197.58394950231</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6463,11 +6463,11 @@
         <v>287</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.53328146991</v>
+        <v>46073.69994813658</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46197.41686297454</v>
+        <v>46197.583529641204</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>288</v>
@@ -6526,11 +6526,11 @@
         <v>290</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.533281701384</v>
+        <v>46073.699948368056</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.41654085648</v>
+        <v>46197.583207523145</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>291</v>
@@ -6589,11 +6589,11 @@
         <v>294</v>
       </c>
       <c r="B85" s="8">
-        <v>46076.71470601852</v>
+        <v>46076.88137268518</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.437559502316</v>
+        <v>46195.60422616898</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>295</v>
@@ -6652,11 +6652,11 @@
         <v>298</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46153.00145027778</v>
+        <v>46153.16811694445</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>225</v>
@@ -6715,11 +6715,11 @@
         <v>301</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.53328224537</v>
+        <v>46073.699948912035</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46154.00118898148</v>
+        <v>46154.16785564815</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>302</v>
@@ -6778,11 +6778,11 @@
         <v>304</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.533279062496</v>
+        <v>46073.69994572917</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46077.4716805787</v>
+        <v>46077.638347245374</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>305</v>
@@ -6825,11 +6825,11 @@
         <v>307</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.53327943287</v>
+        <v>46073.699946099536</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.00127768518</v>
+        <v>46155.16794435185</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>308</v>
@@ -6888,11 +6888,11 @@
         <v>310</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.53327972222</v>
+        <v>46073.69994638889</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.43800342592</v>
+        <v>46195.604670092594</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>274</v>
@@ -6951,11 +6951,11 @@
         <v>313</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.53328002315</v>
+        <v>46073.69994668981</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46161.083654560185</v>
+        <v>46161.25032122685</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>314</v>
@@ -7014,11 +7014,11 @@
         <v>316</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.53328028935</v>
+        <v>46073.69994695602</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.083743298615</v>
+        <v>46162.25040996527</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>317</v>
@@ -7077,11 +7077,11 @@
         <v>319</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.533280578704</v>
+        <v>46073.699947245375</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46077.47213016204</v>
+        <v>46077.6387968287</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>320</v>
@@ -7124,11 +7124,11 @@
         <v>322</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.53328083333</v>
+        <v>46073.699947500005</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.0016708912</v>
+        <v>46174.16833755787</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>323</v>
@@ -7187,11 +7187,11 @@
         <v>326</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.53328112268</v>
+        <v>46073.699947789355</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46174.00167351852</v>
+        <v>46174.168340185184</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>327</v>
@@ -7250,11 +7250,11 @@
         <v>329</v>
       </c>
       <c r="B96" s="5">
-        <v>46092.3230471875</v>
+        <v>46092.48971385417</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46092.33039228009</v>
+        <v>46092.497058946756</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>330</v>
@@ -7303,11 +7303,11 @@
         <v>332</v>
       </c>
       <c r="B97" s="8">
-        <v>46092.32494825231</v>
+        <v>46092.49161491898</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46171.00207628473</v>
+        <v>46171.168742951384</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>333</v>
@@ -7366,11 +7366,11 @@
         <v>335</v>
       </c>
       <c r="B98" s="5">
-        <v>46092.32499508101</v>
+        <v>46092.491661747685</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46181.001539502315</v>
+        <v>46181.16820616898</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>336</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -6404,7 +6404,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46197.58394950231</v>
+        <v>46198.59349042824</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46197.583529641204</v>
+        <v>46198.592367060184</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>288</v>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.583207523145</v>
+        <v>46198.59272494213</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>291</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.69994636574</v>
+        <v>46073.53327969907</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.71869384259</v>
+        <v>46092.55202717593</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.78238695602</v>
+        <v>46118.61572028935</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1697,13 +1697,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.69994672453</v>
+        <v>46073.53328005787</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.7187837963</v>
+        <v>46092.55211712963</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.71880180556</v>
+        <v>46092.55213513889</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1762,13 +1762,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.69994701388</v>
+        <v>46073.53328034723</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.718810590275</v>
+        <v>46092.55214392361</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71882512732</v>
+        <v>46092.55215846065</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1827,13 +1827,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.69994730324</v>
+        <v>46073.53328063658</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71882415509</v>
+        <v>46092.552157488426</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71884173611</v>
+        <v>46092.552175069446</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1892,13 +1892,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.699947581015</v>
+        <v>46073.53328091435</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71883331018</v>
+        <v>46092.55216664352</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.75450768518</v>
+        <v>46093.58784101852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1957,13 +1957,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.69994784722</v>
+        <v>46073.53328118056</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.718850590274</v>
+        <v>46092.55218392361</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71886530092</v>
+        <v>46092.552198634265</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2022,11 +2022,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.699948124995</v>
+        <v>46073.53328145834</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.89302402778</v>
+        <v>46127.72635736111</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2069,13 +2069,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.699948379624</v>
+        <v>46073.53328171297</v>
       </c>
       <c r="C11" s="8">
-        <v>46093.86155634259</v>
+        <v>46093.69488967593</v>
       </c>
       <c r="D11" s="8">
-        <v>46093.86157599537</v>
+        <v>46093.694909328704</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2134,11 +2134,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.69994864584</v>
+        <v>46073.533281979166</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46134.69385214121</v>
+        <v>46134.52718547454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2197,13 +2197,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.69994892361</v>
+        <v>46073.53328225695</v>
       </c>
       <c r="C13" s="8">
-        <v>46093.75482240741</v>
+        <v>46093.58815574074</v>
       </c>
       <c r="D13" s="8">
-        <v>46093.7548365625</v>
+        <v>46093.58816989583</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2250,13 +2250,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.69994622685</v>
+        <v>46073.533279560186</v>
       </c>
       <c r="C14" s="5">
-        <v>46093.75466950232</v>
+        <v>46093.58800283565</v>
       </c>
       <c r="D14" s="5">
-        <v>46093.754690856484</v>
+        <v>46093.58802418981</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2315,13 +2315,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.6999465625</v>
+        <v>46073.53327989583</v>
       </c>
       <c r="C15" s="8">
-        <v>46093.754681597224</v>
+        <v>46093.58801493056</v>
       </c>
       <c r="D15" s="8">
-        <v>46093.75469819445</v>
+        <v>46093.588031527775</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2380,13 +2380,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.69994685185</v>
+        <v>46073.533280185184</v>
       </c>
       <c r="C16" s="5">
-        <v>46093.754692187504</v>
+        <v>46093.58802552083</v>
       </c>
       <c r="D16" s="5">
-        <v>46093.75471203704</v>
+        <v>46093.58804537037</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2445,13 +2445,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.69994711806</v>
+        <v>46073.53328045139</v>
       </c>
       <c r="C17" s="8">
-        <v>46093.7547025463</v>
+        <v>46093.58803587963</v>
       </c>
       <c r="D17" s="8">
-        <v>46093.75472228009</v>
+        <v>46093.58805561342</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2510,13 +2510,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.577641701384</v>
+        <v>46077.41097503473</v>
       </c>
       <c r="C18" s="5">
-        <v>46093.754712118054</v>
+        <v>46093.58804545139</v>
       </c>
       <c r="D18" s="5">
-        <v>46093.7547315625</v>
+        <v>46093.588064895834</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2575,13 +2575,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.57773309028</v>
+        <v>46077.41106642361</v>
       </c>
       <c r="C19" s="8">
-        <v>46093.754724375</v>
+        <v>46093.58805770833</v>
       </c>
       <c r="D19" s="8">
-        <v>46093.75474146991</v>
+        <v>46093.588074803236</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2640,13 +2640,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.69994737269</v>
+        <v>46073.53328070602</v>
       </c>
       <c r="C20" s="5">
-        <v>46093.75480502315</v>
+        <v>46093.588138356485</v>
       </c>
       <c r="D20" s="5">
-        <v>46093.75482354166</v>
+        <v>46093.588156875005</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2705,13 +2705,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.69994763889</v>
+        <v>46073.533280972224</v>
       </c>
       <c r="C21" s="8">
-        <v>46093.87454615741</v>
+        <v>46093.70787949074</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.54278021991</v>
+        <v>46139.37611355324</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2758,13 +2758,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.6999481713</v>
+        <v>46073.53328150463</v>
       </c>
       <c r="C22" s="5">
-        <v>46093.75476994213</v>
+        <v>46093.58810327546</v>
       </c>
       <c r="D22" s="5">
-        <v>46093.754786307865</v>
+        <v>46093.58811964121</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2823,13 +2823,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.69994789352</v>
+        <v>46073.53328122685</v>
       </c>
       <c r="C23" s="8">
-        <v>46093.754781041665</v>
+        <v>46093.588114375</v>
       </c>
       <c r="D23" s="8">
-        <v>46093.75479849537</v>
+        <v>46093.5881318287</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2888,13 +2888,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.69994854167</v>
+        <v>46073.533281875</v>
       </c>
       <c r="C24" s="5">
-        <v>46093.874529837965</v>
+        <v>46093.707863171294</v>
       </c>
       <c r="D24" s="5">
-        <v>46093.87454729166</v>
+        <v>46093.707880625</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2953,13 +2953,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.69994881944</v>
+        <v>46073.53328215278</v>
       </c>
       <c r="C25" s="8">
-        <v>46093.75482736111</v>
+        <v>46093.588160694446</v>
       </c>
       <c r="D25" s="8">
-        <v>46093.754844745374</v>
+        <v>46093.5881780787</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -3018,13 +3018,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.699946319444</v>
+        <v>46073.53327965278</v>
       </c>
       <c r="C26" s="5">
-        <v>46093.754836238426</v>
+        <v>46093.588169571754</v>
       </c>
       <c r="D26" s="5">
-        <v>46093.75485591435</v>
+        <v>46093.58818924769</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3083,13 +3083,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46076.88102377315</v>
+        <v>46076.71435710648</v>
       </c>
       <c r="C27" s="8">
-        <v>46093.75484537037</v>
+        <v>46093.58817870371</v>
       </c>
       <c r="D27" s="8">
-        <v>46093.754866759264</v>
+        <v>46093.58820009259</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3148,13 +3148,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.579292766204</v>
+        <v>46077.41262609954</v>
       </c>
       <c r="C28" s="5">
-        <v>46093.75485412037</v>
+        <v>46093.5881874537</v>
       </c>
       <c r="D28" s="5">
-        <v>46093.75487452546</v>
+        <v>46093.5882078588</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>78</v>
@@ -3213,13 +3213,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.579365196754</v>
+        <v>46077.4126985301</v>
       </c>
       <c r="C29" s="8">
-        <v>46093.754862939815</v>
+        <v>46093.58819627315</v>
       </c>
       <c r="D29" s="8">
-        <v>46093.75488136574</v>
+        <v>46093.58821469908</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>81</v>
@@ -3278,13 +3278,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="5">
-        <v>46139.54271195602</v>
+        <v>46139.37604528935</v>
       </c>
       <c r="C30" s="5">
-        <v>46139.5432959375</v>
+        <v>46139.37662927083</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.548176979166</v>
+        <v>46139.3815103125</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3343,11 +3343,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.699946747685</v>
+        <v>46073.533280081014</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46191.83935533564</v>
+        <v>46191.67268866899</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3390,13 +3390,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.69994704861</v>
+        <v>46073.53328038195</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.839348587964</v>
+        <v>46191.67268192129</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.83935060185</v>
+        <v>46191.67268393519</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3455,13 +3455,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.69994738426</v>
+        <v>46073.53328071759</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.68363072917</v>
+        <v>46182.516964062495</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.68413366898</v>
+        <v>46182.51746700231</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3516,13 +3516,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.69994769676</v>
+        <v>46073.53328103009</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.83755203703</v>
+        <v>46191.670885370375</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.83755358796</v>
+        <v>46191.670886921296</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3577,11 +3577,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.69994803241</v>
+        <v>46073.533281365744</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.65273861111</v>
+        <v>46174.48607194444</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3640,13 +3640,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.699948333335</v>
+        <v>46073.53328166666</v>
       </c>
       <c r="C36" s="5">
-        <v>46174.65273003472</v>
+        <v>46174.48606336805</v>
       </c>
       <c r="D36" s="5">
-        <v>46174.652731724535</v>
+        <v>46174.48606505787</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3701,11 +3701,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.699948622685</v>
+        <v>46073.53328195601</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46174.65273809028</v>
+        <v>46174.48607142361</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3760,13 +3760,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.69994892361</v>
+        <v>46073.53328225695</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.836712743054</v>
+        <v>46191.67004607639</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.83671528935</v>
+        <v>46191.670048622684</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3825,13 +3825,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.699949201386</v>
+        <v>46073.53328253472</v>
       </c>
       <c r="C39" s="8">
-        <v>46174.64929829861</v>
+        <v>46174.482631631945</v>
       </c>
       <c r="D39" s="8">
-        <v>46174.64929997685</v>
+        <v>46174.48263331018</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3886,13 +3886,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.69994585648</v>
+        <v>46073.53327918981</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.67566594908</v>
+        <v>46182.50899928241</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.67566810185</v>
+        <v>46182.50900143519</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3947,13 +3947,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.69994628472</v>
+        <v>46073.53327961806</v>
       </c>
       <c r="C41" s="8">
-        <v>46127.78343253472</v>
+        <v>46127.61676586806</v>
       </c>
       <c r="D41" s="8">
-        <v>46127.78344613426</v>
+        <v>46127.61677946759</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4012,13 +4012,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.69994653935</v>
+        <v>46073.53327987269</v>
       </c>
       <c r="C42" s="5">
-        <v>46120.692551064814</v>
+        <v>46120.52588439814</v>
       </c>
       <c r="D42" s="5">
-        <v>46120.69255305556</v>
+        <v>46120.52588638889</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4073,13 +4073,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.69994680556</v>
+        <v>46073.53328013889</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.783406041664</v>
+        <v>46127.616739375</v>
       </c>
       <c r="D43" s="8">
-        <v>46127.783407256946</v>
+        <v>46127.61674059028</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4134,13 +4134,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.69994707176</v>
+        <v>46073.53328040509</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.78341672454</v>
+        <v>46127.616750057874</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.78341805555</v>
+        <v>46127.616751388894</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4195,13 +4195,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.69994733796</v>
+        <v>46073.5332806713</v>
       </c>
       <c r="C45" s="8">
-        <v>46112.49058179398</v>
+        <v>46112.323915127316</v>
       </c>
       <c r="D45" s="8">
-        <v>46139.54791172454</v>
+        <v>46139.38124505787</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4260,13 +4260,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.69994759259</v>
+        <v>46073.53328092593</v>
       </c>
       <c r="C46" s="5">
-        <v>46104.82754436343</v>
+        <v>46104.66087769676</v>
       </c>
       <c r="D46" s="5">
-        <v>46104.82754626157</v>
+        <v>46104.66087959491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4321,13 +4321,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.699947870366</v>
+        <v>46073.53328120371</v>
       </c>
       <c r="C47" s="8">
-        <v>46132.57863260417</v>
+        <v>46132.4119659375</v>
       </c>
       <c r="D47" s="8">
-        <v>46132.57863447917</v>
+        <v>46132.4119678125</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4382,13 +4382,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46076.881105196764</v>
+        <v>46076.71443853009</v>
       </c>
       <c r="C48" s="5">
-        <v>46112.48812652778</v>
+        <v>46112.32145986111</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.54788491898</v>
+        <v>46139.38121825231</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4447,13 +4447,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46076.88918239583</v>
+        <v>46076.72251572917</v>
       </c>
       <c r="C49" s="8">
-        <v>46112.49184642361</v>
+        <v>46112.32517975694</v>
       </c>
       <c r="D49" s="8">
-        <v>46112.491848171296</v>
+        <v>46112.325181504624</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4502,13 +4502,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46076.88930991898</v>
+        <v>46076.72264325232</v>
       </c>
       <c r="C50" s="5">
-        <v>46112.50604163195</v>
+        <v>46112.339374965275</v>
       </c>
       <c r="D50" s="5">
-        <v>46112.50608989583</v>
+        <v>46112.33942322917</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4557,13 +4557,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.579487986106</v>
+        <v>46077.41282131945</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.83738681713</v>
+        <v>46191.67072015046</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.83738863426</v>
+        <v>46191.67072196759</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4622,13 +4622,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.5872287963</v>
+        <v>46077.42056212963</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.68337204861</v>
+        <v>46182.516705381946</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.68337341435</v>
+        <v>46182.51670674769</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4677,13 +4677,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.58741234954</v>
+        <v>46077.42074568287</v>
       </c>
       <c r="C53" s="8">
-        <v>46182.69210525463</v>
+        <v>46182.52543858797</v>
       </c>
       <c r="D53" s="8">
-        <v>46182.69210671296</v>
+        <v>46182.525440046295</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -4732,13 +4732,13 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.57954119213</v>
+        <v>46077.412874525464</v>
       </c>
       <c r="C54" s="5">
-        <v>46174.65185637731</v>
+        <v>46174.48518971065</v>
       </c>
       <c r="D54" s="5">
-        <v>46174.6518578588</v>
+        <v>46174.48519119213</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4797,13 +4797,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.587555833336</v>
+        <v>46077.420889166664</v>
       </c>
       <c r="C55" s="8">
-        <v>46094.7587408449</v>
+        <v>46094.59207417824</v>
       </c>
       <c r="D55" s="8">
-        <v>46169.8399244676</v>
+        <v>46169.673257800925</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>110</v>
@@ -4852,13 +4852,13 @@
         <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.5876627199</v>
+        <v>46077.42099605324</v>
       </c>
       <c r="C56" s="5">
-        <v>46174.65173</v>
+        <v>46174.48506333333</v>
       </c>
       <c r="D56" s="5">
-        <v>46174.651731377315</v>
+        <v>46174.48506471065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -4907,13 +4907,13 @@
         <v>197</v>
       </c>
       <c r="B57" s="8">
-        <v>46139.543413900465</v>
+        <v>46139.37674723379</v>
       </c>
       <c r="C57" s="8">
-        <v>46191.840089791665</v>
+        <v>46191.673423125</v>
       </c>
       <c r="D57" s="8">
-        <v>46191.84009155093</v>
+        <v>46191.673424884255</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4972,13 +4972,13 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46139.543700821756</v>
+        <v>46139.37703415509</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.839869421296</v>
+        <v>46191.67320275463</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.83987099537</v>
+        <v>46191.673204328705</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -5027,13 +5027,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46139.54378479166</v>
+        <v>46139.377118125005</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.83995417824</v>
+        <v>46191.67328751157</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.83995613426</v>
+        <v>46191.673289467595</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5082,11 +5082,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.69994815972</v>
+        <v>46073.53328149306</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46129.586425601854</v>
+        <v>46129.41975893518</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5129,13 +5129,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.6999484375</v>
+        <v>46073.53328177083</v>
       </c>
       <c r="C61" s="8">
-        <v>46099.54242106482</v>
+        <v>46099.37575439815</v>
       </c>
       <c r="D61" s="8">
-        <v>46099.54242268519</v>
+        <v>46099.37575601852</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5194,13 +5194,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.699946249995</v>
+        <v>46073.53327958334</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.586253912035</v>
+        <v>46129.41958724537</v>
       </c>
       <c r="D62" s="5">
-        <v>46129.58626813657</v>
+        <v>46129.41960146991</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5259,13 +5259,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46092.494241736116</v>
+        <v>46092.327575069445</v>
       </c>
       <c r="C63" s="8">
-        <v>46129.58641790509</v>
+        <v>46129.41975123843</v>
       </c>
       <c r="D63" s="8">
-        <v>46139.54817715278</v>
+        <v>46139.38151048611</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>115</v>
@@ -5322,11 +5322,11 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.49428590278</v>
+        <v>46092.32761923611</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46154.16811805556</v>
+        <v>46154.00145138889</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5385,11 +5385,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.69994662037</v>
+        <v>46073.5332799537</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46195.6020638426</v>
+        <v>46195.43539717593</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5432,13 +5432,13 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.69994689815</v>
+        <v>46073.53328023148</v>
       </c>
       <c r="C66" s="5">
-        <v>46195.60205410879</v>
+        <v>46195.43538744213</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.60205646991</v>
+        <v>46195.43538980324</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5497,11 +5497,11 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.69994719907</v>
+        <v>46073.53328053241</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.60206259259</v>
+        <v>46195.435395925924</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5560,11 +5560,11 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.69994748842</v>
+        <v>46073.533280821764</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46077.62916171296</v>
+        <v>46077.4624950463</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5607,11 +5607,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.69994777778</v>
+        <v>46073.533281111115</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46092.50399041666</v>
+        <v>46092.337323750005</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5670,11 +5670,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.699948113426</v>
+        <v>46073.533281446755</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46129.58642229167</v>
+        <v>46129.419755625</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5733,11 +5733,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.69994846065</v>
+        <v>46073.53328179398</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46129.5864233912</v>
+        <v>46129.419756724536</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5796,11 +5796,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.699948865746</v>
+        <v>46073.533282199074</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.604225717594</v>
+        <v>46195.43755905093</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5843,11 +5843,11 @@
         <v>258</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.69995097222</v>
+        <v>46073.53328430555</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.67567376157</v>
+        <v>46182.50900709491</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5906,11 +5906,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.69994640046</v>
+        <v>46073.5332797338</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46121.187778182866</v>
+        <v>46121.0211115162</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>56</v>
@@ -5969,11 +5969,11 @@
         <v>263</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.699946782406</v>
+        <v>46073.53328011574</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.8375600463</v>
+        <v>46191.67089337963</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>
@@ -6032,13 +6032,13 @@
         <v>266</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.69994708333</v>
+        <v>46073.53328041667</v>
       </c>
       <c r="C76" s="5">
-        <v>46195.603957824074</v>
+        <v>46195.4372911574</v>
       </c>
       <c r="D76" s="5">
-        <v>46195.603959687505</v>
+        <v>46195.437293020834</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6097,13 +6097,13 @@
         <v>269</v>
       </c>
       <c r="B77" s="8">
-        <v>46076.88127923611</v>
+        <v>46076.71461256944</v>
       </c>
       <c r="C77" s="8">
-        <v>46195.60421921297</v>
+        <v>46195.4375525463</v>
       </c>
       <c r="D77" s="8">
-        <v>46195.60422127315</v>
+        <v>46195.437554606484</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>270</v>
@@ -6162,13 +6162,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.57961084491</v>
+        <v>46077.41294417824</v>
       </c>
       <c r="C78" s="5">
-        <v>46195.60466336805</v>
+        <v>46195.43799670139</v>
       </c>
       <c r="D78" s="5">
-        <v>46195.60466490741</v>
+        <v>46195.43799824074</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6227,11 +6227,11 @@
         <v>275</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.57965403935</v>
+        <v>46077.412987372685</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.692112696765</v>
+        <v>46182.52544603009</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>188</v>
@@ -6290,11 +6290,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.69994733796</v>
+        <v>46073.5332806713</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46078.621237141204</v>
+        <v>46078.45457047454</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>277</v>
@@ -6337,11 +6337,11 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.69994759259</v>
+        <v>46073.53328092593</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46128.16821587963</v>
+        <v>46128.00154921296</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6400,11 +6400,11 @@
         <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.69994784722</v>
+        <v>46073.53328118056</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.59349042824</v>
+        <v>46198.426823761576</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6463,11 +6463,11 @@
         <v>287</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.69994813658</v>
+        <v>46073.53328146991</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46198.592367060184</v>
+        <v>46198.42570039352</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>288</v>
@@ -6526,11 +6526,11 @@
         <v>290</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.699948368056</v>
+        <v>46073.533281701384</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46198.59272494213</v>
+        <v>46198.426058275465</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>291</v>
@@ -6589,11 +6589,11 @@
         <v>294</v>
       </c>
       <c r="B85" s="8">
-        <v>46076.88137268518</v>
+        <v>46076.71470601852</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.60422616898</v>
+        <v>46195.437559502316</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>295</v>
@@ -6652,11 +6652,11 @@
         <v>298</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.69994864584</v>
+        <v>46073.533281979166</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46153.16811694445</v>
+        <v>46153.00145027778</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>225</v>
@@ -6715,11 +6715,11 @@
         <v>301</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.699948912035</v>
+        <v>46073.53328224537</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46154.16785564815</v>
+        <v>46154.00118898148</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>302</v>
@@ -6778,11 +6778,11 @@
         <v>304</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.69994572917</v>
+        <v>46073.533279062496</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46077.638347245374</v>
+        <v>46077.4716805787</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>305</v>
@@ -6825,11 +6825,11 @@
         <v>307</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.699946099536</v>
+        <v>46073.53327943287</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.16794435185</v>
+        <v>46155.00127768518</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>308</v>
@@ -6888,11 +6888,11 @@
         <v>310</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.69994638889</v>
+        <v>46073.53327972222</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.604670092594</v>
+        <v>46195.43800342592</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>274</v>
@@ -6951,11 +6951,11 @@
         <v>313</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.69994668981</v>
+        <v>46073.53328002315</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46161.25032122685</v>
+        <v>46161.083654560185</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>314</v>
@@ -7014,11 +7014,11 @@
         <v>316</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.69994695602</v>
+        <v>46073.53328028935</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.25040996527</v>
+        <v>46162.083743298615</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>317</v>
@@ -7077,11 +7077,11 @@
         <v>319</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.699947245375</v>
+        <v>46073.533280578704</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46077.6387968287</v>
+        <v>46077.47213016204</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>320</v>
@@ -7124,11 +7124,11 @@
         <v>322</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.699947500005</v>
+        <v>46073.53328083333</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.16833755787</v>
+        <v>46174.0016708912</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>323</v>
@@ -7187,11 +7187,11 @@
         <v>326</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.699947789355</v>
+        <v>46073.53328112268</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46174.168340185184</v>
+        <v>46174.00167351852</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>327</v>
@@ -7250,11 +7250,11 @@
         <v>329</v>
       </c>
       <c r="B96" s="5">
-        <v>46092.48971385417</v>
+        <v>46092.3230471875</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46092.497058946756</v>
+        <v>46092.33039228009</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>330</v>
@@ -7303,11 +7303,11 @@
         <v>332</v>
       </c>
       <c r="B97" s="8">
-        <v>46092.49161491898</v>
+        <v>46092.32494825231</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46171.168742951384</v>
+        <v>46171.00207628473</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>333</v>
@@ -7366,11 +7366,11 @@
         <v>335</v>
       </c>
       <c r="B98" s="5">
-        <v>46092.491661747685</v>
+        <v>46092.32499508101</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46181.16820616898</v>
+        <v>46181.001539502315</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>336</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.53327969907</v>
+        <v>46073.69994636574</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55202717593</v>
+        <v>46092.71869384259</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.61572028935</v>
+        <v>46118.78238695602</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1697,13 +1697,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.53328005787</v>
+        <v>46073.69994672453</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55211712963</v>
+        <v>46092.7187837963</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55213513889</v>
+        <v>46092.71880180556</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1762,13 +1762,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.53328034723</v>
+        <v>46073.69994701388</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55214392361</v>
+        <v>46092.718810590275</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55215846065</v>
+        <v>46092.71882512732</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1827,13 +1827,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.53328063658</v>
+        <v>46073.69994730324</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.552157488426</v>
+        <v>46092.71882415509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.552175069446</v>
+        <v>46092.71884173611</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1892,13 +1892,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.53328091435</v>
+        <v>46073.699947581015</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55216664352</v>
+        <v>46092.71883331018</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.58784101852</v>
+        <v>46093.75450768518</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1957,13 +1957,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55218392361</v>
+        <v>46092.718850590274</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.552198634265</v>
+        <v>46092.71886530092</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2022,11 +2022,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.53328145834</v>
+        <v>46073.699948124995</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.72635736111</v>
+        <v>46127.89302402778</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2069,13 +2069,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.53328171297</v>
+        <v>46073.699948379624</v>
       </c>
       <c r="C11" s="8">
-        <v>46093.69488967593</v>
+        <v>46093.86155634259</v>
       </c>
       <c r="D11" s="8">
-        <v>46093.694909328704</v>
+        <v>46093.86157599537</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2134,11 +2134,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46134.52718547454</v>
+        <v>46134.69385214121</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2197,13 +2197,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C13" s="8">
-        <v>46093.58815574074</v>
+        <v>46093.75482240741</v>
       </c>
       <c r="D13" s="8">
-        <v>46093.58816989583</v>
+        <v>46093.7548365625</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2250,13 +2250,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.533279560186</v>
+        <v>46073.69994622685</v>
       </c>
       <c r="C14" s="5">
-        <v>46093.58800283565</v>
+        <v>46093.75466950232</v>
       </c>
       <c r="D14" s="5">
-        <v>46093.58802418981</v>
+        <v>46093.754690856484</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2315,13 +2315,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.53327989583</v>
+        <v>46073.6999465625</v>
       </c>
       <c r="C15" s="8">
-        <v>46093.58801493056</v>
+        <v>46093.754681597224</v>
       </c>
       <c r="D15" s="8">
-        <v>46093.588031527775</v>
+        <v>46093.75469819445</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2380,13 +2380,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.533280185184</v>
+        <v>46073.69994685185</v>
       </c>
       <c r="C16" s="5">
-        <v>46093.58802552083</v>
+        <v>46093.754692187504</v>
       </c>
       <c r="D16" s="5">
-        <v>46093.58804537037</v>
+        <v>46093.75471203704</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2445,13 +2445,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.53328045139</v>
+        <v>46073.69994711806</v>
       </c>
       <c r="C17" s="8">
-        <v>46093.58803587963</v>
+        <v>46093.7547025463</v>
       </c>
       <c r="D17" s="8">
-        <v>46093.58805561342</v>
+        <v>46093.75472228009</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2510,13 +2510,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.41097503473</v>
+        <v>46077.577641701384</v>
       </c>
       <c r="C18" s="5">
-        <v>46093.58804545139</v>
+        <v>46093.754712118054</v>
       </c>
       <c r="D18" s="5">
-        <v>46093.588064895834</v>
+        <v>46093.7547315625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2575,13 +2575,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.41106642361</v>
+        <v>46077.57773309028</v>
       </c>
       <c r="C19" s="8">
-        <v>46093.58805770833</v>
+        <v>46093.754724375</v>
       </c>
       <c r="D19" s="8">
-        <v>46093.588074803236</v>
+        <v>46093.75474146991</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2640,13 +2640,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.53328070602</v>
+        <v>46073.69994737269</v>
       </c>
       <c r="C20" s="5">
-        <v>46093.588138356485</v>
+        <v>46093.75480502315</v>
       </c>
       <c r="D20" s="5">
-        <v>46093.588156875005</v>
+        <v>46093.75482354166</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2705,13 +2705,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.533280972224</v>
+        <v>46073.69994763889</v>
       </c>
       <c r="C21" s="8">
-        <v>46093.70787949074</v>
+        <v>46093.87454615741</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.37611355324</v>
+        <v>46139.54278021991</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2758,13 +2758,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.53328150463</v>
+        <v>46073.6999481713</v>
       </c>
       <c r="C22" s="5">
-        <v>46093.58810327546</v>
+        <v>46093.75476994213</v>
       </c>
       <c r="D22" s="5">
-        <v>46093.58811964121</v>
+        <v>46093.754786307865</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2823,13 +2823,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.53328122685</v>
+        <v>46073.69994789352</v>
       </c>
       <c r="C23" s="8">
-        <v>46093.588114375</v>
+        <v>46093.754781041665</v>
       </c>
       <c r="D23" s="8">
-        <v>46093.5881318287</v>
+        <v>46093.75479849537</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2888,13 +2888,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.533281875</v>
+        <v>46073.69994854167</v>
       </c>
       <c r="C24" s="5">
-        <v>46093.707863171294</v>
+        <v>46093.874529837965</v>
       </c>
       <c r="D24" s="5">
-        <v>46093.707880625</v>
+        <v>46093.87454729166</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2953,13 +2953,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.53328215278</v>
+        <v>46073.69994881944</v>
       </c>
       <c r="C25" s="8">
-        <v>46093.588160694446</v>
+        <v>46093.75482736111</v>
       </c>
       <c r="D25" s="8">
-        <v>46093.5881780787</v>
+        <v>46093.754844745374</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -3018,13 +3018,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.53327965278</v>
+        <v>46073.699946319444</v>
       </c>
       <c r="C26" s="5">
-        <v>46093.588169571754</v>
+        <v>46093.754836238426</v>
       </c>
       <c r="D26" s="5">
-        <v>46093.58818924769</v>
+        <v>46093.75485591435</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3083,13 +3083,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46076.71435710648</v>
+        <v>46076.88102377315</v>
       </c>
       <c r="C27" s="8">
-        <v>46093.58817870371</v>
+        <v>46093.75484537037</v>
       </c>
       <c r="D27" s="8">
-        <v>46093.58820009259</v>
+        <v>46093.754866759264</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3148,13 +3148,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.41262609954</v>
+        <v>46077.579292766204</v>
       </c>
       <c r="C28" s="5">
-        <v>46093.5881874537</v>
+        <v>46093.75485412037</v>
       </c>
       <c r="D28" s="5">
-        <v>46093.5882078588</v>
+        <v>46093.75487452546</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>78</v>
@@ -3213,13 +3213,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.4126985301</v>
+        <v>46077.579365196754</v>
       </c>
       <c r="C29" s="8">
-        <v>46093.58819627315</v>
+        <v>46093.754862939815</v>
       </c>
       <c r="D29" s="8">
-        <v>46093.58821469908</v>
+        <v>46093.75488136574</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>81</v>
@@ -3278,13 +3278,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="5">
-        <v>46139.37604528935</v>
+        <v>46139.54271195602</v>
       </c>
       <c r="C30" s="5">
-        <v>46139.37662927083</v>
+        <v>46139.5432959375</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.3815103125</v>
+        <v>46139.548176979166</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3343,11 +3343,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.533280081014</v>
+        <v>46073.699946747685</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46191.67268866899</v>
+        <v>46191.83935533564</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3390,13 +3390,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.53328038195</v>
+        <v>46073.69994704861</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.67268192129</v>
+        <v>46191.839348587964</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.67268393519</v>
+        <v>46191.83935060185</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3455,13 +3455,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.53328071759</v>
+        <v>46073.69994738426</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.516964062495</v>
+        <v>46182.68363072917</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.51746700231</v>
+        <v>46182.68413366898</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3516,13 +3516,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.53328103009</v>
+        <v>46073.69994769676</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.670885370375</v>
+        <v>46191.83755203703</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.670886921296</v>
+        <v>46191.83755358796</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3577,11 +3577,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.533281365744</v>
+        <v>46073.69994803241</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.48607194444</v>
+        <v>46174.65273861111</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3640,13 +3640,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.53328166666</v>
+        <v>46073.699948333335</v>
       </c>
       <c r="C36" s="5">
-        <v>46174.48606336805</v>
+        <v>46174.65273003472</v>
       </c>
       <c r="D36" s="5">
-        <v>46174.48606505787</v>
+        <v>46174.652731724535</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3701,11 +3701,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.53328195601</v>
+        <v>46073.699948622685</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46174.48607142361</v>
+        <v>46174.65273809028</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3760,13 +3760,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.67004607639</v>
+        <v>46191.836712743054</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.670048622684</v>
+        <v>46191.83671528935</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3825,13 +3825,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.53328253472</v>
+        <v>46073.699949201386</v>
       </c>
       <c r="C39" s="8">
-        <v>46174.482631631945</v>
+        <v>46174.64929829861</v>
       </c>
       <c r="D39" s="8">
-        <v>46174.48263331018</v>
+        <v>46174.64929997685</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3886,13 +3886,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.53327918981</v>
+        <v>46073.69994585648</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.50899928241</v>
+        <v>46182.67566594908</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.50900143519</v>
+        <v>46182.67566810185</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3947,13 +3947,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.53327961806</v>
+        <v>46073.69994628472</v>
       </c>
       <c r="C41" s="8">
-        <v>46127.61676586806</v>
+        <v>46127.78343253472</v>
       </c>
       <c r="D41" s="8">
-        <v>46127.61677946759</v>
+        <v>46127.78344613426</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4012,13 +4012,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.53327987269</v>
+        <v>46073.69994653935</v>
       </c>
       <c r="C42" s="5">
-        <v>46120.52588439814</v>
+        <v>46120.692551064814</v>
       </c>
       <c r="D42" s="5">
-        <v>46120.52588638889</v>
+        <v>46120.69255305556</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4073,13 +4073,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.53328013889</v>
+        <v>46073.69994680556</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.616739375</v>
+        <v>46127.783406041664</v>
       </c>
       <c r="D43" s="8">
-        <v>46127.61674059028</v>
+        <v>46127.783407256946</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4134,13 +4134,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.53328040509</v>
+        <v>46073.69994707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.616750057874</v>
+        <v>46127.78341672454</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.616751388894</v>
+        <v>46127.78341805555</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4195,13 +4195,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C45" s="8">
-        <v>46112.323915127316</v>
+        <v>46112.49058179398</v>
       </c>
       <c r="D45" s="8">
-        <v>46139.38124505787</v>
+        <v>46139.54791172454</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4260,13 +4260,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C46" s="5">
-        <v>46104.66087769676</v>
+        <v>46104.82754436343</v>
       </c>
       <c r="D46" s="5">
-        <v>46104.66087959491</v>
+        <v>46104.82754626157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4321,13 +4321,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.53328120371</v>
+        <v>46073.699947870366</v>
       </c>
       <c r="C47" s="8">
-        <v>46132.4119659375</v>
+        <v>46132.57863260417</v>
       </c>
       <c r="D47" s="8">
-        <v>46132.4119678125</v>
+        <v>46132.57863447917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4382,13 +4382,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46076.71443853009</v>
+        <v>46076.881105196764</v>
       </c>
       <c r="C48" s="5">
-        <v>46112.32145986111</v>
+        <v>46112.48812652778</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.38121825231</v>
+        <v>46139.54788491898</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4447,13 +4447,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46076.72251572917</v>
+        <v>46076.88918239583</v>
       </c>
       <c r="C49" s="8">
-        <v>46112.32517975694</v>
+        <v>46112.49184642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46112.325181504624</v>
+        <v>46112.491848171296</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4502,13 +4502,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46076.72264325232</v>
+        <v>46076.88930991898</v>
       </c>
       <c r="C50" s="5">
-        <v>46112.339374965275</v>
+        <v>46112.50604163195</v>
       </c>
       <c r="D50" s="5">
-        <v>46112.33942322917</v>
+        <v>46112.50608989583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4557,13 +4557,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.41282131945</v>
+        <v>46077.579487986106</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.67072015046</v>
+        <v>46191.83738681713</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.67072196759</v>
+        <v>46191.83738863426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4622,13 +4622,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.42056212963</v>
+        <v>46077.5872287963</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.516705381946</v>
+        <v>46182.68337204861</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.51670674769</v>
+        <v>46182.68337341435</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4677,13 +4677,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.42074568287</v>
+        <v>46077.58741234954</v>
       </c>
       <c r="C53" s="8">
-        <v>46182.52543858797</v>
+        <v>46182.69210525463</v>
       </c>
       <c r="D53" s="8">
-        <v>46182.525440046295</v>
+        <v>46182.69210671296</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -4732,13 +4732,13 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.412874525464</v>
+        <v>46077.57954119213</v>
       </c>
       <c r="C54" s="5">
-        <v>46174.48518971065</v>
+        <v>46174.65185637731</v>
       </c>
       <c r="D54" s="5">
-        <v>46174.48519119213</v>
+        <v>46174.6518578588</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4797,13 +4797,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.420889166664</v>
+        <v>46077.587555833336</v>
       </c>
       <c r="C55" s="8">
-        <v>46094.59207417824</v>
+        <v>46094.7587408449</v>
       </c>
       <c r="D55" s="8">
-        <v>46169.673257800925</v>
+        <v>46169.8399244676</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>110</v>
@@ -4852,13 +4852,13 @@
         <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.42099605324</v>
+        <v>46077.5876627199</v>
       </c>
       <c r="C56" s="5">
-        <v>46174.48506333333</v>
+        <v>46174.65173</v>
       </c>
       <c r="D56" s="5">
-        <v>46174.48506471065</v>
+        <v>46174.651731377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -4907,13 +4907,13 @@
         <v>197</v>
       </c>
       <c r="B57" s="8">
-        <v>46139.37674723379</v>
+        <v>46139.543413900465</v>
       </c>
       <c r="C57" s="8">
-        <v>46191.673423125</v>
+        <v>46191.840089791665</v>
       </c>
       <c r="D57" s="8">
-        <v>46191.673424884255</v>
+        <v>46191.84009155093</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4972,13 +4972,13 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46139.37703415509</v>
+        <v>46139.543700821756</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.67320275463</v>
+        <v>46191.839869421296</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.673204328705</v>
+        <v>46191.83987099537</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -5027,13 +5027,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46139.377118125005</v>
+        <v>46139.54378479166</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.67328751157</v>
+        <v>46191.83995417824</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.673289467595</v>
+        <v>46191.83995613426</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5082,11 +5082,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.53328149306</v>
+        <v>46073.69994815972</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46129.41975893518</v>
+        <v>46129.586425601854</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5129,13 +5129,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.53328177083</v>
+        <v>46073.6999484375</v>
       </c>
       <c r="C61" s="8">
-        <v>46099.37575439815</v>
+        <v>46099.54242106482</v>
       </c>
       <c r="D61" s="8">
-        <v>46099.37575601852</v>
+        <v>46099.54242268519</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5194,13 +5194,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.53327958334</v>
+        <v>46073.699946249995</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.41958724537</v>
+        <v>46129.586253912035</v>
       </c>
       <c r="D62" s="5">
-        <v>46129.41960146991</v>
+        <v>46129.58626813657</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5259,13 +5259,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46092.327575069445</v>
+        <v>46092.494241736116</v>
       </c>
       <c r="C63" s="8">
-        <v>46129.41975123843</v>
+        <v>46129.58641790509</v>
       </c>
       <c r="D63" s="8">
-        <v>46139.38151048611</v>
+        <v>46139.54817715278</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>115</v>
@@ -5322,11 +5322,11 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.32761923611</v>
+        <v>46092.49428590278</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46154.00145138889</v>
+        <v>46154.16811805556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5385,11 +5385,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.5332799537</v>
+        <v>46073.69994662037</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46195.43539717593</v>
+        <v>46195.6020638426</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5432,13 +5432,13 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.53328023148</v>
+        <v>46073.69994689815</v>
       </c>
       <c r="C66" s="5">
-        <v>46195.43538744213</v>
+        <v>46195.60205410879</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.43538980324</v>
+        <v>46195.60205646991</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5497,11 +5497,11 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.53328053241</v>
+        <v>46073.69994719907</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.435395925924</v>
+        <v>46195.60206259259</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5560,11 +5560,11 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.533280821764</v>
+        <v>46073.69994748842</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46077.4624950463</v>
+        <v>46077.62916171296</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5607,11 +5607,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.533281111115</v>
+        <v>46073.69994777778</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46092.337323750005</v>
+        <v>46092.50399041666</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5670,11 +5670,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.533281446755</v>
+        <v>46073.699948113426</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46129.419755625</v>
+        <v>46129.58642229167</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5733,11 +5733,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.53328179398</v>
+        <v>46073.69994846065</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46129.419756724536</v>
+        <v>46129.5864233912</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5796,11 +5796,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.533282199074</v>
+        <v>46073.699948865746</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.43755905093</v>
+        <v>46195.604225717594</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5843,11 +5843,11 @@
         <v>258</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.53328430555</v>
+        <v>46073.69995097222</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.50900709491</v>
+        <v>46182.67567376157</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5906,11 +5906,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.5332797338</v>
+        <v>46073.69994640046</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46121.0211115162</v>
+        <v>46121.187778182866</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>56</v>
@@ -5969,11 +5969,11 @@
         <v>263</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.53328011574</v>
+        <v>46073.699946782406</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.67089337963</v>
+        <v>46191.8375600463</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>
@@ -6032,13 +6032,13 @@
         <v>266</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.53328041667</v>
+        <v>46073.69994708333</v>
       </c>
       <c r="C76" s="5">
-        <v>46195.4372911574</v>
+        <v>46195.603957824074</v>
       </c>
       <c r="D76" s="5">
-        <v>46195.437293020834</v>
+        <v>46195.603959687505</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6097,13 +6097,13 @@
         <v>269</v>
       </c>
       <c r="B77" s="8">
-        <v>46076.71461256944</v>
+        <v>46076.88127923611</v>
       </c>
       <c r="C77" s="8">
-        <v>46195.4375525463</v>
+        <v>46195.60421921297</v>
       </c>
       <c r="D77" s="8">
-        <v>46195.437554606484</v>
+        <v>46195.60422127315</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>270</v>
@@ -6162,13 +6162,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.41294417824</v>
+        <v>46077.57961084491</v>
       </c>
       <c r="C78" s="5">
-        <v>46195.43799670139</v>
+        <v>46195.60466336805</v>
       </c>
       <c r="D78" s="5">
-        <v>46195.43799824074</v>
+        <v>46195.60466490741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6227,11 +6227,11 @@
         <v>275</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.412987372685</v>
+        <v>46077.57965403935</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.52544603009</v>
+        <v>46182.692112696765</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>188</v>
@@ -6290,11 +6290,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46078.45457047454</v>
+        <v>46078.621237141204</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>277</v>
@@ -6337,11 +6337,11 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46128.00154921296</v>
+        <v>46128.16821587963</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6400,11 +6400,11 @@
         <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.426823761576</v>
+        <v>46198.59349042824</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6463,11 +6463,11 @@
         <v>287</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.53328146991</v>
+        <v>46073.69994813658</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46198.42570039352</v>
+        <v>46198.592367060184</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>288</v>
@@ -6526,11 +6526,11 @@
         <v>290</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.533281701384</v>
+        <v>46073.699948368056</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46198.426058275465</v>
+        <v>46198.59272494213</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>291</v>
@@ -6589,11 +6589,11 @@
         <v>294</v>
       </c>
       <c r="B85" s="8">
-        <v>46076.71470601852</v>
+        <v>46076.88137268518</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.437559502316</v>
+        <v>46195.60422616898</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>295</v>
@@ -6652,11 +6652,11 @@
         <v>298</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46153.00145027778</v>
+        <v>46153.16811694445</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>225</v>
@@ -6715,11 +6715,11 @@
         <v>301</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.53328224537</v>
+        <v>46073.699948912035</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46154.00118898148</v>
+        <v>46154.16785564815</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>302</v>
@@ -6778,11 +6778,11 @@
         <v>304</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.533279062496</v>
+        <v>46073.69994572917</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46077.4716805787</v>
+        <v>46077.638347245374</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>305</v>
@@ -6825,11 +6825,11 @@
         <v>307</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.53327943287</v>
+        <v>46073.699946099536</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.00127768518</v>
+        <v>46155.16794435185</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>308</v>
@@ -6888,11 +6888,11 @@
         <v>310</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.53327972222</v>
+        <v>46073.69994638889</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.43800342592</v>
+        <v>46195.604670092594</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>274</v>
@@ -6951,11 +6951,11 @@
         <v>313</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.53328002315</v>
+        <v>46073.69994668981</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46161.083654560185</v>
+        <v>46161.25032122685</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>314</v>
@@ -7014,11 +7014,11 @@
         <v>316</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.53328028935</v>
+        <v>46073.69994695602</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.083743298615</v>
+        <v>46162.25040996527</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>317</v>
@@ -7077,11 +7077,11 @@
         <v>319</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.533280578704</v>
+        <v>46073.699947245375</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46077.47213016204</v>
+        <v>46077.6387968287</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>320</v>
@@ -7124,11 +7124,11 @@
         <v>322</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.53328083333</v>
+        <v>46073.699947500005</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.0016708912</v>
+        <v>46174.16833755787</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>323</v>
@@ -7187,11 +7187,11 @@
         <v>326</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.53328112268</v>
+        <v>46073.699947789355</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46174.00167351852</v>
+        <v>46174.168340185184</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>327</v>
@@ -7250,11 +7250,11 @@
         <v>329</v>
       </c>
       <c r="B96" s="5">
-        <v>46092.3230471875</v>
+        <v>46092.48971385417</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46092.33039228009</v>
+        <v>46092.497058946756</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>330</v>
@@ -7303,11 +7303,11 @@
         <v>332</v>
       </c>
       <c r="B97" s="8">
-        <v>46092.32494825231</v>
+        <v>46092.49161491898</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46171.00207628473</v>
+        <v>46171.168742951384</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>333</v>
@@ -7366,11 +7366,11 @@
         <v>335</v>
       </c>
       <c r="B98" s="5">
-        <v>46092.32499508101</v>
+        <v>46092.491661747685</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46181.001539502315</v>
+        <v>46181.16820616898</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>336</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46195.6020638426</v>
+        <v>46198.821161875</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5434,11 +5434,9 @@
       <c r="B66" s="5">
         <v>46073.69994689815</v>
       </c>
-      <c r="C66" s="5">
-        <v>46195.60205410879</v>
-      </c>
+      <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46195.60205646991</v>
+        <v>46198.822638171296</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5501,7 +5499,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.60206259259</v>
+        <v>46198.8211615162</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5847,7 +5845,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.67567376157</v>
+        <v>46198.8234224537</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5973,7 +5971,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46191.8375600463</v>
+        <v>46198.823039097224</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46198.822638171296</v>
+        <v>46199.82444644676</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46198.8234224537</v>
+        <v>46199.830143969906</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46198.823039097224</v>
+        <v>46199.82646660879</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.69994636574</v>
+        <v>46073.53327969907</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.71869384259</v>
+        <v>46092.55202717593</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.78238695602</v>
+        <v>46118.61572028935</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1697,13 +1697,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.69994672453</v>
+        <v>46073.53328005787</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.7187837963</v>
+        <v>46092.55211712963</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.71880180556</v>
+        <v>46092.55213513889</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1762,13 +1762,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.69994701388</v>
+        <v>46073.53328034723</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.718810590275</v>
+        <v>46092.55214392361</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71882512732</v>
+        <v>46092.55215846065</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1827,13 +1827,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.69994730324</v>
+        <v>46073.53328063658</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71882415509</v>
+        <v>46092.552157488426</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71884173611</v>
+        <v>46092.552175069446</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1892,13 +1892,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.699947581015</v>
+        <v>46073.53328091435</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71883331018</v>
+        <v>46092.55216664352</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.75450768518</v>
+        <v>46093.58784101852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1957,13 +1957,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.69994784722</v>
+        <v>46073.53328118056</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.718850590274</v>
+        <v>46092.55218392361</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71886530092</v>
+        <v>46092.552198634265</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2022,11 +2022,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.699948124995</v>
+        <v>46073.53328145834</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.89302402778</v>
+        <v>46127.72635736111</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2069,13 +2069,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.699948379624</v>
+        <v>46073.53328171297</v>
       </c>
       <c r="C11" s="8">
-        <v>46093.86155634259</v>
+        <v>46093.69488967593</v>
       </c>
       <c r="D11" s="8">
-        <v>46093.86157599537</v>
+        <v>46093.694909328704</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2134,11 +2134,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.69994864584</v>
+        <v>46073.533281979166</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46134.69385214121</v>
+        <v>46134.52718547454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2197,13 +2197,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.69994892361</v>
+        <v>46073.53328225695</v>
       </c>
       <c r="C13" s="8">
-        <v>46093.75482240741</v>
+        <v>46093.58815574074</v>
       </c>
       <c r="D13" s="8">
-        <v>46093.7548365625</v>
+        <v>46093.58816989583</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2250,13 +2250,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.69994622685</v>
+        <v>46073.533279560186</v>
       </c>
       <c r="C14" s="5">
-        <v>46093.75466950232</v>
+        <v>46093.58800283565</v>
       </c>
       <c r="D14" s="5">
-        <v>46093.754690856484</v>
+        <v>46093.58802418981</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2315,13 +2315,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.6999465625</v>
+        <v>46073.53327989583</v>
       </c>
       <c r="C15" s="8">
-        <v>46093.754681597224</v>
+        <v>46093.58801493056</v>
       </c>
       <c r="D15" s="8">
-        <v>46093.75469819445</v>
+        <v>46093.588031527775</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2380,13 +2380,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.69994685185</v>
+        <v>46073.533280185184</v>
       </c>
       <c r="C16" s="5">
-        <v>46093.754692187504</v>
+        <v>46093.58802552083</v>
       </c>
       <c r="D16" s="5">
-        <v>46093.75471203704</v>
+        <v>46093.58804537037</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2445,13 +2445,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.69994711806</v>
+        <v>46073.53328045139</v>
       </c>
       <c r="C17" s="8">
-        <v>46093.7547025463</v>
+        <v>46093.58803587963</v>
       </c>
       <c r="D17" s="8">
-        <v>46093.75472228009</v>
+        <v>46093.58805561342</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2510,13 +2510,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.577641701384</v>
+        <v>46077.41097503473</v>
       </c>
       <c r="C18" s="5">
-        <v>46093.754712118054</v>
+        <v>46093.58804545139</v>
       </c>
       <c r="D18" s="5">
-        <v>46093.7547315625</v>
+        <v>46093.588064895834</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2575,13 +2575,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.57773309028</v>
+        <v>46077.41106642361</v>
       </c>
       <c r="C19" s="8">
-        <v>46093.754724375</v>
+        <v>46093.58805770833</v>
       </c>
       <c r="D19" s="8">
-        <v>46093.75474146991</v>
+        <v>46093.588074803236</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2640,13 +2640,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.69994737269</v>
+        <v>46073.53328070602</v>
       </c>
       <c r="C20" s="5">
-        <v>46093.75480502315</v>
+        <v>46093.588138356485</v>
       </c>
       <c r="D20" s="5">
-        <v>46093.75482354166</v>
+        <v>46093.588156875005</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2705,13 +2705,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.69994763889</v>
+        <v>46073.533280972224</v>
       </c>
       <c r="C21" s="8">
-        <v>46093.87454615741</v>
+        <v>46093.70787949074</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.54278021991</v>
+        <v>46139.37611355324</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2758,13 +2758,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.6999481713</v>
+        <v>46073.53328150463</v>
       </c>
       <c r="C22" s="5">
-        <v>46093.75476994213</v>
+        <v>46093.58810327546</v>
       </c>
       <c r="D22" s="5">
-        <v>46093.754786307865</v>
+        <v>46093.58811964121</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2823,13 +2823,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.69994789352</v>
+        <v>46073.53328122685</v>
       </c>
       <c r="C23" s="8">
-        <v>46093.754781041665</v>
+        <v>46093.588114375</v>
       </c>
       <c r="D23" s="8">
-        <v>46093.75479849537</v>
+        <v>46093.5881318287</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2888,13 +2888,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.69994854167</v>
+        <v>46073.533281875</v>
       </c>
       <c r="C24" s="5">
-        <v>46093.874529837965</v>
+        <v>46093.707863171294</v>
       </c>
       <c r="D24" s="5">
-        <v>46093.87454729166</v>
+        <v>46093.707880625</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2953,13 +2953,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.69994881944</v>
+        <v>46073.53328215278</v>
       </c>
       <c r="C25" s="8">
-        <v>46093.75482736111</v>
+        <v>46093.588160694446</v>
       </c>
       <c r="D25" s="8">
-        <v>46093.754844745374</v>
+        <v>46093.5881780787</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -3018,13 +3018,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.699946319444</v>
+        <v>46073.53327965278</v>
       </c>
       <c r="C26" s="5">
-        <v>46093.754836238426</v>
+        <v>46093.588169571754</v>
       </c>
       <c r="D26" s="5">
-        <v>46093.75485591435</v>
+        <v>46093.58818924769</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3083,13 +3083,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46076.88102377315</v>
+        <v>46076.71435710648</v>
       </c>
       <c r="C27" s="8">
-        <v>46093.75484537037</v>
+        <v>46093.58817870371</v>
       </c>
       <c r="D27" s="8">
-        <v>46093.754866759264</v>
+        <v>46093.58820009259</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3148,13 +3148,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.579292766204</v>
+        <v>46077.41262609954</v>
       </c>
       <c r="C28" s="5">
-        <v>46093.75485412037</v>
+        <v>46093.5881874537</v>
       </c>
       <c r="D28" s="5">
-        <v>46093.75487452546</v>
+        <v>46093.5882078588</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>78</v>
@@ -3213,13 +3213,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.579365196754</v>
+        <v>46077.4126985301</v>
       </c>
       <c r="C29" s="8">
-        <v>46093.754862939815</v>
+        <v>46093.58819627315</v>
       </c>
       <c r="D29" s="8">
-        <v>46093.75488136574</v>
+        <v>46093.58821469908</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>81</v>
@@ -3278,13 +3278,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="5">
-        <v>46139.54271195602</v>
+        <v>46139.37604528935</v>
       </c>
       <c r="C30" s="5">
-        <v>46139.5432959375</v>
+        <v>46139.37662927083</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.548176979166</v>
+        <v>46139.3815103125</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3343,11 +3343,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.699946747685</v>
+        <v>46073.533280081014</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46191.83935533564</v>
+        <v>46191.67268866899</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3390,13 +3390,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.69994704861</v>
+        <v>46073.53328038195</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.839348587964</v>
+        <v>46191.67268192129</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.83935060185</v>
+        <v>46191.67268393519</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3455,13 +3455,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.69994738426</v>
+        <v>46073.53328071759</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.68363072917</v>
+        <v>46182.516964062495</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.68413366898</v>
+        <v>46182.51746700231</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3516,13 +3516,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.69994769676</v>
+        <v>46073.53328103009</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.83755203703</v>
+        <v>46191.670885370375</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.83755358796</v>
+        <v>46191.670886921296</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3577,11 +3577,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.69994803241</v>
+        <v>46073.533281365744</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.65273861111</v>
+        <v>46174.48607194444</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3640,13 +3640,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.699948333335</v>
+        <v>46073.53328166666</v>
       </c>
       <c r="C36" s="5">
-        <v>46174.65273003472</v>
+        <v>46174.48606336805</v>
       </c>
       <c r="D36" s="5">
-        <v>46174.652731724535</v>
+        <v>46174.48606505787</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3701,11 +3701,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.699948622685</v>
+        <v>46073.53328195601</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46174.65273809028</v>
+        <v>46174.48607142361</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3760,13 +3760,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.69994892361</v>
+        <v>46073.53328225695</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.836712743054</v>
+        <v>46191.67004607639</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.83671528935</v>
+        <v>46191.670048622684</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3825,13 +3825,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.699949201386</v>
+        <v>46073.53328253472</v>
       </c>
       <c r="C39" s="8">
-        <v>46174.64929829861</v>
+        <v>46174.482631631945</v>
       </c>
       <c r="D39" s="8">
-        <v>46174.64929997685</v>
+        <v>46174.48263331018</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3886,13 +3886,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.69994585648</v>
+        <v>46073.53327918981</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.67566594908</v>
+        <v>46182.50899928241</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.67566810185</v>
+        <v>46182.50900143519</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3947,13 +3947,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.69994628472</v>
+        <v>46073.53327961806</v>
       </c>
       <c r="C41" s="8">
-        <v>46127.78343253472</v>
+        <v>46127.61676586806</v>
       </c>
       <c r="D41" s="8">
-        <v>46127.78344613426</v>
+        <v>46127.61677946759</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4012,13 +4012,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.69994653935</v>
+        <v>46073.53327987269</v>
       </c>
       <c r="C42" s="5">
-        <v>46120.692551064814</v>
+        <v>46120.52588439814</v>
       </c>
       <c r="D42" s="5">
-        <v>46120.69255305556</v>
+        <v>46120.52588638889</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4073,13 +4073,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.69994680556</v>
+        <v>46073.53328013889</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.783406041664</v>
+        <v>46127.616739375</v>
       </c>
       <c r="D43" s="8">
-        <v>46127.783407256946</v>
+        <v>46127.61674059028</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4134,13 +4134,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.69994707176</v>
+        <v>46073.53328040509</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.78341672454</v>
+        <v>46127.616750057874</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.78341805555</v>
+        <v>46127.616751388894</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4195,13 +4195,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.69994733796</v>
+        <v>46073.5332806713</v>
       </c>
       <c r="C45" s="8">
-        <v>46112.49058179398</v>
+        <v>46112.323915127316</v>
       </c>
       <c r="D45" s="8">
-        <v>46139.54791172454</v>
+        <v>46139.38124505787</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4260,13 +4260,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.69994759259</v>
+        <v>46073.53328092593</v>
       </c>
       <c r="C46" s="5">
-        <v>46104.82754436343</v>
+        <v>46104.66087769676</v>
       </c>
       <c r="D46" s="5">
-        <v>46104.82754626157</v>
+        <v>46104.66087959491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4321,13 +4321,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.699947870366</v>
+        <v>46073.53328120371</v>
       </c>
       <c r="C47" s="8">
-        <v>46132.57863260417</v>
+        <v>46132.4119659375</v>
       </c>
       <c r="D47" s="8">
-        <v>46132.57863447917</v>
+        <v>46132.4119678125</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4382,13 +4382,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46076.881105196764</v>
+        <v>46076.71443853009</v>
       </c>
       <c r="C48" s="5">
-        <v>46112.48812652778</v>
+        <v>46112.32145986111</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.54788491898</v>
+        <v>46139.38121825231</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4447,13 +4447,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46076.88918239583</v>
+        <v>46076.72251572917</v>
       </c>
       <c r="C49" s="8">
-        <v>46112.49184642361</v>
+        <v>46112.32517975694</v>
       </c>
       <c r="D49" s="8">
-        <v>46112.491848171296</v>
+        <v>46112.325181504624</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4502,13 +4502,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46076.88930991898</v>
+        <v>46076.72264325232</v>
       </c>
       <c r="C50" s="5">
-        <v>46112.50604163195</v>
+        <v>46112.339374965275</v>
       </c>
       <c r="D50" s="5">
-        <v>46112.50608989583</v>
+        <v>46112.33942322917</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4557,13 +4557,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.579487986106</v>
+        <v>46077.41282131945</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.83738681713</v>
+        <v>46191.67072015046</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.83738863426</v>
+        <v>46191.67072196759</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4622,13 +4622,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.5872287963</v>
+        <v>46077.42056212963</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.68337204861</v>
+        <v>46182.516705381946</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.68337341435</v>
+        <v>46182.51670674769</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4677,13 +4677,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.58741234954</v>
+        <v>46077.42074568287</v>
       </c>
       <c r="C53" s="8">
-        <v>46182.69210525463</v>
+        <v>46182.52543858797</v>
       </c>
       <c r="D53" s="8">
-        <v>46182.69210671296</v>
+        <v>46182.525440046295</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -4732,13 +4732,13 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.57954119213</v>
+        <v>46077.412874525464</v>
       </c>
       <c r="C54" s="5">
-        <v>46174.65185637731</v>
+        <v>46174.48518971065</v>
       </c>
       <c r="D54" s="5">
-        <v>46174.6518578588</v>
+        <v>46174.48519119213</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4797,13 +4797,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.587555833336</v>
+        <v>46077.420889166664</v>
       </c>
       <c r="C55" s="8">
-        <v>46094.7587408449</v>
+        <v>46094.59207417824</v>
       </c>
       <c r="D55" s="8">
-        <v>46169.8399244676</v>
+        <v>46169.673257800925</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>110</v>
@@ -4852,13 +4852,13 @@
         <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.5876627199</v>
+        <v>46077.42099605324</v>
       </c>
       <c r="C56" s="5">
-        <v>46174.65173</v>
+        <v>46174.48506333333</v>
       </c>
       <c r="D56" s="5">
-        <v>46174.651731377315</v>
+        <v>46174.48506471065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -4907,13 +4907,13 @@
         <v>197</v>
       </c>
       <c r="B57" s="8">
-        <v>46139.543413900465</v>
+        <v>46139.37674723379</v>
       </c>
       <c r="C57" s="8">
-        <v>46191.840089791665</v>
+        <v>46191.673423125</v>
       </c>
       <c r="D57" s="8">
-        <v>46191.84009155093</v>
+        <v>46191.673424884255</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4972,13 +4972,13 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46139.543700821756</v>
+        <v>46139.37703415509</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.839869421296</v>
+        <v>46191.67320275463</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.83987099537</v>
+        <v>46191.673204328705</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -5027,13 +5027,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46139.54378479166</v>
+        <v>46139.377118125005</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.83995417824</v>
+        <v>46191.67328751157</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.83995613426</v>
+        <v>46191.673289467595</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5082,11 +5082,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.69994815972</v>
+        <v>46073.53328149306</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46129.586425601854</v>
+        <v>46129.41975893518</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5129,13 +5129,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.6999484375</v>
+        <v>46073.53328177083</v>
       </c>
       <c r="C61" s="8">
-        <v>46099.54242106482</v>
+        <v>46099.37575439815</v>
       </c>
       <c r="D61" s="8">
-        <v>46099.54242268519</v>
+        <v>46099.37575601852</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5194,13 +5194,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.699946249995</v>
+        <v>46073.53327958334</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.586253912035</v>
+        <v>46129.41958724537</v>
       </c>
       <c r="D62" s="5">
-        <v>46129.58626813657</v>
+        <v>46129.41960146991</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5259,13 +5259,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46092.494241736116</v>
+        <v>46092.327575069445</v>
       </c>
       <c r="C63" s="8">
-        <v>46129.58641790509</v>
+        <v>46129.41975123843</v>
       </c>
       <c r="D63" s="8">
-        <v>46139.54817715278</v>
+        <v>46139.38151048611</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>115</v>
@@ -5322,11 +5322,11 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.49428590278</v>
+        <v>46092.32761923611</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46154.16811805556</v>
+        <v>46154.00145138889</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5385,11 +5385,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.69994662037</v>
+        <v>46073.5332799537</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46198.821161875</v>
+        <v>46198.654495208335</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5432,11 +5432,11 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.69994689815</v>
+        <v>46073.53328023148</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46199.82444644676</v>
+        <v>46199.65777978009</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5495,11 +5495,11 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.69994719907</v>
+        <v>46073.53328053241</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46198.8211615162</v>
+        <v>46198.654494849536</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5558,11 +5558,11 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.69994748842</v>
+        <v>46073.533280821764</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46077.62916171296</v>
+        <v>46077.4624950463</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5605,11 +5605,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.69994777778</v>
+        <v>46073.533281111115</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46092.50399041666</v>
+        <v>46092.337323750005</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5668,11 +5668,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.699948113426</v>
+        <v>46073.533281446755</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46129.58642229167</v>
+        <v>46129.419755625</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5731,11 +5731,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.69994846065</v>
+        <v>46073.53328179398</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46129.5864233912</v>
+        <v>46129.419756724536</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5794,11 +5794,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.699948865746</v>
+        <v>46073.533282199074</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.604225717594</v>
+        <v>46195.43755905093</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5841,11 +5841,11 @@
         <v>258</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.69995097222</v>
+        <v>46073.53328430555</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46199.830143969906</v>
+        <v>46199.66347730324</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5904,11 +5904,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.69994640046</v>
+        <v>46073.5332797338</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46121.187778182866</v>
+        <v>46121.0211115162</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>56</v>
@@ -5967,11 +5967,11 @@
         <v>263</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.699946782406</v>
+        <v>46073.53328011574</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46199.82646660879</v>
+        <v>46199.65979994213</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>
@@ -6030,13 +6030,13 @@
         <v>266</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.69994708333</v>
+        <v>46073.53328041667</v>
       </c>
       <c r="C76" s="5">
-        <v>46195.603957824074</v>
+        <v>46195.4372911574</v>
       </c>
       <c r="D76" s="5">
-        <v>46195.603959687505</v>
+        <v>46195.437293020834</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6095,13 +6095,13 @@
         <v>269</v>
       </c>
       <c r="B77" s="8">
-        <v>46076.88127923611</v>
+        <v>46076.71461256944</v>
       </c>
       <c r="C77" s="8">
-        <v>46195.60421921297</v>
+        <v>46195.4375525463</v>
       </c>
       <c r="D77" s="8">
-        <v>46195.60422127315</v>
+        <v>46195.437554606484</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>270</v>
@@ -6160,13 +6160,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.57961084491</v>
+        <v>46077.41294417824</v>
       </c>
       <c r="C78" s="5">
-        <v>46195.60466336805</v>
+        <v>46195.43799670139</v>
       </c>
       <c r="D78" s="5">
-        <v>46195.60466490741</v>
+        <v>46195.43799824074</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6225,11 +6225,11 @@
         <v>275</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.57965403935</v>
+        <v>46077.412987372685</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.692112696765</v>
+        <v>46182.52544603009</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>188</v>
@@ -6288,11 +6288,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.69994733796</v>
+        <v>46073.5332806713</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46078.621237141204</v>
+        <v>46078.45457047454</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>277</v>
@@ -6335,11 +6335,11 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.69994759259</v>
+        <v>46073.53328092593</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46128.16821587963</v>
+        <v>46128.00154921296</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6398,11 +6398,11 @@
         <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.69994784722</v>
+        <v>46073.53328118056</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.59349042824</v>
+        <v>46198.426823761576</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6461,11 +6461,11 @@
         <v>287</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.69994813658</v>
+        <v>46073.53328146991</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46198.592367060184</v>
+        <v>46198.42570039352</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>288</v>
@@ -6524,11 +6524,11 @@
         <v>290</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.699948368056</v>
+        <v>46073.533281701384</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46198.59272494213</v>
+        <v>46198.426058275465</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>291</v>
@@ -6587,11 +6587,11 @@
         <v>294</v>
       </c>
       <c r="B85" s="8">
-        <v>46076.88137268518</v>
+        <v>46076.71470601852</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.60422616898</v>
+        <v>46195.437559502316</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>295</v>
@@ -6650,11 +6650,11 @@
         <v>298</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.69994864584</v>
+        <v>46073.533281979166</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46153.16811694445</v>
+        <v>46153.00145027778</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>225</v>
@@ -6713,11 +6713,11 @@
         <v>301</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.699948912035</v>
+        <v>46073.53328224537</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46154.16785564815</v>
+        <v>46154.00118898148</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>302</v>
@@ -6776,11 +6776,11 @@
         <v>304</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.69994572917</v>
+        <v>46073.533279062496</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46077.638347245374</v>
+        <v>46077.4716805787</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>305</v>
@@ -6823,11 +6823,11 @@
         <v>307</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.699946099536</v>
+        <v>46073.53327943287</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.16794435185</v>
+        <v>46155.00127768518</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>308</v>
@@ -6886,11 +6886,11 @@
         <v>310</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.69994638889</v>
+        <v>46073.53327972222</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.604670092594</v>
+        <v>46195.43800342592</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>274</v>
@@ -6949,11 +6949,11 @@
         <v>313</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.69994668981</v>
+        <v>46073.53328002315</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46161.25032122685</v>
+        <v>46161.083654560185</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>314</v>
@@ -7012,11 +7012,11 @@
         <v>316</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.69994695602</v>
+        <v>46073.53328028935</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.25040996527</v>
+        <v>46162.083743298615</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>317</v>
@@ -7075,11 +7075,11 @@
         <v>319</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.699947245375</v>
+        <v>46073.533280578704</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46077.6387968287</v>
+        <v>46077.47213016204</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>320</v>
@@ -7122,11 +7122,11 @@
         <v>322</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.699947500005</v>
+        <v>46073.53328083333</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.16833755787</v>
+        <v>46174.0016708912</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>323</v>
@@ -7185,11 +7185,11 @@
         <v>326</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.699947789355</v>
+        <v>46073.53328112268</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46174.168340185184</v>
+        <v>46174.00167351852</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>327</v>
@@ -7248,11 +7248,11 @@
         <v>329</v>
       </c>
       <c r="B96" s="5">
-        <v>46092.48971385417</v>
+        <v>46092.3230471875</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46092.497058946756</v>
+        <v>46092.33039228009</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>330</v>
@@ -7301,11 +7301,11 @@
         <v>332</v>
       </c>
       <c r="B97" s="8">
-        <v>46092.49161491898</v>
+        <v>46092.32494825231</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46171.168742951384</v>
+        <v>46171.00207628473</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>333</v>
@@ -7364,11 +7364,11 @@
         <v>335</v>
       </c>
       <c r="B98" s="5">
-        <v>46092.491661747685</v>
+        <v>46092.32499508101</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46181.16820616898</v>
+        <v>46181.001539502315</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>336</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.53327969907</v>
+        <v>46073.69994636574</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55202717593</v>
+        <v>46092.71869384259</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.61572028935</v>
+        <v>46118.78238695602</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1697,13 +1697,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.53328005787</v>
+        <v>46073.69994672453</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55211712963</v>
+        <v>46092.7187837963</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55213513889</v>
+        <v>46092.71880180556</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1762,13 +1762,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.53328034723</v>
+        <v>46073.69994701388</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55214392361</v>
+        <v>46092.718810590275</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55215846065</v>
+        <v>46092.71882512732</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1827,13 +1827,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.53328063658</v>
+        <v>46073.69994730324</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.552157488426</v>
+        <v>46092.71882415509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.552175069446</v>
+        <v>46092.71884173611</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1892,13 +1892,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.53328091435</v>
+        <v>46073.699947581015</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55216664352</v>
+        <v>46092.71883331018</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.58784101852</v>
+        <v>46093.75450768518</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1957,13 +1957,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55218392361</v>
+        <v>46092.718850590274</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.552198634265</v>
+        <v>46092.71886530092</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2022,11 +2022,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.53328145834</v>
+        <v>46073.699948124995</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.72635736111</v>
+        <v>46127.89302402778</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2069,13 +2069,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.53328171297</v>
+        <v>46073.699948379624</v>
       </c>
       <c r="C11" s="8">
-        <v>46093.69488967593</v>
+        <v>46093.86155634259</v>
       </c>
       <c r="D11" s="8">
-        <v>46093.694909328704</v>
+        <v>46093.86157599537</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2134,11 +2134,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46134.52718547454</v>
+        <v>46134.69385214121</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2197,13 +2197,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C13" s="8">
-        <v>46093.58815574074</v>
+        <v>46093.75482240741</v>
       </c>
       <c r="D13" s="8">
-        <v>46093.58816989583</v>
+        <v>46093.7548365625</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2250,13 +2250,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.533279560186</v>
+        <v>46073.69994622685</v>
       </c>
       <c r="C14" s="5">
-        <v>46093.58800283565</v>
+        <v>46093.75466950232</v>
       </c>
       <c r="D14" s="5">
-        <v>46093.58802418981</v>
+        <v>46093.754690856484</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2315,13 +2315,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.53327989583</v>
+        <v>46073.6999465625</v>
       </c>
       <c r="C15" s="8">
-        <v>46093.58801493056</v>
+        <v>46093.754681597224</v>
       </c>
       <c r="D15" s="8">
-        <v>46093.588031527775</v>
+        <v>46093.75469819445</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2380,13 +2380,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.533280185184</v>
+        <v>46073.69994685185</v>
       </c>
       <c r="C16" s="5">
-        <v>46093.58802552083</v>
+        <v>46093.754692187504</v>
       </c>
       <c r="D16" s="5">
-        <v>46093.58804537037</v>
+        <v>46093.75471203704</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2445,13 +2445,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.53328045139</v>
+        <v>46073.69994711806</v>
       </c>
       <c r="C17" s="8">
-        <v>46093.58803587963</v>
+        <v>46093.7547025463</v>
       </c>
       <c r="D17" s="8">
-        <v>46093.58805561342</v>
+        <v>46093.75472228009</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2510,13 +2510,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.41097503473</v>
+        <v>46077.577641701384</v>
       </c>
       <c r="C18" s="5">
-        <v>46093.58804545139</v>
+        <v>46093.754712118054</v>
       </c>
       <c r="D18" s="5">
-        <v>46093.588064895834</v>
+        <v>46093.7547315625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2575,13 +2575,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.41106642361</v>
+        <v>46077.57773309028</v>
       </c>
       <c r="C19" s="8">
-        <v>46093.58805770833</v>
+        <v>46093.754724375</v>
       </c>
       <c r="D19" s="8">
-        <v>46093.588074803236</v>
+        <v>46093.75474146991</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2640,13 +2640,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.53328070602</v>
+        <v>46073.69994737269</v>
       </c>
       <c r="C20" s="5">
-        <v>46093.588138356485</v>
+        <v>46093.75480502315</v>
       </c>
       <c r="D20" s="5">
-        <v>46093.588156875005</v>
+        <v>46093.75482354166</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2705,13 +2705,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.533280972224</v>
+        <v>46073.69994763889</v>
       </c>
       <c r="C21" s="8">
-        <v>46093.70787949074</v>
+        <v>46093.87454615741</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.37611355324</v>
+        <v>46139.54278021991</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2758,13 +2758,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.53328150463</v>
+        <v>46073.6999481713</v>
       </c>
       <c r="C22" s="5">
-        <v>46093.58810327546</v>
+        <v>46093.75476994213</v>
       </c>
       <c r="D22" s="5">
-        <v>46093.58811964121</v>
+        <v>46093.754786307865</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2823,13 +2823,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.53328122685</v>
+        <v>46073.69994789352</v>
       </c>
       <c r="C23" s="8">
-        <v>46093.588114375</v>
+        <v>46093.754781041665</v>
       </c>
       <c r="D23" s="8">
-        <v>46093.5881318287</v>
+        <v>46093.75479849537</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2888,13 +2888,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.533281875</v>
+        <v>46073.69994854167</v>
       </c>
       <c r="C24" s="5">
-        <v>46093.707863171294</v>
+        <v>46093.874529837965</v>
       </c>
       <c r="D24" s="5">
-        <v>46093.707880625</v>
+        <v>46093.87454729166</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2953,13 +2953,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.53328215278</v>
+        <v>46073.69994881944</v>
       </c>
       <c r="C25" s="8">
-        <v>46093.588160694446</v>
+        <v>46093.75482736111</v>
       </c>
       <c r="D25" s="8">
-        <v>46093.5881780787</v>
+        <v>46093.754844745374</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -3018,13 +3018,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.53327965278</v>
+        <v>46073.699946319444</v>
       </c>
       <c r="C26" s="5">
-        <v>46093.588169571754</v>
+        <v>46093.754836238426</v>
       </c>
       <c r="D26" s="5">
-        <v>46093.58818924769</v>
+        <v>46093.75485591435</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3083,13 +3083,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46076.71435710648</v>
+        <v>46076.88102377315</v>
       </c>
       <c r="C27" s="8">
-        <v>46093.58817870371</v>
+        <v>46093.75484537037</v>
       </c>
       <c r="D27" s="8">
-        <v>46093.58820009259</v>
+        <v>46093.754866759264</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3148,13 +3148,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.41262609954</v>
+        <v>46077.579292766204</v>
       </c>
       <c r="C28" s="5">
-        <v>46093.5881874537</v>
+        <v>46093.75485412037</v>
       </c>
       <c r="D28" s="5">
-        <v>46093.5882078588</v>
+        <v>46093.75487452546</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>78</v>
@@ -3213,13 +3213,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.4126985301</v>
+        <v>46077.579365196754</v>
       </c>
       <c r="C29" s="8">
-        <v>46093.58819627315</v>
+        <v>46093.754862939815</v>
       </c>
       <c r="D29" s="8">
-        <v>46093.58821469908</v>
+        <v>46093.75488136574</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>81</v>
@@ -3278,13 +3278,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="5">
-        <v>46139.37604528935</v>
+        <v>46139.54271195602</v>
       </c>
       <c r="C30" s="5">
-        <v>46139.37662927083</v>
+        <v>46139.5432959375</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.3815103125</v>
+        <v>46139.548176979166</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3343,11 +3343,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.533280081014</v>
+        <v>46073.699946747685</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46191.67268866899</v>
+        <v>46191.83935533564</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3390,13 +3390,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.53328038195</v>
+        <v>46073.69994704861</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.67268192129</v>
+        <v>46191.839348587964</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.67268393519</v>
+        <v>46191.83935060185</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3455,13 +3455,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.53328071759</v>
+        <v>46073.69994738426</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.516964062495</v>
+        <v>46182.68363072917</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.51746700231</v>
+        <v>46182.68413366898</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3516,13 +3516,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.53328103009</v>
+        <v>46073.69994769676</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.670885370375</v>
+        <v>46191.83755203703</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.670886921296</v>
+        <v>46191.83755358796</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3577,11 +3577,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.533281365744</v>
+        <v>46073.69994803241</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.48607194444</v>
+        <v>46174.65273861111</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3640,13 +3640,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.53328166666</v>
+        <v>46073.699948333335</v>
       </c>
       <c r="C36" s="5">
-        <v>46174.48606336805</v>
+        <v>46174.65273003472</v>
       </c>
       <c r="D36" s="5">
-        <v>46174.48606505787</v>
+        <v>46174.652731724535</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3701,11 +3701,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.53328195601</v>
+        <v>46073.699948622685</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46174.48607142361</v>
+        <v>46174.65273809028</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3760,13 +3760,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.67004607639</v>
+        <v>46191.836712743054</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.670048622684</v>
+        <v>46191.83671528935</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3825,13 +3825,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.53328253472</v>
+        <v>46073.699949201386</v>
       </c>
       <c r="C39" s="8">
-        <v>46174.482631631945</v>
+        <v>46174.64929829861</v>
       </c>
       <c r="D39" s="8">
-        <v>46174.48263331018</v>
+        <v>46174.64929997685</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3886,13 +3886,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.53327918981</v>
+        <v>46073.69994585648</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.50899928241</v>
+        <v>46182.67566594908</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.50900143519</v>
+        <v>46182.67566810185</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3947,13 +3947,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.53327961806</v>
+        <v>46073.69994628472</v>
       </c>
       <c r="C41" s="8">
-        <v>46127.61676586806</v>
+        <v>46127.78343253472</v>
       </c>
       <c r="D41" s="8">
-        <v>46127.61677946759</v>
+        <v>46127.78344613426</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4012,13 +4012,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.53327987269</v>
+        <v>46073.69994653935</v>
       </c>
       <c r="C42" s="5">
-        <v>46120.52588439814</v>
+        <v>46120.692551064814</v>
       </c>
       <c r="D42" s="5">
-        <v>46120.52588638889</v>
+        <v>46120.69255305556</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4073,13 +4073,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.53328013889</v>
+        <v>46073.69994680556</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.616739375</v>
+        <v>46127.783406041664</v>
       </c>
       <c r="D43" s="8">
-        <v>46127.61674059028</v>
+        <v>46127.783407256946</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4134,13 +4134,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.53328040509</v>
+        <v>46073.69994707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.616750057874</v>
+        <v>46127.78341672454</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.616751388894</v>
+        <v>46127.78341805555</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4195,13 +4195,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C45" s="8">
-        <v>46112.323915127316</v>
+        <v>46112.49058179398</v>
       </c>
       <c r="D45" s="8">
-        <v>46139.38124505787</v>
+        <v>46139.54791172454</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4260,13 +4260,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C46" s="5">
-        <v>46104.66087769676</v>
+        <v>46104.82754436343</v>
       </c>
       <c r="D46" s="5">
-        <v>46104.66087959491</v>
+        <v>46104.82754626157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4321,13 +4321,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.53328120371</v>
+        <v>46073.699947870366</v>
       </c>
       <c r="C47" s="8">
-        <v>46132.4119659375</v>
+        <v>46132.57863260417</v>
       </c>
       <c r="D47" s="8">
-        <v>46132.4119678125</v>
+        <v>46132.57863447917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4382,13 +4382,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46076.71443853009</v>
+        <v>46076.881105196764</v>
       </c>
       <c r="C48" s="5">
-        <v>46112.32145986111</v>
+        <v>46112.48812652778</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.38121825231</v>
+        <v>46139.54788491898</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4447,13 +4447,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46076.72251572917</v>
+        <v>46076.88918239583</v>
       </c>
       <c r="C49" s="8">
-        <v>46112.32517975694</v>
+        <v>46112.49184642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46112.325181504624</v>
+        <v>46112.491848171296</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4502,13 +4502,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46076.72264325232</v>
+        <v>46076.88930991898</v>
       </c>
       <c r="C50" s="5">
-        <v>46112.339374965275</v>
+        <v>46112.50604163195</v>
       </c>
       <c r="D50" s="5">
-        <v>46112.33942322917</v>
+        <v>46112.50608989583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4557,13 +4557,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.41282131945</v>
+        <v>46077.579487986106</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.67072015046</v>
+        <v>46191.83738681713</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.67072196759</v>
+        <v>46191.83738863426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4622,13 +4622,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.42056212963</v>
+        <v>46077.5872287963</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.516705381946</v>
+        <v>46182.68337204861</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.51670674769</v>
+        <v>46182.68337341435</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4677,13 +4677,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.42074568287</v>
+        <v>46077.58741234954</v>
       </c>
       <c r="C53" s="8">
-        <v>46182.52543858797</v>
+        <v>46182.69210525463</v>
       </c>
       <c r="D53" s="8">
-        <v>46182.525440046295</v>
+        <v>46182.69210671296</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -4732,13 +4732,13 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.412874525464</v>
+        <v>46077.57954119213</v>
       </c>
       <c r="C54" s="5">
-        <v>46174.48518971065</v>
+        <v>46174.65185637731</v>
       </c>
       <c r="D54" s="5">
-        <v>46174.48519119213</v>
+        <v>46174.6518578588</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4797,13 +4797,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.420889166664</v>
+        <v>46077.587555833336</v>
       </c>
       <c r="C55" s="8">
-        <v>46094.59207417824</v>
+        <v>46094.7587408449</v>
       </c>
       <c r="D55" s="8">
-        <v>46169.673257800925</v>
+        <v>46169.8399244676</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>110</v>
@@ -4852,13 +4852,13 @@
         <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.42099605324</v>
+        <v>46077.5876627199</v>
       </c>
       <c r="C56" s="5">
-        <v>46174.48506333333</v>
+        <v>46174.65173</v>
       </c>
       <c r="D56" s="5">
-        <v>46174.48506471065</v>
+        <v>46174.651731377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -4907,13 +4907,13 @@
         <v>197</v>
       </c>
       <c r="B57" s="8">
-        <v>46139.37674723379</v>
+        <v>46139.543413900465</v>
       </c>
       <c r="C57" s="8">
-        <v>46191.673423125</v>
+        <v>46191.840089791665</v>
       </c>
       <c r="D57" s="8">
-        <v>46191.673424884255</v>
+        <v>46191.84009155093</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4972,13 +4972,13 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46139.37703415509</v>
+        <v>46139.543700821756</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.67320275463</v>
+        <v>46191.839869421296</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.673204328705</v>
+        <v>46191.83987099537</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -5027,13 +5027,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46139.377118125005</v>
+        <v>46139.54378479166</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.67328751157</v>
+        <v>46191.83995417824</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.673289467595</v>
+        <v>46191.83995613426</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5082,11 +5082,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.53328149306</v>
+        <v>46073.69994815972</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46129.41975893518</v>
+        <v>46129.586425601854</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5129,13 +5129,13 @@
         <v>209</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.53328177083</v>
+        <v>46073.6999484375</v>
       </c>
       <c r="C61" s="8">
-        <v>46099.37575439815</v>
+        <v>46099.54242106482</v>
       </c>
       <c r="D61" s="8">
-        <v>46099.37575601852</v>
+        <v>46099.54242268519</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>210</v>
@@ -5194,13 +5194,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.53327958334</v>
+        <v>46073.699946249995</v>
       </c>
       <c r="C62" s="5">
-        <v>46129.41958724537</v>
+        <v>46129.586253912035</v>
       </c>
       <c r="D62" s="5">
-        <v>46129.41960146991</v>
+        <v>46129.58626813657</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5259,13 +5259,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46092.327575069445</v>
+        <v>46092.494241736116</v>
       </c>
       <c r="C63" s="8">
-        <v>46129.41975123843</v>
+        <v>46129.58641790509</v>
       </c>
       <c r="D63" s="8">
-        <v>46139.38151048611</v>
+        <v>46139.54817715278</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>115</v>
@@ -5322,11 +5322,11 @@
         <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.32761923611</v>
+        <v>46092.49428590278</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46154.00145138889</v>
+        <v>46154.16811805556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>222</v>
@@ -5385,11 +5385,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.5332799537</v>
+        <v>46073.69994662037</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46198.654495208335</v>
+        <v>46198.821161875</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>
@@ -5432,11 +5432,11 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.53328023148</v>
+        <v>46073.69994689815</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46199.65777978009</v>
+        <v>46199.82444644676</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>231</v>
@@ -5495,11 +5495,11 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.53328053241</v>
+        <v>46073.69994719907</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46198.654494849536</v>
+        <v>46198.8211615162</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5558,11 +5558,11 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.533280821764</v>
+        <v>46073.69994748842</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46077.4624950463</v>
+        <v>46077.62916171296</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5605,11 +5605,11 @@
         <v>243</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.533281111115</v>
+        <v>46073.69994777778</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46092.337323750005</v>
+        <v>46092.50399041666</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>244</v>
@@ -5668,11 +5668,11 @@
         <v>248</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.533281446755</v>
+        <v>46073.699948113426</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46129.419755625</v>
+        <v>46129.58642229167</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>249</v>
@@ -5731,11 +5731,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.53328179398</v>
+        <v>46073.69994846065</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46129.419756724536</v>
+        <v>46129.5864233912</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5794,11 +5794,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.533282199074</v>
+        <v>46073.699948865746</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.43755905093</v>
+        <v>46195.604225717594</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>228</v>
@@ -5841,11 +5841,11 @@
         <v>258</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.53328430555</v>
+        <v>46073.69995097222</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46199.66347730324</v>
+        <v>46199.830143969906</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5904,11 +5904,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.5332797338</v>
+        <v>46073.69994640046</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46121.0211115162</v>
+        <v>46121.187778182866</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>56</v>
@@ -5967,11 +5967,11 @@
         <v>263</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.53328011574</v>
+        <v>46073.699946782406</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46199.65979994213</v>
+        <v>46199.82646660879</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>264</v>
@@ -6030,13 +6030,13 @@
         <v>266</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.53328041667</v>
+        <v>46073.69994708333</v>
       </c>
       <c r="C76" s="5">
-        <v>46195.4372911574</v>
+        <v>46195.603957824074</v>
       </c>
       <c r="D76" s="5">
-        <v>46195.437293020834</v>
+        <v>46195.603959687505</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>267</v>
@@ -6095,13 +6095,13 @@
         <v>269</v>
       </c>
       <c r="B77" s="8">
-        <v>46076.71461256944</v>
+        <v>46076.88127923611</v>
       </c>
       <c r="C77" s="8">
-        <v>46195.4375525463</v>
+        <v>46195.60421921297</v>
       </c>
       <c r="D77" s="8">
-        <v>46195.437554606484</v>
+        <v>46195.60422127315</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>270</v>
@@ -6160,13 +6160,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46077.41294417824</v>
+        <v>46077.57961084491</v>
       </c>
       <c r="C78" s="5">
-        <v>46195.43799670139</v>
+        <v>46195.60466336805</v>
       </c>
       <c r="D78" s="5">
-        <v>46195.43799824074</v>
+        <v>46195.60466490741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6225,11 +6225,11 @@
         <v>275</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.412987372685</v>
+        <v>46077.57965403935</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.52544603009</v>
+        <v>46182.692112696765</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>188</v>
@@ -6288,11 +6288,11 @@
         <v>276</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46078.45457047454</v>
+        <v>46078.621237141204</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>277</v>
@@ -6335,11 +6335,11 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46128.00154921296</v>
+        <v>46128.16821587963</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6398,11 +6398,11 @@
         <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.426823761576</v>
+        <v>46198.59349042824</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6461,11 +6461,11 @@
         <v>287</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.53328146991</v>
+        <v>46073.69994813658</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46198.42570039352</v>
+        <v>46198.592367060184</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>288</v>
@@ -6524,11 +6524,11 @@
         <v>290</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.533281701384</v>
+        <v>46073.699948368056</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46198.426058275465</v>
+        <v>46198.59272494213</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>291</v>
@@ -6587,11 +6587,11 @@
         <v>294</v>
       </c>
       <c r="B85" s="8">
-        <v>46076.71470601852</v>
+        <v>46076.88137268518</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.437559502316</v>
+        <v>46195.60422616898</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>295</v>
@@ -6650,11 +6650,11 @@
         <v>298</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46153.00145027778</v>
+        <v>46153.16811694445</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>225</v>
@@ -6713,11 +6713,11 @@
         <v>301</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.53328224537</v>
+        <v>46073.699948912035</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46154.00118898148</v>
+        <v>46154.16785564815</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>302</v>
@@ -6776,11 +6776,11 @@
         <v>304</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.533279062496</v>
+        <v>46073.69994572917</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46077.4716805787</v>
+        <v>46077.638347245374</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>305</v>
@@ -6823,11 +6823,11 @@
         <v>307</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.53327943287</v>
+        <v>46073.699946099536</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.00127768518</v>
+        <v>46155.16794435185</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>308</v>
@@ -6886,11 +6886,11 @@
         <v>310</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.53327972222</v>
+        <v>46073.69994638889</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.43800342592</v>
+        <v>46195.604670092594</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>274</v>
@@ -6949,11 +6949,11 @@
         <v>313</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.53328002315</v>
+        <v>46073.69994668981</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46161.083654560185</v>
+        <v>46161.25032122685</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>314</v>
@@ -7012,11 +7012,11 @@
         <v>316</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.53328028935</v>
+        <v>46073.69994695602</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.083743298615</v>
+        <v>46162.25040996527</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>317</v>
@@ -7075,11 +7075,11 @@
         <v>319</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.533280578704</v>
+        <v>46073.699947245375</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46077.47213016204</v>
+        <v>46077.6387968287</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>320</v>
@@ -7122,11 +7122,11 @@
         <v>322</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.53328083333</v>
+        <v>46073.699947500005</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.0016708912</v>
+        <v>46174.16833755787</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>323</v>
@@ -7185,11 +7185,11 @@
         <v>326</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.53328112268</v>
+        <v>46073.699947789355</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46174.00167351852</v>
+        <v>46174.168340185184</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>327</v>
@@ -7248,11 +7248,11 @@
         <v>329</v>
       </c>
       <c r="B96" s="5">
-        <v>46092.3230471875</v>
+        <v>46092.48971385417</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46092.33039228009</v>
+        <v>46092.497058946756</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>330</v>
@@ -7301,11 +7301,11 @@
         <v>332</v>
       </c>
       <c r="B97" s="8">
-        <v>46092.32494825231</v>
+        <v>46092.49161491898</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46171.00207628473</v>
+        <v>46171.168742951384</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>333</v>
@@ -7364,11 +7364,11 @@
         <v>335</v>
       </c>
       <c r="B98" s="5">
-        <v>46092.32499508101</v>
+        <v>46092.491661747685</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46181.001539502315</v>
+        <v>46181.16820616898</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>336</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="339">
   <si>
     <t xml:space="preserve">50001490-ZITRON PERU METRO DE LIMA PV04-PV05 </t>
   </si>
@@ -631,6 +631,18 @@
     <t xml:space="preserve">Fabricacion externa OT 4204 - 4205 </t>
   </si>
   <si>
+    <t>1216239551129098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad  fabricacion externa </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
     <t>1213380177588299</t>
   </si>
   <si>
@@ -722,12 +734,6 @@
   </si>
   <si>
     <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
   </si>
   <si>
     <t>Bodega:,Preparación Materiales</t>
@@ -1545,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U98"/>
+  <dimension ref="A1:U99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -4913,7 +4919,7 @@
         <v>46191.840089791665</v>
       </c>
       <c r="D57" s="8">
-        <v>46191.84009155093</v>
+        <v>46205.80892784722</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -5082,24 +5088,28 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.69994815972</v>
+        <v>46205.80892462963</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46129.586425601854</v>
+        <v>46205.80976949074</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="6"/>
+        <v>208</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>209</v>
+      </c>
       <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
+      <c r="J60" s="5">
+        <v>46205</v>
+      </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
       </c>
@@ -5107,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>26</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>208</v>
+        <v>26</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5126,84 +5136,66 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.6999484375</v>
-      </c>
-      <c r="C61" s="8">
-        <v>46099.54242106482</v>
-      </c>
+        <v>46073.69994815972</v>
+      </c>
+      <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46099.54242268519</v>
+        <v>46129.586425601854</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="H61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="I61" s="8">
-        <v>46003</v>
-      </c>
-      <c r="J61" s="8">
-        <v>46009</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="P61" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q61" s="8">
-        <v>46003</v>
-      </c>
-      <c r="R61" s="8">
-        <v>46010</v>
-      </c>
-      <c r="S61" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T61" s="9">
-        <v>1</v>
-      </c>
-      <c r="U61" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q61" s="9"/>
+      <c r="R61" s="9"/>
+      <c r="S61" s="9"/>
+      <c r="T61" s="9"/>
+      <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" s="5">
+        <v>46073.6999484375</v>
+      </c>
+      <c r="C62" s="5">
+        <v>46099.54242106482</v>
+      </c>
+      <c r="D62" s="5">
+        <v>46099.54242268519</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="B62" s="5">
-        <v>46073.699946249995</v>
-      </c>
-      <c r="C62" s="5">
-        <v>46129.586253912035</v>
-      </c>
-      <c r="D62" s="5">
-        <v>46129.58626813657</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5215,10 +5207,10 @@
         <v>216</v>
       </c>
       <c r="I62" s="5">
-        <v>46058</v>
+        <v>46003</v>
       </c>
       <c r="J62" s="5">
-        <v>46064</v>
+        <v>46009</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
@@ -5230,19 +5222,19 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="P62" s="6" t="s">
-        <v>218</v>
-      </c>
       <c r="Q62" s="5">
-        <v>46058</v>
+        <v>46003</v>
       </c>
       <c r="R62" s="5">
-        <v>46064</v>
+        <v>46010</v>
       </c>
       <c r="S62" s="10" t="s">
         <v>31</v>
@@ -5256,32 +5248,34 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B63" s="8">
+        <v>46073.699946249995</v>
+      </c>
+      <c r="C63" s="8">
+        <v>46129.586253912035</v>
+      </c>
+      <c r="D63" s="8">
+        <v>46129.58626813657</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B63" s="8">
-        <v>46092.494241736116</v>
-      </c>
-      <c r="C63" s="8">
-        <v>46129.58641790509</v>
-      </c>
-      <c r="D63" s="8">
-        <v>46139.54817715278</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>215</v>
-      </c>
       <c r="H63" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="I63" s="9"/>
+        <v>220</v>
+      </c>
+      <c r="I63" s="8">
+        <v>46058</v>
+      </c>
       <c r="J63" s="8">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="K63" s="9" t="s">
         <v>26</v>
@@ -5293,19 +5287,19 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q63" s="8">
-        <v>46065</v>
+        <v>46058</v>
       </c>
       <c r="R63" s="8">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="S63" s="10" t="s">
         <v>31</v>
@@ -5319,90 +5313,96 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.49428590278</v>
-      </c>
-      <c r="C64" s="6"/>
+        <v>46092.494241736116</v>
+      </c>
+      <c r="C64" s="5">
+        <v>46129.58641790509</v>
+      </c>
       <c r="D64" s="5">
-        <v>46154.16811805556</v>
+        <v>46139.54817715278</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="I64" s="6"/>
+      <c r="J64" s="5">
+        <v>46065</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="I64" s="5">
-        <v>46154</v>
-      </c>
-      <c r="J64" s="5">
-        <v>46154</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>226</v>
-      </c>
       <c r="Q64" s="5">
-        <v>46154</v>
+        <v>46065</v>
       </c>
       <c r="R64" s="5">
-        <v>46154</v>
-      </c>
-      <c r="S64" s="11" t="s">
-        <v>128</v>
+        <v>46065</v>
+      </c>
+      <c r="S64" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="10" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="U64" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.69994662037</v>
+        <v>46092.49428590278</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46198.821161875</v>
+        <v>46154.16811805556</v>
       </c>
       <c r="E65" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="9"/>
+      <c r="I65" s="8">
+        <v>46154</v>
+      </c>
+      <c r="J65" s="8">
+        <v>46154</v>
+      </c>
       <c r="K65" s="9" t="s">
         <v>26</v>
       </c>
@@ -5410,138 +5410,132 @@
         <v>26</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>26</v>
+        <v>211</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>229</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q65" s="9"/>
-      <c r="R65" s="9"/>
-      <c r="S65" s="9"/>
-      <c r="T65" s="9"/>
-      <c r="U65" s="9"/>
+        <v>230</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>46154</v>
+      </c>
+      <c r="R65" s="8">
+        <v>46154</v>
+      </c>
+      <c r="S65" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T65" s="9">
+        <v>0</v>
+      </c>
+      <c r="U65" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.69994689815</v>
+        <v>46073.69994662037</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46199.82444644676</v>
+        <v>46198.821161875</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="H66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O66" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="I66" s="5">
-        <v>46063</v>
-      </c>
-      <c r="J66" s="5">
-        <v>46064</v>
-      </c>
-      <c r="K66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>171</v>
-      </c>
       <c r="P66" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q66" s="5">
-        <v>46063</v>
-      </c>
-      <c r="R66" s="5">
-        <v>46065</v>
-      </c>
-      <c r="S66" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T66" s="6">
-        <v>0</v>
-      </c>
-      <c r="U66" s="12" t="s">
-        <v>201</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.69994719907</v>
+        <v>46073.69994689815</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46198.8211615162</v>
+        <v>46199.82444644676</v>
       </c>
       <c r="E67" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="F67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="9" t="s">
+      <c r="H67" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="H67" s="9" t="s">
+      <c r="I67" s="8">
+        <v>46063</v>
+      </c>
+      <c r="J67" s="8">
+        <v>46064</v>
+      </c>
+      <c r="K67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="O67" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="P67" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="I67" s="8">
+      <c r="Q67" s="8">
+        <v>46063</v>
+      </c>
+      <c r="R67" s="8">
         <v>46065</v>
-      </c>
-      <c r="J67" s="8">
-        <v>46066</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="O67" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q67" s="8">
-        <v>46065</v>
-      </c>
-      <c r="R67" s="8">
-        <v>46066</v>
       </c>
       <c r="S67" s="10" t="s">
         <v>31</v>
@@ -5549,172 +5543,172 @@
       <c r="T67" s="9">
         <v>0</v>
       </c>
-      <c r="U67" s="10" t="s">
-        <v>58</v>
+      <c r="U67" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.69994748842</v>
+        <v>46073.69994719907</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46077.62916171296</v>
+        <v>46198.8211615162</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I68" s="5">
+        <v>46065</v>
+      </c>
+      <c r="J68" s="5">
+        <v>46066</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M68" s="6" t="s">
+      <c r="Q68" s="5">
+        <v>46065</v>
+      </c>
+      <c r="R68" s="5">
+        <v>46066</v>
+      </c>
+      <c r="S68" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="N68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+      <c r="U68" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.69994777778</v>
+        <v>46073.69994748842</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46092.50399041666</v>
+        <v>46077.62916171296</v>
       </c>
       <c r="E69" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O69" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="I69" s="8">
-        <v>46069</v>
-      </c>
-      <c r="J69" s="8">
-        <v>46077</v>
-      </c>
-      <c r="K69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="O69" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="P69" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q69" s="8">
-        <v>46069</v>
-      </c>
-      <c r="R69" s="8">
-        <v>46077</v>
-      </c>
-      <c r="S69" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T69" s="9">
-        <v>0</v>
-      </c>
-      <c r="U69" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q69" s="9"/>
+      <c r="R69" s="9"/>
+      <c r="S69" s="9"/>
+      <c r="T69" s="9"/>
+      <c r="U69" s="9"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.699948113426</v>
+        <v>46073.69994777778</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46129.58642229167</v>
+        <v>46092.50399041666</v>
       </c>
       <c r="E70" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="I70" s="5">
+        <v>46069</v>
+      </c>
+      <c r="J70" s="5">
+        <v>46077</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="I70" s="5">
-        <v>46078</v>
-      </c>
-      <c r="J70" s="5">
-        <v>46106</v>
-      </c>
-      <c r="K70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>251</v>
-      </c>
       <c r="Q70" s="5">
-        <v>46078</v>
+        <v>46069</v>
       </c>
       <c r="R70" s="5">
-        <v>46106</v>
+        <v>46077</v>
       </c>
       <c r="S70" s="10" t="s">
         <v>31</v>
@@ -5728,56 +5722,56 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.69994846065</v>
+        <v>46073.699948113426</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46129.5864233912</v>
+        <v>46129.58642229167</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I71" s="8">
+        <v>46078</v>
+      </c>
+      <c r="J71" s="8">
+        <v>46106</v>
+      </c>
+      <c r="K71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="I71" s="8">
-        <v>46107</v>
-      </c>
-      <c r="J71" s="8">
-        <v>46108</v>
-      </c>
-      <c r="K71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>255</v>
-      </c>
       <c r="Q71" s="8">
-        <v>46107</v>
+        <v>46078</v>
       </c>
       <c r="R71" s="8">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="S71" s="10" t="s">
         <v>31</v>
@@ -5791,27 +5785,33 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.699948865746</v>
+        <v>46073.69994846065</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46195.604225717594</v>
+        <v>46129.5864233912</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
+        <v>208</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I72" s="5">
+        <v>46107</v>
+      </c>
+      <c r="J72" s="5">
+        <v>46108</v>
+      </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
       </c>
@@ -5819,138 +5819,132 @@
         <v>26</v>
       </c>
       <c r="M72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>46107</v>
+      </c>
+      <c r="R72" s="5">
+        <v>46108</v>
+      </c>
+      <c r="S72" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="N72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O72" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
+      <c r="U72" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>258</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.69995097222</v>
+        <v>46073.699948865746</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46199.830143969906</v>
+        <v>46195.604225717594</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O73" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="I73" s="8">
-        <v>46097</v>
-      </c>
-      <c r="J73" s="8">
-        <v>46098</v>
-      </c>
-      <c r="K73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>148</v>
-      </c>
       <c r="P73" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q73" s="8">
-        <v>46097</v>
-      </c>
-      <c r="R73" s="8">
-        <v>46098</v>
-      </c>
-      <c r="S73" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T73" s="9">
-        <v>0</v>
-      </c>
-      <c r="U73" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q73" s="9"/>
+      <c r="R73" s="9"/>
+      <c r="S73" s="9"/>
+      <c r="T73" s="9"/>
+      <c r="U73" s="9"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.69994640046</v>
+        <v>46073.69995097222</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46121.187778182866</v>
+        <v>46199.830143969906</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>56</v>
+        <v>261</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I74" s="5">
+        <v>46097</v>
+      </c>
+      <c r="J74" s="5">
+        <v>46098</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="H74" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="I74" s="5">
-        <v>46119</v>
-      </c>
-      <c r="J74" s="5">
-        <v>46120</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" s="6" t="s">
-        <v>228</v>
-      </c>
       <c r="O74" s="6" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>262</v>
       </c>
       <c r="Q74" s="5">
-        <v>46119</v>
+        <v>46097</v>
       </c>
       <c r="R74" s="5">
-        <v>46120</v>
+        <v>46098</v>
       </c>
       <c r="S74" s="10" t="s">
         <v>31</v>
@@ -5967,53 +5961,53 @@
         <v>263</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.699946782406</v>
+        <v>46073.69994640046</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46199.82646660879</v>
+        <v>46121.187778182866</v>
       </c>
       <c r="E75" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="I75" s="8">
+        <v>46119</v>
+      </c>
+      <c r="J75" s="8">
+        <v>46120</v>
+      </c>
+      <c r="K75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="O75" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="P75" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="F75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="I75" s="8">
-        <v>46132</v>
-      </c>
-      <c r="J75" s="8">
-        <v>46133</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>265</v>
-      </c>
       <c r="Q75" s="8">
-        <v>46132</v>
+        <v>46119</v>
       </c>
       <c r="R75" s="8">
-        <v>46133</v>
+        <v>46120</v>
       </c>
       <c r="S75" s="10" t="s">
         <v>31</v>
@@ -6027,126 +6021,124 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B76" s="5">
+        <v>46073.699946782406</v>
+      </c>
+      <c r="C76" s="6"/>
+      <c r="D76" s="5">
+        <v>46199.82646660879</v>
+      </c>
+      <c r="E76" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B76" s="5">
-        <v>46073.69994708333</v>
-      </c>
-      <c r="C76" s="5">
-        <v>46195.603957824074</v>
-      </c>
-      <c r="D76" s="5">
-        <v>46195.603959687505</v>
-      </c>
-      <c r="E76" s="6" t="s">
+      <c r="F76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I76" s="5">
+        <v>46132</v>
+      </c>
+      <c r="J76" s="5">
+        <v>46133</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="F76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="I76" s="5">
-        <v>46147</v>
-      </c>
-      <c r="J76" s="5">
-        <v>46148</v>
-      </c>
-      <c r="K76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N76" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>268</v>
-      </c>
       <c r="Q76" s="5">
-        <v>46147</v>
+        <v>46132</v>
       </c>
       <c r="R76" s="5">
-        <v>46148</v>
-      </c>
-      <c r="S76" s="11" t="s">
-        <v>128</v>
+        <v>46133</v>
+      </c>
+      <c r="S76" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
-      <c r="U76" s="12" t="s">
-        <v>201</v>
+      <c r="U76" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B77" s="8">
+        <v>46073.69994708333</v>
+      </c>
+      <c r="C77" s="8">
+        <v>46195.603957824074</v>
+      </c>
+      <c r="D77" s="8">
+        <v>46195.603959687505</v>
+      </c>
+      <c r="E77" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="B77" s="8">
-        <v>46076.88127923611</v>
-      </c>
-      <c r="C77" s="8">
-        <v>46195.60421921297</v>
-      </c>
-      <c r="D77" s="8">
-        <v>46195.60422127315</v>
-      </c>
-      <c r="E77" s="9" t="s">
+      <c r="F77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="I77" s="8">
+        <v>46147</v>
+      </c>
+      <c r="J77" s="8">
+        <v>46148</v>
+      </c>
+      <c r="K77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="O77" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="P77" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="I77" s="8">
-        <v>46121</v>
-      </c>
-      <c r="J77" s="8">
-        <v>46122</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>271</v>
-      </c>
       <c r="Q77" s="8">
-        <v>46121</v>
+        <v>46147</v>
       </c>
       <c r="R77" s="8">
-        <v>46122</v>
-      </c>
-      <c r="S77" s="10" t="s">
-        <v>31</v>
+        <v>46148</v>
+      </c>
+      <c r="S77" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="T77" s="9">
         <v>0</v>
@@ -6157,58 +6149,58 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B78" s="5">
+        <v>46076.88127923611</v>
+      </c>
+      <c r="C78" s="5">
+        <v>46195.60421921297</v>
+      </c>
+      <c r="D78" s="5">
+        <v>46195.60422127315</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B78" s="5">
-        <v>46077.57961084491</v>
-      </c>
-      <c r="C78" s="5">
-        <v>46195.60466336805</v>
-      </c>
-      <c r="D78" s="5">
-        <v>46195.60466490741</v>
-      </c>
-      <c r="E78" s="6" t="s">
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I78" s="5">
+        <v>46121</v>
+      </c>
+      <c r="J78" s="5">
+        <v>46122</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="I78" s="5">
-        <v>46104</v>
-      </c>
-      <c r="J78" s="5">
-        <v>46105</v>
-      </c>
-      <c r="K78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N78" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>274</v>
-      </c>
       <c r="Q78" s="5">
-        <v>46104</v>
+        <v>46121</v>
       </c>
       <c r="R78" s="5">
-        <v>46105</v>
+        <v>46122</v>
       </c>
       <c r="S78" s="10" t="s">
         <v>31</v>
@@ -6216,62 +6208,64 @@
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="10" t="s">
-        <v>58</v>
+      <c r="U78" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B79" s="8">
+        <v>46077.57961084491</v>
+      </c>
+      <c r="C79" s="8">
+        <v>46195.60466336805</v>
+      </c>
+      <c r="D79" s="8">
+        <v>46195.60466490741</v>
+      </c>
+      <c r="E79" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="B79" s="8">
-        <v>46077.57965403935</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8">
-        <v>46182.692112696765</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="I79" s="8">
+        <v>46104</v>
+      </c>
+      <c r="J79" s="8">
+        <v>46105</v>
+      </c>
+      <c r="K79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="H79" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="I79" s="8">
-        <v>46098</v>
-      </c>
-      <c r="J79" s="8">
-        <v>46099</v>
-      </c>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>228</v>
-      </c>
       <c r="O79" s="9" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q79" s="8">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="R79" s="8">
-        <v>46099</v>
+        <v>46105</v>
       </c>
       <c r="S79" s="10" t="s">
         <v>31</v>
@@ -6285,27 +6279,33 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.69994733796</v>
+        <v>46077.57965403935</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46078.621237141204</v>
+        <v>46182.692112696765</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>277</v>
+        <v>188</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
+        <v>236</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="I80" s="5">
+        <v>46098</v>
+      </c>
+      <c r="J80" s="5">
+        <v>46099</v>
+      </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
       </c>
@@ -6313,141 +6313,135 @@
         <v>26</v>
       </c>
       <c r="M80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>46098</v>
+      </c>
+      <c r="R80" s="5">
+        <v>46099</v>
+      </c>
+      <c r="S80" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="N80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
+      <c r="U80" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.69994759259</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46128.16821587963</v>
+        <v>46078.621237141204</v>
       </c>
       <c r="E81" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="9"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O81" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="I81" s="8">
-        <v>46111</v>
-      </c>
-      <c r="J81" s="8">
-        <v>46128</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>253</v>
-      </c>
       <c r="P81" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q81" s="8">
-        <v>46111</v>
-      </c>
-      <c r="R81" s="8">
-        <v>46119</v>
-      </c>
-      <c r="S81" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T81" s="9">
-        <v>0</v>
-      </c>
-      <c r="U81" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q81" s="9"/>
+      <c r="R81" s="9"/>
+      <c r="S81" s="9"/>
+      <c r="T81" s="9"/>
+      <c r="U81" s="9"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.69994784722</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.59349042824</v>
+        <v>46128.16821587963</v>
       </c>
       <c r="E82" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="I82" s="5">
+        <v>46111</v>
+      </c>
+      <c r="J82" s="5">
+        <v>46128</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="F82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="I82" s="5">
-        <v>46149</v>
-      </c>
-      <c r="J82" s="5">
-        <v>46150</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>286</v>
-      </c>
       <c r="Q82" s="5">
-        <v>46149</v>
+        <v>46111</v>
       </c>
       <c r="R82" s="5">
-        <v>46150</v>
-      </c>
-      <c r="S82" s="11" t="s">
-        <v>128</v>
+        <v>46119</v>
+      </c>
+      <c r="S82" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
@@ -6458,59 +6452,59 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.69994813658</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46198.592367060184</v>
+        <v>46198.59349042824</v>
       </c>
       <c r="E83" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="I83" s="8">
+        <v>46149</v>
+      </c>
+      <c r="J83" s="8">
+        <v>46150</v>
+      </c>
+      <c r="K83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="O83" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="F83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="I83" s="8">
-        <v>46134</v>
-      </c>
-      <c r="J83" s="8">
-        <v>46135</v>
-      </c>
-      <c r="K83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>286</v>
-      </c>
       <c r="Q83" s="8">
-        <v>46134</v>
+        <v>46149</v>
       </c>
       <c r="R83" s="8">
-        <v>46135</v>
-      </c>
-      <c r="S83" s="10" t="s">
-        <v>31</v>
+        <v>46150</v>
+      </c>
+      <c r="S83" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="T83" s="9">
         <v>0</v>
@@ -6521,62 +6515,62 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.699948368056</v>
+        <v>46073.69994813658</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46198.59272494213</v>
+        <v>46198.592367060184</v>
       </c>
       <c r="E84" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="I84" s="5">
+        <v>46134</v>
+      </c>
+      <c r="J84" s="5">
+        <v>46135</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="O84" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="I84" s="5">
-        <v>46136</v>
-      </c>
-      <c r="J84" s="5">
-        <v>46139</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>292</v>
-      </c>
       <c r="P84" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q84" s="5">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="R84" s="5">
-        <v>46139</v>
-      </c>
-      <c r="S84" s="12" t="s">
-        <v>293</v>
+        <v>46135</v>
+      </c>
+      <c r="S84" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T84" s="6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
         <v>58</v>
@@ -6584,62 +6578,62 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B85" s="8">
-        <v>46076.88137268518</v>
+        <v>46073.699948368056</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46195.60422616898</v>
+        <v>46198.59272494213</v>
       </c>
       <c r="E85" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="I85" s="8">
+        <v>46136</v>
+      </c>
+      <c r="J85" s="8">
+        <v>46139</v>
+      </c>
+      <c r="K85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="O85" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="P85" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q85" s="8">
+        <v>46136</v>
+      </c>
+      <c r="R85" s="8">
+        <v>46139</v>
+      </c>
+      <c r="S85" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="F85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="I85" s="8">
-        <v>46129</v>
-      </c>
-      <c r="J85" s="8">
-        <v>46132</v>
-      </c>
-      <c r="K85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="O85" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="P85" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q85" s="8">
-        <v>46129</v>
-      </c>
-      <c r="R85" s="8">
-        <v>46132</v>
-      </c>
-      <c r="S85" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="T85" s="9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U85" s="10" t="s">
         <v>58</v>
@@ -6647,32 +6641,32 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.69994864584</v>
+        <v>46076.88137268518</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46153.16811694445</v>
+        <v>46195.60422616898</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>225</v>
+        <v>297</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I86" s="5">
-        <v>46153</v>
+        <v>46129</v>
       </c>
       <c r="J86" s="5">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>26</v>
@@ -6684,22 +6678,22 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="P86" s="6" t="s">
-        <v>300</v>
-      </c>
       <c r="Q86" s="5">
-        <v>46153</v>
+        <v>46129</v>
       </c>
       <c r="R86" s="5">
-        <v>46153</v>
-      </c>
-      <c r="S86" s="11" t="s">
-        <v>128</v>
+        <v>46132</v>
+      </c>
+      <c r="S86" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6710,56 +6704,56 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.699948912035</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46154.16785564815</v>
+        <v>46153.16811694445</v>
       </c>
       <c r="E87" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="I87" s="8">
+        <v>46153</v>
+      </c>
+      <c r="J87" s="8">
+        <v>46153</v>
+      </c>
+      <c r="K87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="O87" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="P87" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="F87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="I87" s="8">
-        <v>46154</v>
-      </c>
-      <c r="J87" s="8">
-        <v>46154</v>
-      </c>
-      <c r="K87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="O87" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>303</v>
-      </c>
       <c r="Q87" s="8">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="R87" s="8">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="S87" s="11" t="s">
         <v>128</v>
@@ -6773,142 +6767,142 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.69994572917</v>
+        <v>46073.699948912035</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46077.638347245374</v>
+        <v>46154.16785564815</v>
       </c>
       <c r="E88" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="I88" s="5">
+        <v>46154</v>
+      </c>
+      <c r="J88" s="5">
+        <v>46154</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M88" s="6" t="s">
+      <c r="Q88" s="5">
+        <v>46154</v>
+      </c>
+      <c r="R88" s="5">
+        <v>46154</v>
+      </c>
+      <c r="S88" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="N88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
+      <c r="U88" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.699946099536</v>
+        <v>46073.69994572917</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46155.16794435185</v>
+        <v>46077.638347245374</v>
       </c>
       <c r="E89" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H89" s="9"/>
+      <c r="I89" s="9"/>
+      <c r="J89" s="9"/>
+      <c r="K89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O89" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="F89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I89" s="8">
-        <v>46155</v>
-      </c>
-      <c r="J89" s="8">
-        <v>46155</v>
-      </c>
-      <c r="K89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>302</v>
-      </c>
       <c r="P89" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q89" s="8">
-        <v>46155</v>
-      </c>
-      <c r="R89" s="8">
-        <v>46155</v>
-      </c>
-      <c r="S89" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="T89" s="9">
-        <v>0</v>
-      </c>
-      <c r="U89" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q89" s="9"/>
+      <c r="R89" s="9"/>
+      <c r="S89" s="9"/>
+      <c r="T89" s="9"/>
+      <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.69994638889</v>
+        <v>46073.699946099536</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46195.604670092594</v>
+        <v>46155.16794435185</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>281</v>
+        <v>35</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>281</v>
+        <v>36</v>
       </c>
       <c r="I90" s="5">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="J90" s="5">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>26</v>
@@ -6920,19 +6914,19 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="P90" s="6" t="s">
-        <v>312</v>
-      </c>
       <c r="Q90" s="5">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="R90" s="5">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="S90" s="11" t="s">
         <v>128</v>
@@ -6946,56 +6940,56 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.69994668981</v>
+        <v>46073.69994638889</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46161.25032122685</v>
+        <v>46195.604670092594</v>
       </c>
       <c r="E91" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="I91" s="8">
+        <v>46156</v>
+      </c>
+      <c r="J91" s="8">
+        <v>46160</v>
+      </c>
+      <c r="K91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="O91" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="P91" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="F91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="I91" s="8">
-        <v>46161</v>
-      </c>
-      <c r="J91" s="8">
-        <v>46161</v>
-      </c>
-      <c r="K91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="O91" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="P91" s="9" t="s">
-        <v>315</v>
-      </c>
       <c r="Q91" s="8">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="R91" s="8">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="S91" s="11" t="s">
         <v>128</v>
@@ -7009,56 +7003,56 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.69994695602</v>
+        <v>46073.69994668981</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46162.25040996527</v>
+        <v>46161.25032122685</v>
       </c>
       <c r="E92" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="I92" s="5">
+        <v>46161</v>
+      </c>
+      <c r="J92" s="5">
+        <v>46161</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="P92" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="I92" s="5">
-        <v>46162</v>
-      </c>
-      <c r="J92" s="5">
-        <v>46162</v>
-      </c>
-      <c r="K92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N92" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>318</v>
-      </c>
       <c r="Q92" s="5">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="R92" s="5">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="S92" s="11" t="s">
         <v>128</v>
@@ -7072,136 +7066,136 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.699947245375</v>
+        <v>46073.69994695602</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46077.6387968287</v>
+        <v>46162.25040996527</v>
       </c>
       <c r="E93" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I93" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J93" s="8">
+        <v>46162</v>
+      </c>
+      <c r="K93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N93" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="O93" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="P93" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="F93" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
-      <c r="I93" s="9"/>
-      <c r="J93" s="9"/>
-      <c r="K93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M93" s="9" t="s">
+      <c r="Q93" s="8">
+        <v>46162</v>
+      </c>
+      <c r="R93" s="8">
+        <v>46162</v>
+      </c>
+      <c r="S93" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T93" s="9">
         <v>0</v>
       </c>
-      <c r="N93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O93" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
-      <c r="S93" s="9"/>
-      <c r="T93" s="9"/>
-      <c r="U93" s="9"/>
+      <c r="U93" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.699947500005</v>
+        <v>46073.699947245375</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46174.16833755787</v>
+        <v>46077.6387968287</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O94" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="I94" s="5">
-        <v>46164</v>
-      </c>
-      <c r="J94" s="5">
-        <v>46174</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>317</v>
-      </c>
       <c r="P94" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q94" s="5">
-        <v>46164</v>
-      </c>
-      <c r="R94" s="5">
-        <v>46174</v>
-      </c>
-      <c r="S94" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="T94" s="6">
-        <v>0</v>
-      </c>
-      <c r="U94" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.699947789355</v>
+        <v>46073.699947500005</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46174.168340185184</v>
+        <v>46174.16833755787</v>
       </c>
       <c r="E95" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>325</v>
       </c>
       <c r="I95" s="8">
         <v>46164</v>
@@ -7219,13 +7213,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q95" s="8">
         <v>46164</v>
@@ -7245,47 +7239,57 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B96" s="5">
-        <v>46092.48971385417</v>
+        <v>46073.699947789355</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46092.497058946756</v>
+        <v>46174.168340185184</v>
       </c>
       <c r="E96" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="I96" s="5">
+        <v>46164</v>
+      </c>
+      <c r="J96" s="5">
+        <v>46174</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="O96" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F96" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>331</v>
-      </c>
       <c r="P96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
+        <v>322</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>46164</v>
+      </c>
+      <c r="R96" s="5">
+        <v>46174</v>
+      </c>
       <c r="S96" s="11" t="s">
         <v>128</v>
       </c>
@@ -7298,57 +7302,47 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B97" s="8">
-        <v>46092.49161491898</v>
+        <v>46092.48971385417</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46171.168742951384</v>
+        <v>46092.497058946756</v>
       </c>
       <c r="E97" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H97" s="9"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O97" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I97" s="8">
-        <v>46164</v>
-      </c>
-      <c r="J97" s="8">
-        <v>46171</v>
-      </c>
-      <c r="K97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N97" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="O97" s="9" t="s">
-        <v>317</v>
-      </c>
       <c r="P97" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q97" s="8">
-        <v>46164</v>
-      </c>
-      <c r="R97" s="8">
-        <v>46171</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q97" s="9"/>
+      <c r="R97" s="9"/>
       <c r="S97" s="11" t="s">
         <v>128</v>
       </c>
@@ -7361,17 +7355,17 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B98" s="5">
-        <v>46092.491661747685</v>
+        <v>46092.49161491898</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46181.16820616898</v>
+        <v>46171.168742951384</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7383,10 +7377,10 @@
         <v>50</v>
       </c>
       <c r="I98" s="5">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="J98" s="5">
-        <v>46181</v>
+        <v>46171</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>26</v>
@@ -7398,19 +7392,19 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="Q98" s="5">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="R98" s="5">
-        <v>46181</v>
+        <v>46171</v>
       </c>
       <c r="S98" s="11" t="s">
         <v>128</v>
@@ -7419,6 +7413,69 @@
         <v>0</v>
       </c>
       <c r="U98" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A99" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B99" s="8">
+        <v>46092.491661747685</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="8">
+        <v>46181.16820616898</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I99" s="8">
+        <v>46174</v>
+      </c>
+      <c r="J99" s="8">
+        <v>46181</v>
+      </c>
+      <c r="K99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="O99" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="P99" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q99" s="8">
+        <v>46174</v>
+      </c>
+      <c r="R99" s="8">
+        <v>46181</v>
+      </c>
+      <c r="S99" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T99" s="9">
+        <v>0</v>
+      </c>
+      <c r="U99" s="10" t="s">
         <v>58</v>
       </c>
     </row>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5446,7 +5446,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46198.821161875</v>
+        <v>46206.53745743056</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5554,9 +5554,11 @@
       <c r="B68" s="5">
         <v>46073.69994719907</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46206.53745016204</v>
+      </c>
       <c r="D68" s="5">
-        <v>46198.8211615162</v>
+        <v>46206.53745243055</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>240</v>
@@ -5666,7 +5668,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46092.50399041666</v>
+        <v>46206.53745877315</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>246</v>
@@ -5792,7 +5794,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46129.5864233912</v>
+        <v>46206.53801936343</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46206.53801936343</v>
+        <v>46206.58041065972</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46206.58041065972</v>
+        <v>46209.56306775463</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="341">
   <si>
     <t xml:space="preserve">50001490-ZITRON PERU METRO DE LIMA PV04-PV05 </t>
   </si>
@@ -944,6 +944,12 @@
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
   </si>
   <si>
     <t>Embalaje,Logistica:</t>
@@ -6886,7 +6892,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46155.16794435185</v>
+        <v>46210.60325569444</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>310</v>
@@ -6895,10 +6901,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>36</v>
+        <v>312</v>
       </c>
       <c r="I90" s="5">
         <v>46155</v>
@@ -6922,7 +6928,7 @@
         <v>304</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q90" s="5">
         <v>46155</v>
@@ -6942,7 +6948,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B91" s="8">
         <v>46073.69994638889</v>
@@ -6982,10 +6988,10 @@
         <v>307</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q91" s="8">
         <v>46156</v>
@@ -7005,7 +7011,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B92" s="5">
         <v>46073.69994668981</v>
@@ -7015,7 +7021,7 @@
         <v>46161.25032122685</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7048,7 +7054,7 @@
         <v>276</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q92" s="5">
         <v>46161</v>
@@ -7068,7 +7074,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B93" s="8">
         <v>46073.69994695602</v>
@@ -7078,7 +7084,7 @@
         <v>46162.25040996527</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7108,10 +7114,10 @@
         <v>307</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q93" s="8">
         <v>46162</v>
@@ -7131,7 +7137,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B94" s="5">
         <v>46073.699947245375</v>
@@ -7141,7 +7147,7 @@
         <v>46077.6387968287</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -7165,7 +7171,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -7178,7 +7184,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B95" s="8">
         <v>46073.699947500005</v>
@@ -7188,16 +7194,16 @@
         <v>46174.16833755787</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I95" s="8">
         <v>46164</v>
@@ -7215,13 +7221,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q95" s="8">
         <v>46164</v>
@@ -7241,7 +7247,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B96" s="5">
         <v>46073.699947789355</v>
@@ -7251,16 +7257,16 @@
         <v>46174.168340185184</v>
       </c>
       <c r="E96" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>329</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>327</v>
       </c>
       <c r="I96" s="5">
         <v>46164</v>
@@ -7278,13 +7284,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q96" s="5">
         <v>46164</v>
@@ -7304,7 +7310,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B97" s="8">
         <v>46092.48971385417</v>
@@ -7314,7 +7320,7 @@
         <v>46092.497058946756</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>25</v>
@@ -7338,7 +7344,7 @@
         <v>26</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>26</v>
@@ -7357,7 +7363,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B98" s="5">
         <v>46092.49161491898</v>
@@ -7367,7 +7373,7 @@
         <v>46171.168742951384</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7394,13 +7400,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q98" s="5">
         <v>46164</v>
@@ -7420,7 +7426,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B99" s="8">
         <v>46092.491661747685</v>
@@ -7430,7 +7436,7 @@
         <v>46181.16820616898</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7457,13 +7463,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q99" s="8">
         <v>46174</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="326">
   <si>
     <t xml:space="preserve">50001490-ZITRON PERU METRO DE LIMA PV04-PV05 </t>
   </si>
@@ -643,6 +643,9 @@
     <t>nicolas.lopez@zitron.com</t>
   </si>
   <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
     <t>1213380177588299</t>
   </si>
   <si>
@@ -685,7 +688,7 @@
     <t>1213598288999630</t>
   </si>
   <si>
-    <t xml:space="preserve">Armado,Control de calidad Armado,Montaje motor,Montaje Alabe,Montaje Rodete,Ingenieria y diseñoo:,Montaje Sensor,Propuesta Fabricacion externa </t>
+    <t xml:space="preserve">Montaje motor,Montaje Alabe,Montaje Rodete,Ingenieria y diseñoo:,Montaje Sensor,Propuesta Fabricacion externa </t>
   </si>
   <si>
     <t>1213598288999631</t>
@@ -736,238 +739,190 @@
     <t>Control de calidad compras materiales a codigo // compras locale aprovisionamiento</t>
   </si>
   <si>
-    <t>Bodega:,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1213380177588305</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213380177588306</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
+    <t>1213380177588309</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Sensor,Recepcion Alabe,Recepcion Tableros,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1213380177588310</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213380177588311</t>
+  </si>
+  <si>
+    <t>Bodega:,Revisión tableros pruebas</t>
+  </si>
+  <si>
+    <t>1213380177588312</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213380177588313</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje motor</t>
+  </si>
+  <si>
+    <t>1213400421980588</t>
+  </si>
+  <si>
+    <t>Recepcion Sensor</t>
+  </si>
+  <si>
+    <t>Bodega:,Montaje Sensor</t>
+  </si>
+  <si>
+    <t>1213400424143464</t>
+  </si>
+  <si>
+    <t>Recepcion Atenuador</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
+    <t>1213400424143465</t>
+  </si>
+  <si>
+    <t>1213380177588314</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1213380177588315</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:,Montaje Sensor</t>
+  </si>
+  <si>
+    <t>1213380177588316</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion motor,Check Planos</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,Montaje:</t>
+  </si>
+  <si>
+    <t>1213380177588317</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Alabe,Check Planos</t>
+  </si>
+  <si>
+    <t>1213380177588318</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Rodete,Check Planos</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1213400421980589</t>
+  </si>
+  <si>
+    <t>Montaje Sensor</t>
+  </si>
+  <si>
+    <t>Revestimiento,Recepcion Sensor,Check Planos</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,Montaje:,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213380177588319</t>
+  </si>
+  <si>
+    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor</t>
+  </si>
+  <si>
+    <t>Montaje:,Check Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213380177588320</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1213380177588321</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+  </si>
+  <si>
+    <t>1213380177588322</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>Embalaje,Logistica:</t>
+  </si>
+  <si>
+    <t>1213380177588323</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Revisión tableros pruebas,Recepcion Atenuador,Recepcion  Damper</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Logistica:</t>
+  </si>
+  <si>
+    <t>1213380177588324</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
   </si>
   <si>
     <t>Nicolás Mol</t>
   </si>
   <si>
     <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Armado,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213380177588307</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Caldereria:</t>
-  </si>
-  <si>
-    <t>1213380177588308</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Armado,Check Planos</t>
-  </si>
-  <si>
-    <t>Caldereria:,Revestimiento</t>
-  </si>
-  <si>
-    <t>1213380177588309</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Sensor,Recepcion Alabe,Recepcion Tableros,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1213380177588310</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213380177588311</t>
-  </si>
-  <si>
-    <t>Bodega:,Revisión tableros pruebas</t>
-  </si>
-  <si>
-    <t>1213380177588312</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213380177588313</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje motor</t>
-  </si>
-  <si>
-    <t>1213400421980588</t>
-  </si>
-  <si>
-    <t>Recepcion Sensor</t>
-  </si>
-  <si>
-    <t>Bodega:,Montaje Sensor</t>
-  </si>
-  <si>
-    <t>1213400424143464</t>
-  </si>
-  <si>
-    <t>Recepcion Atenuador</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t>1213400424143465</t>
-  </si>
-  <si>
-    <t>1213380177588314</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1213380177588315</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:,Montaje Sensor</t>
-  </si>
-  <si>
-    <t>1213380177588316</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion motor,Check Planos</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,Montaje:</t>
-  </si>
-  <si>
-    <t>1213380177588317</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Alabe,Check Planos</t>
-  </si>
-  <si>
-    <t>1213380177588318</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Rodete,Check Planos</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1213400421980589</t>
-  </si>
-  <si>
-    <t>Montaje Sensor</t>
-  </si>
-  <si>
-    <t>Revestimiento,Recepcion Sensor,Check Planos</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,Montaje:,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213380177588319</t>
-  </si>
-  <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje Sensor</t>
-  </si>
-  <si>
-    <t>Montaje:,Check Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213380177588320</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1213380177588321</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
-  </si>
-  <si>
-    <t>1213380177588322</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>Embalaje,Logistica:</t>
-  </si>
-  <si>
-    <t>1213380177588323</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Revisión tableros pruebas,Recepcion Atenuador,Recepcion  Damper</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Logistica:</t>
-  </si>
-  <si>
-    <t>1213380177588324</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
   </si>
   <si>
     <t>Despacho,Logistica:</t>
@@ -1557,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U99"/>
+  <dimension ref="A1:U95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5098,7 +5053,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46205.80976949074</v>
+        <v>46210.86168509259</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5132,7 +5087,7 @@
         <v>26</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5142,7 +5097,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B61" s="8">
         <v>46073.69994815972</v>
@@ -5152,7 +5107,7 @@
         <v>46129.586425601854</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5176,7 +5131,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5189,7 +5144,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46073.6999484375</v>
@@ -5201,16 +5156,16 @@
         <v>46099.54242268519</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I62" s="5">
         <v>46003</v>
@@ -5228,13 +5183,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q62" s="5">
         <v>46003</v>
@@ -5254,7 +5209,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B63" s="8">
         <v>46073.699946249995</v>
@@ -5266,16 +5221,16 @@
         <v>46129.58626813657</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I63" s="8">
         <v>46058</v>
@@ -5293,13 +5248,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q63" s="8">
         <v>46058</v>
@@ -5319,7 +5274,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46092.494241736116</v>
@@ -5328,7 +5283,7 @@
         <v>46129.58641790509</v>
       </c>
       <c r="D64" s="5">
-        <v>46139.54817715278</v>
+        <v>46210.861392569444</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>115</v>
@@ -5337,10 +5292,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5356,13 +5311,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="5">
         <v>46065</v>
@@ -5382,7 +5337,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46092.49428590278</v>
@@ -5392,16 +5347,16 @@
         <v>46154.16811805556</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I65" s="8">
         <v>46154</v>
@@ -5419,13 +5374,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q65" s="8">
         <v>46154</v>
@@ -5445,17 +5400,17 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46073.69994662037</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46206.53745743056</v>
+        <v>46210.858702094905</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5479,7 +5434,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5492,26 +5447,28 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B67" s="8">
         <v>46073.69994689815</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46210.858693472226</v>
+      </c>
       <c r="D67" s="8">
-        <v>46199.82444644676</v>
+        <v>46210.85869597222</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I67" s="8">
         <v>46063</v>
@@ -5529,13 +5486,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>171</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="8">
         <v>46063</v>
@@ -5555,7 +5512,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
         <v>46073.69994719907</v>
@@ -5564,10 +5521,10 @@
         <v>46206.53745016204</v>
       </c>
       <c r="D68" s="5">
-        <v>46206.53745243055</v>
+        <v>46210.86139240741</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5594,13 +5551,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="5">
         <v>46065</v>
@@ -5623,14 +5580,14 @@
         <v>242</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.69994748842</v>
+        <v>46073.699948865746</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46077.62916171296</v>
+        <v>46195.604225717594</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5654,7 +5611,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5667,56 +5624,56 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.69994777778</v>
+        <v>46073.69995097222</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46206.53745877315</v>
+        <v>46199.830143969906</v>
       </c>
       <c r="E70" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I70" s="5">
+        <v>46097</v>
+      </c>
+      <c r="J70" s="5">
+        <v>46098</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="I70" s="5">
-        <v>46069</v>
-      </c>
-      <c r="J70" s="5">
-        <v>46077</v>
-      </c>
-      <c r="K70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>249</v>
-      </c>
       <c r="Q70" s="5">
-        <v>46069</v>
+        <v>46097</v>
       </c>
       <c r="R70" s="5">
-        <v>46077</v>
+        <v>46098</v>
       </c>
       <c r="S70" s="10" t="s">
         <v>31</v>
@@ -5730,56 +5687,56 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.699948113426</v>
+        <v>46073.69994640046</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46129.58642229167</v>
+        <v>46121.187778182866</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>251</v>
+        <v>56</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="H71" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="I71" s="8">
+        <v>46119</v>
+      </c>
+      <c r="J71" s="8">
+        <v>46120</v>
+      </c>
+      <c r="K71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="I71" s="8">
-        <v>46078</v>
-      </c>
-      <c r="J71" s="8">
-        <v>46106</v>
-      </c>
-      <c r="K71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>253</v>
-      </c>
       <c r="Q71" s="8">
-        <v>46078</v>
+        <v>46119</v>
       </c>
       <c r="R71" s="8">
-        <v>46106</v>
+        <v>46120</v>
       </c>
       <c r="S71" s="10" t="s">
         <v>31</v>
@@ -5793,32 +5750,32 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.69994846065</v>
+        <v>46073.699946782406</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46209.56306775463</v>
+        <v>46199.82646660879</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="I72" s="5">
-        <v>46107</v>
+        <v>46132</v>
       </c>
       <c r="J72" s="5">
-        <v>46108</v>
+        <v>46133</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
@@ -5830,19 +5787,19 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>256</v>
+        <v>130</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="Q72" s="5">
-        <v>46107</v>
+        <v>46132</v>
       </c>
       <c r="R72" s="5">
-        <v>46108</v>
+        <v>46133</v>
       </c>
       <c r="S72" s="10" t="s">
         <v>31</v>
@@ -5856,27 +5813,35 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.699948865746</v>
-      </c>
-      <c r="C73" s="9"/>
+        <v>46073.69994708333</v>
+      </c>
+      <c r="C73" s="8">
+        <v>46195.603957824074</v>
+      </c>
       <c r="D73" s="8">
-        <v>46195.604225717594</v>
+        <v>46195.603959687505</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="9"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
+        <v>237</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="I73" s="8">
+        <v>46147</v>
+      </c>
+      <c r="J73" s="8">
+        <v>46148</v>
+      </c>
       <c r="K73" s="9" t="s">
         <v>26</v>
       </c>
@@ -5884,51 +5849,63 @@
         <v>26</v>
       </c>
       <c r="M73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="P73" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q73" s="8">
+        <v>46147</v>
+      </c>
+      <c r="R73" s="8">
+        <v>46148</v>
+      </c>
+      <c r="S73" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T73" s="9">
         <v>0</v>
       </c>
-      <c r="N73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q73" s="9"/>
-      <c r="R73" s="9"/>
-      <c r="S73" s="9"/>
-      <c r="T73" s="9"/>
-      <c r="U73" s="9"/>
+      <c r="U73" s="12" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46073.69995097222</v>
-      </c>
-      <c r="C74" s="6"/>
+        <v>46076.88127923611</v>
+      </c>
+      <c r="C74" s="5">
+        <v>46195.60421921297</v>
+      </c>
       <c r="D74" s="5">
-        <v>46199.830143969906</v>
+        <v>46195.60422127315</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I74" s="5">
-        <v>46097</v>
+        <v>46121</v>
       </c>
       <c r="J74" s="5">
-        <v>46098</v>
+        <v>46122</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
@@ -5940,19 +5917,19 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="Q74" s="5">
-        <v>46097</v>
+        <v>46121</v>
       </c>
       <c r="R74" s="5">
-        <v>46098</v>
+        <v>46122</v>
       </c>
       <c r="S74" s="10" t="s">
         <v>31</v>
@@ -5960,38 +5937,40 @@
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="10" t="s">
-        <v>58</v>
+      <c r="U74" s="12" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B75" s="8">
-        <v>46073.69994640046</v>
-      </c>
-      <c r="C75" s="9"/>
+        <v>46077.57961084491</v>
+      </c>
+      <c r="C75" s="8">
+        <v>46195.60466336805</v>
+      </c>
       <c r="D75" s="8">
-        <v>46121.187778182866</v>
+        <v>46195.60466490741</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>56</v>
+        <v>259</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I75" s="8">
-        <v>46119</v>
+        <v>46104</v>
       </c>
       <c r="J75" s="8">
-        <v>46120</v>
+        <v>46105</v>
       </c>
       <c r="K75" s="9" t="s">
         <v>26</v>
@@ -6003,19 +5982,19 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="Q75" s="8">
-        <v>46119</v>
+        <v>46104</v>
       </c>
       <c r="R75" s="8">
-        <v>46120</v>
+        <v>46105</v>
       </c>
       <c r="S75" s="10" t="s">
         <v>31</v>
@@ -6029,32 +6008,32 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B76" s="5">
-        <v>46073.699946782406</v>
+        <v>46077.57965403935</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46199.82646660879</v>
+        <v>46182.692112696765</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I76" s="5">
-        <v>46132</v>
+        <v>46098</v>
       </c>
       <c r="J76" s="5">
-        <v>46133</v>
+        <v>46099</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
@@ -6066,19 +6045,19 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="Q76" s="5">
-        <v>46132</v>
+        <v>46098</v>
       </c>
       <c r="R76" s="5">
-        <v>46133</v>
+        <v>46099</v>
       </c>
       <c r="S76" s="10" t="s">
         <v>31</v>
@@ -6092,35 +6071,27 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.69994708333</v>
-      </c>
-      <c r="C77" s="8">
-        <v>46195.603957824074</v>
-      </c>
+        <v>46073.69994733796</v>
+      </c>
+      <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46195.603959687505</v>
+        <v>46078.621237141204</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="I77" s="8">
-        <v>46147</v>
-      </c>
-      <c r="J77" s="8">
-        <v>46148</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
       <c r="K77" s="9" t="s">
         <v>26</v>
       </c>
@@ -6128,63 +6099,51 @@
         <v>26</v>
       </c>
       <c r="M77" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>232</v>
+        <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>157</v>
+        <v>264</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q77" s="8">
-        <v>46147</v>
-      </c>
-      <c r="R77" s="8">
-        <v>46148</v>
-      </c>
-      <c r="S77" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="T77" s="9">
-        <v>0</v>
-      </c>
-      <c r="U77" s="12" t="s">
-        <v>201</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
+      <c r="S77" s="9"/>
+      <c r="T77" s="9"/>
+      <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B78" s="5">
-        <v>46076.88127923611</v>
-      </c>
-      <c r="C78" s="5">
-        <v>46195.60421921297</v>
-      </c>
+        <v>46073.69994759259</v>
+      </c>
+      <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46195.60422127315</v>
+        <v>46210.861684930554</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>272</v>
+        <v>210</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="I78" s="5">
-        <v>46121</v>
+        <v>46111</v>
       </c>
       <c r="J78" s="5">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
@@ -6196,19 +6155,19 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="Q78" s="5">
-        <v>46121</v>
+        <v>46111</v>
       </c>
       <c r="R78" s="5">
-        <v>46122</v>
+        <v>46119</v>
       </c>
       <c r="S78" s="10" t="s">
         <v>31</v>
@@ -6216,40 +6175,38 @@
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="12" t="s">
-        <v>201</v>
+      <c r="U78" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.57961084491</v>
-      </c>
-      <c r="C79" s="8">
-        <v>46195.60466336805</v>
-      </c>
+        <v>46073.69994784722</v>
+      </c>
+      <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46195.60466490741</v>
+        <v>46198.59349042824</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="I79" s="8">
-        <v>46104</v>
+        <v>46149</v>
       </c>
       <c r="J79" s="8">
-        <v>46105</v>
+        <v>46150</v>
       </c>
       <c r="K79" s="9" t="s">
         <v>26</v>
@@ -6261,22 +6218,22 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>195</v>
+        <v>270</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q79" s="8">
-        <v>46104</v>
+        <v>46149</v>
       </c>
       <c r="R79" s="8">
-        <v>46105</v>
-      </c>
-      <c r="S79" s="10" t="s">
-        <v>31</v>
+        <v>46150</v>
+      </c>
+      <c r="S79" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="T79" s="9">
         <v>0</v>
@@ -6287,32 +6244,32 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B80" s="5">
-        <v>46077.57965403935</v>
+        <v>46073.69994813658</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.692112696765</v>
+        <v>46198.592367060184</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>188</v>
+        <v>273</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="I80" s="5">
-        <v>46098</v>
+        <v>46134</v>
       </c>
       <c r="J80" s="5">
-        <v>46099</v>
+        <v>46135</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6324,19 +6281,19 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>187</v>
+        <v>274</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q80" s="5">
-        <v>46098</v>
+        <v>46134</v>
       </c>
       <c r="R80" s="5">
-        <v>46099</v>
+        <v>46135</v>
       </c>
       <c r="S80" s="10" t="s">
         <v>31</v>
@@ -6350,27 +6307,33 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.69994733796</v>
+        <v>46073.699948368056</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46078.621237141204</v>
+        <v>46198.59272494213</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
+        <v>266</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="I81" s="8">
+        <v>46136</v>
+      </c>
+      <c r="J81" s="8">
+        <v>46139</v>
+      </c>
       <c r="K81" s="9" t="s">
         <v>26</v>
       </c>
@@ -6378,75 +6341,85 @@
         <v>26</v>
       </c>
       <c r="M81" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>26</v>
+        <v>263</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q81" s="9"/>
-      <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
-      <c r="T81" s="9"/>
-      <c r="U81" s="9"/>
+        <v>271</v>
+      </c>
+      <c r="Q81" s="8">
+        <v>46136</v>
+      </c>
+      <c r="R81" s="8">
+        <v>46139</v>
+      </c>
+      <c r="S81" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="T81" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U81" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46073.69994759259</v>
+        <v>46076.88137268518</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46128.16821587963</v>
+        <v>46195.60422616898</v>
       </c>
       <c r="E82" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="I82" s="5">
+        <v>46129</v>
+      </c>
+      <c r="J82" s="5">
+        <v>46132</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="F82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="I82" s="5">
-        <v>46111</v>
-      </c>
-      <c r="J82" s="5">
-        <v>46128</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>284</v>
-      </c>
       <c r="Q82" s="5">
-        <v>46111</v>
+        <v>46129</v>
       </c>
       <c r="R82" s="5">
-        <v>46119</v>
+        <v>46132</v>
       </c>
       <c r="S82" s="10" t="s">
         <v>31</v>
@@ -6460,32 +6433,32 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.69994784722</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46198.59349042824</v>
+        <v>46153.16811694445</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="I83" s="8">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="J83" s="8">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="K83" s="9" t="s">
         <v>26</v>
@@ -6497,19 +6470,19 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Q83" s="8">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="R83" s="8">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="S83" s="11" t="s">
         <v>128</v>
@@ -6523,32 +6496,32 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.69994813658</v>
+        <v>46073.699948912035</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46198.592367060184</v>
+        <v>46154.16785564815</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="I84" s="5">
-        <v>46134</v>
+        <v>46154</v>
       </c>
       <c r="J84" s="5">
-        <v>46135</v>
+        <v>46154</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
@@ -6560,22 +6533,22 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>291</v>
+        <v>227</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>288</v>
       </c>
       <c r="Q84" s="5">
-        <v>46134</v>
+        <v>46154</v>
       </c>
       <c r="R84" s="5">
-        <v>46135</v>
-      </c>
-      <c r="S84" s="10" t="s">
-        <v>31</v>
+        <v>46154</v>
+      </c>
+      <c r="S84" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6586,33 +6559,27 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46073.699948368056</v>
+        <v>46073.69994572917</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46198.59272494213</v>
+        <v>46077.638347245374</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="I85" s="8">
-        <v>46136</v>
-      </c>
-      <c r="J85" s="8">
-        <v>46139</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="9"/>
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
       <c r="K85" s="9" t="s">
         <v>26</v>
       </c>
@@ -6620,61 +6587,51 @@
         <v>26</v>
       </c>
       <c r="M85" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>279</v>
+        <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q85" s="8">
-        <v>46136</v>
-      </c>
-      <c r="R85" s="8">
-        <v>46139</v>
-      </c>
-      <c r="S85" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="T85" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="U85" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q85" s="9"/>
+      <c r="R85" s="9"/>
+      <c r="S85" s="9"/>
+      <c r="T85" s="9"/>
+      <c r="U85" s="9"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B86" s="5">
-        <v>46076.88137268518</v>
+        <v>46073.699946099536</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46195.60422616898</v>
+        <v>46210.60325569444</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="I86" s="5">
-        <v>46129</v>
+        <v>46155</v>
       </c>
       <c r="J86" s="5">
-        <v>46132</v>
+        <v>46155</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>26</v>
@@ -6686,22 +6643,22 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q86" s="5">
-        <v>46129</v>
+        <v>46155</v>
       </c>
       <c r="R86" s="5">
-        <v>46132</v>
-      </c>
-      <c r="S86" s="10" t="s">
-        <v>31</v>
+        <v>46155</v>
+      </c>
+      <c r="S86" s="11" t="s">
+        <v>128</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6712,32 +6669,32 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.69994864584</v>
+        <v>46073.69994638889</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46153.16811694445</v>
+        <v>46195.604670092594</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="I87" s="8">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="J87" s="8">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="K87" s="9" t="s">
         <v>26</v>
@@ -6749,19 +6706,19 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="Q87" s="8">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="R87" s="8">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="S87" s="11" t="s">
         <v>128</v>
@@ -6775,56 +6732,56 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.699948912035</v>
+        <v>46073.69994668981</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46154.16785564815</v>
+        <v>46161.25032122685</v>
       </c>
       <c r="E88" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="I88" s="5">
+        <v>46161</v>
+      </c>
+      <c r="J88" s="5">
+        <v>46161</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="I88" s="5">
-        <v>46154</v>
-      </c>
-      <c r="J88" s="5">
-        <v>46154</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>305</v>
-      </c>
       <c r="Q88" s="5">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="R88" s="5">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="S88" s="11" t="s">
         <v>128</v>
@@ -6838,142 +6795,142 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.69994572917</v>
+        <v>46073.69994695602</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46077.638347245374</v>
+        <v>46162.25040996527</v>
       </c>
       <c r="E89" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="I89" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J89" s="8">
+        <v>46162</v>
+      </c>
+      <c r="K89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="O89" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="P89" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="F89" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="9"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="9"/>
-      <c r="K89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="9" t="s">
+      <c r="Q89" s="8">
+        <v>46162</v>
+      </c>
+      <c r="R89" s="8">
+        <v>46162</v>
+      </c>
+      <c r="S89" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T89" s="9">
         <v>0</v>
       </c>
-      <c r="N89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q89" s="9"/>
-      <c r="R89" s="9"/>
-      <c r="S89" s="9"/>
-      <c r="T89" s="9"/>
-      <c r="U89" s="9"/>
+      <c r="U89" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.699946099536</v>
+        <v>46073.699947245375</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46210.60325569444</v>
+        <v>46077.6387968287</v>
       </c>
       <c r="E90" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O90" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="F90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G90" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="I90" s="5">
-        <v>46155</v>
-      </c>
-      <c r="J90" s="5">
-        <v>46155</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>304</v>
-      </c>
       <c r="P90" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q90" s="5">
-        <v>46155</v>
-      </c>
-      <c r="R90" s="5">
-        <v>46155</v>
-      </c>
-      <c r="S90" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="T90" s="6">
-        <v>0</v>
-      </c>
-      <c r="U90" s="10" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6"/>
+      <c r="T90" s="6"/>
+      <c r="U90" s="6"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.69994638889</v>
+        <v>46073.699947500005</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46195.604670092594</v>
+        <v>46174.16833755787</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="I91" s="8">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="J91" s="8">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="K91" s="9" t="s">
         <v>26</v>
@@ -6985,19 +6942,19 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="Q91" s="8">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="R91" s="8">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="S91" s="11" t="s">
         <v>128</v>
@@ -7011,32 +6968,32 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.69994668981</v>
+        <v>46073.699947789355</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46161.25032122685</v>
+        <v>46174.168340185184</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>247</v>
+        <v>313</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>248</v>
+        <v>314</v>
       </c>
       <c r="I92" s="5">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="J92" s="5">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>26</v>
@@ -7048,19 +7005,19 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="Q92" s="5">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="R92" s="5">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="S92" s="11" t="s">
         <v>128</v>
@@ -7074,33 +7031,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B93" s="8">
-        <v>46073.69994695602</v>
+        <v>46092.48971385417</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46162.25040996527</v>
+        <v>46092.497058946756</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="I93" s="8">
-        <v>46162</v>
-      </c>
-      <c r="J93" s="8">
-        <v>46162</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="9"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="9"/>
       <c r="K93" s="9" t="s">
         <v>26</v>
       </c>
@@ -7108,23 +7059,19 @@
         <v>26</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q93" s="8">
-        <v>46162</v>
-      </c>
-      <c r="R93" s="8">
-        <v>46162</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="9"/>
       <c r="S93" s="11" t="s">
         <v>128</v>
       </c>
@@ -7137,27 +7084,33 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B94" s="5">
-        <v>46073.699947245375</v>
+        <v>46092.49161491898</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46077.6387968287</v>
+        <v>46171.168742951384</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
+        <v>49</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I94" s="5">
+        <v>46164</v>
+      </c>
+      <c r="J94" s="5">
+        <v>46171</v>
+      </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
       </c>
@@ -7165,75 +7118,85 @@
         <v>26</v>
       </c>
       <c r="M94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46164</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46171</v>
+      </c>
+      <c r="S94" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="N94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+      <c r="U94" s="10" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B95" s="8">
-        <v>46073.699947500005</v>
+        <v>46092.491661747685</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46174.16833755787</v>
+        <v>46181.16820616898</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>328</v>
+        <v>49</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>329</v>
+        <v>50</v>
       </c>
       <c r="I95" s="8">
-        <v>46164</v>
+        <v>46174</v>
       </c>
       <c r="J95" s="8">
+        <v>46181</v>
+      </c>
+      <c r="K95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N95" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="O95" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="P95" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q95" s="8">
         <v>46174</v>
       </c>
-      <c r="K95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N95" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q95" s="8">
-        <v>46164</v>
-      </c>
       <c r="R95" s="8">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="S95" s="11" t="s">
         <v>128</v>
@@ -7242,248 +7205,6 @@
         <v>0</v>
       </c>
       <c r="U95" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B96" s="5">
-        <v>46073.699947789355</v>
-      </c>
-      <c r="C96" s="6"/>
-      <c r="D96" s="5">
-        <v>46174.168340185184</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="I96" s="5">
-        <v>46164</v>
-      </c>
-      <c r="J96" s="5">
-        <v>46174</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q96" s="5">
-        <v>46164</v>
-      </c>
-      <c r="R96" s="5">
-        <v>46174</v>
-      </c>
-      <c r="S96" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="T96" s="6">
-        <v>0</v>
-      </c>
-      <c r="U96" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B97" s="8">
-        <v>46092.48971385417</v>
-      </c>
-      <c r="C97" s="9"/>
-      <c r="D97" s="8">
-        <v>46092.497058946756</v>
-      </c>
-      <c r="E97" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="9"/>
-      <c r="I97" s="9"/>
-      <c r="J97" s="9"/>
-      <c r="K97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O97" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q97" s="9"/>
-      <c r="R97" s="9"/>
-      <c r="S97" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="T97" s="9">
-        <v>0</v>
-      </c>
-      <c r="U97" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B98" s="5">
-        <v>46092.49161491898</v>
-      </c>
-      <c r="C98" s="6"/>
-      <c r="D98" s="5">
-        <v>46171.168742951384</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I98" s="5">
-        <v>46164</v>
-      </c>
-      <c r="J98" s="5">
-        <v>46171</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N98" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="O98" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q98" s="5">
-        <v>46164</v>
-      </c>
-      <c r="R98" s="5">
-        <v>46171</v>
-      </c>
-      <c r="S98" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="B99" s="8">
-        <v>46092.491661747685</v>
-      </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="8">
-        <v>46181.16820616898</v>
-      </c>
-      <c r="E99" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I99" s="8">
-        <v>46174</v>
-      </c>
-      <c r="J99" s="8">
-        <v>46181</v>
-      </c>
-      <c r="K99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N99" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="O99" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="P99" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q99" s="8">
-        <v>46174</v>
-      </c>
-      <c r="R99" s="8">
-        <v>46181</v>
-      </c>
-      <c r="S99" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="T99" s="9">
-        <v>0</v>
-      </c>
-      <c r="U99" s="10" t="s">
         <v>58</v>
       </c>
     </row>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1615,13 +1615,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.69994636574</v>
+        <v>46073.53327969907</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.71869384259</v>
+        <v>46092.55202717593</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.78238695602</v>
+        <v>46118.61572028935</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1664,13 +1664,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.69994672453</v>
+        <v>46073.53328005787</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.7187837963</v>
+        <v>46092.55211712963</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.71880180556</v>
+        <v>46092.55213513889</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1729,13 +1729,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.69994701388</v>
+        <v>46073.53328034723</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.718810590275</v>
+        <v>46092.55214392361</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71882512732</v>
+        <v>46092.55215846065</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1794,13 +1794,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.69994730324</v>
+        <v>46073.53328063658</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.71882415509</v>
+        <v>46092.552157488426</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71884173611</v>
+        <v>46092.552175069446</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1859,13 +1859,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.699947581015</v>
+        <v>46073.53328091435</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.71883331018</v>
+        <v>46092.55216664352</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.75450768518</v>
+        <v>46093.58784101852</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1924,13 +1924,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.69994784722</v>
+        <v>46073.53328118056</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.718850590274</v>
+        <v>46092.55218392361</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71886530092</v>
+        <v>46092.552198634265</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1989,11 +1989,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.699948124995</v>
+        <v>46073.53328145834</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.89302402778</v>
+        <v>46127.72635736111</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2036,13 +2036,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.699948379624</v>
+        <v>46073.53328171297</v>
       </c>
       <c r="C11" s="8">
-        <v>46093.86155634259</v>
+        <v>46093.69488967593</v>
       </c>
       <c r="D11" s="8">
-        <v>46093.86157599537</v>
+        <v>46093.694909328704</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2101,11 +2101,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.69994864584</v>
+        <v>46073.533281979166</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46134.69385214121</v>
+        <v>46134.52718547454</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2164,13 +2164,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.69994892361</v>
+        <v>46073.53328225695</v>
       </c>
       <c r="C13" s="8">
-        <v>46093.75482240741</v>
+        <v>46093.58815574074</v>
       </c>
       <c r="D13" s="8">
-        <v>46093.7548365625</v>
+        <v>46093.58816989583</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2217,13 +2217,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.69994622685</v>
+        <v>46073.533279560186</v>
       </c>
       <c r="C14" s="5">
-        <v>46093.75466950232</v>
+        <v>46093.58800283565</v>
       </c>
       <c r="D14" s="5">
-        <v>46093.754690856484</v>
+        <v>46093.58802418981</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2282,13 +2282,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.6999465625</v>
+        <v>46073.53327989583</v>
       </c>
       <c r="C15" s="8">
-        <v>46093.754681597224</v>
+        <v>46093.58801493056</v>
       </c>
       <c r="D15" s="8">
-        <v>46093.75469819445</v>
+        <v>46093.588031527775</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2347,13 +2347,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.69994685185</v>
+        <v>46073.533280185184</v>
       </c>
       <c r="C16" s="5">
-        <v>46093.754692187504</v>
+        <v>46093.58802552083</v>
       </c>
       <c r="D16" s="5">
-        <v>46093.75471203704</v>
+        <v>46093.58804537037</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2412,13 +2412,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.69994711806</v>
+        <v>46073.53328045139</v>
       </c>
       <c r="C17" s="8">
-        <v>46093.7547025463</v>
+        <v>46093.58803587963</v>
       </c>
       <c r="D17" s="8">
-        <v>46093.75472228009</v>
+        <v>46093.58805561342</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2477,13 +2477,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.577641701384</v>
+        <v>46077.41097503473</v>
       </c>
       <c r="C18" s="5">
-        <v>46093.754712118054</v>
+        <v>46093.58804545139</v>
       </c>
       <c r="D18" s="5">
-        <v>46093.7547315625</v>
+        <v>46093.588064895834</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2542,13 +2542,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.57773309028</v>
+        <v>46077.41106642361</v>
       </c>
       <c r="C19" s="8">
-        <v>46093.754724375</v>
+        <v>46093.58805770833</v>
       </c>
       <c r="D19" s="8">
-        <v>46093.75474146991</v>
+        <v>46093.588074803236</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2607,13 +2607,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.69994737269</v>
+        <v>46073.53328070602</v>
       </c>
       <c r="C20" s="5">
-        <v>46093.75480502315</v>
+        <v>46093.588138356485</v>
       </c>
       <c r="D20" s="5">
-        <v>46093.75482354166</v>
+        <v>46093.588156875005</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2672,13 +2672,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.69994763889</v>
+        <v>46073.533280972224</v>
       </c>
       <c r="C21" s="8">
-        <v>46093.87454615741</v>
+        <v>46093.70787949074</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.54278021991</v>
+        <v>46139.37611355324</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2725,13 +2725,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.6999481713</v>
+        <v>46073.53328150463</v>
       </c>
       <c r="C22" s="5">
-        <v>46093.75476994213</v>
+        <v>46093.58810327546</v>
       </c>
       <c r="D22" s="5">
-        <v>46093.754786307865</v>
+        <v>46093.58811964121</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2790,13 +2790,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.69994789352</v>
+        <v>46073.53328122685</v>
       </c>
       <c r="C23" s="8">
-        <v>46093.754781041665</v>
+        <v>46093.588114375</v>
       </c>
       <c r="D23" s="8">
-        <v>46093.75479849537</v>
+        <v>46093.5881318287</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2855,13 +2855,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.69994854167</v>
+        <v>46073.533281875</v>
       </c>
       <c r="C24" s="5">
-        <v>46093.874529837965</v>
+        <v>46093.707863171294</v>
       </c>
       <c r="D24" s="5">
-        <v>46093.87454729166</v>
+        <v>46093.707880625</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2920,13 +2920,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.69994881944</v>
+        <v>46073.53328215278</v>
       </c>
       <c r="C25" s="8">
-        <v>46093.75482736111</v>
+        <v>46093.588160694446</v>
       </c>
       <c r="D25" s="8">
-        <v>46093.754844745374</v>
+        <v>46093.5881780787</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2985,13 +2985,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.699946319444</v>
+        <v>46073.53327965278</v>
       </c>
       <c r="C26" s="5">
-        <v>46093.754836238426</v>
+        <v>46093.588169571754</v>
       </c>
       <c r="D26" s="5">
-        <v>46093.75485591435</v>
+        <v>46093.58818924769</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3050,13 +3050,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46076.88102377315</v>
+        <v>46076.71435710648</v>
       </c>
       <c r="C27" s="8">
-        <v>46093.75484537037</v>
+        <v>46093.58817870371</v>
       </c>
       <c r="D27" s="8">
-        <v>46093.754866759264</v>
+        <v>46093.58820009259</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3115,13 +3115,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.579292766204</v>
+        <v>46077.41262609954</v>
       </c>
       <c r="C28" s="5">
-        <v>46093.75485412037</v>
+        <v>46093.5881874537</v>
       </c>
       <c r="D28" s="5">
-        <v>46093.75487452546</v>
+        <v>46093.5882078588</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>78</v>
@@ -3180,13 +3180,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.579365196754</v>
+        <v>46077.4126985301</v>
       </c>
       <c r="C29" s="8">
-        <v>46093.754862939815</v>
+        <v>46093.58819627315</v>
       </c>
       <c r="D29" s="8">
-        <v>46093.75488136574</v>
+        <v>46093.58821469908</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>81</v>
@@ -3245,13 +3245,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="5">
-        <v>46139.54271195602</v>
+        <v>46139.37604528935</v>
       </c>
       <c r="C30" s="5">
-        <v>46139.5432959375</v>
+        <v>46139.37662927083</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.548176979166</v>
+        <v>46139.3815103125</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3310,11 +3310,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.699946747685</v>
+        <v>46073.533280081014</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46191.83935533564</v>
+        <v>46191.67268866899</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3357,13 +3357,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.69994704861</v>
+        <v>46073.53328038195</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.839348587964</v>
+        <v>46191.67268192129</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.83935060185</v>
+        <v>46191.67268393519</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3422,13 +3422,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.69994738426</v>
+        <v>46073.53328071759</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.68363072917</v>
+        <v>46182.516964062495</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.68413366898</v>
+        <v>46182.51746700231</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3483,13 +3483,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.69994769676</v>
+        <v>46073.53328103009</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.83755203703</v>
+        <v>46191.670885370375</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.83755358796</v>
+        <v>46191.670886921296</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3544,11 +3544,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.69994803241</v>
+        <v>46073.533281365744</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.65273861111</v>
+        <v>46174.48607194444</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3607,13 +3607,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.699948333335</v>
+        <v>46073.53328166666</v>
       </c>
       <c r="C36" s="5">
-        <v>46174.65273003472</v>
+        <v>46174.48606336805</v>
       </c>
       <c r="D36" s="5">
-        <v>46174.652731724535</v>
+        <v>46174.48606505787</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3668,11 +3668,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.699948622685</v>
+        <v>46073.53328195601</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46174.65273809028</v>
+        <v>46174.48607142361</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3727,13 +3727,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.69994892361</v>
+        <v>46073.53328225695</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.836712743054</v>
+        <v>46191.67004607639</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.83671528935</v>
+        <v>46191.670048622684</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3792,13 +3792,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.699949201386</v>
+        <v>46073.53328253472</v>
       </c>
       <c r="C39" s="8">
-        <v>46174.64929829861</v>
+        <v>46174.482631631945</v>
       </c>
       <c r="D39" s="8">
-        <v>46174.64929997685</v>
+        <v>46174.48263331018</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3853,13 +3853,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.69994585648</v>
+        <v>46073.53327918981</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.67566594908</v>
+        <v>46182.50899928241</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.67566810185</v>
+        <v>46182.50900143519</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3914,13 +3914,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.69994628472</v>
+        <v>46073.53327961806</v>
       </c>
       <c r="C41" s="8">
-        <v>46127.78343253472</v>
+        <v>46127.61676586806</v>
       </c>
       <c r="D41" s="8">
-        <v>46127.78344613426</v>
+        <v>46127.61677946759</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3979,13 +3979,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.69994653935</v>
+        <v>46073.53327987269</v>
       </c>
       <c r="C42" s="5">
-        <v>46120.692551064814</v>
+        <v>46120.52588439814</v>
       </c>
       <c r="D42" s="5">
-        <v>46120.69255305556</v>
+        <v>46120.52588638889</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4040,13 +4040,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.69994680556</v>
+        <v>46073.53328013889</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.783406041664</v>
+        <v>46127.616739375</v>
       </c>
       <c r="D43" s="8">
-        <v>46127.783407256946</v>
+        <v>46127.61674059028</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4101,13 +4101,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.69994707176</v>
+        <v>46073.53328040509</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.78341672454</v>
+        <v>46127.616750057874</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.78341805555</v>
+        <v>46127.616751388894</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4162,13 +4162,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.69994733796</v>
+        <v>46073.5332806713</v>
       </c>
       <c r="C45" s="8">
-        <v>46112.49058179398</v>
+        <v>46112.323915127316</v>
       </c>
       <c r="D45" s="8">
-        <v>46139.54791172454</v>
+        <v>46139.38124505787</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4227,13 +4227,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.69994759259</v>
+        <v>46073.53328092593</v>
       </c>
       <c r="C46" s="5">
-        <v>46104.82754436343</v>
+        <v>46104.66087769676</v>
       </c>
       <c r="D46" s="5">
-        <v>46104.82754626157</v>
+        <v>46104.66087959491</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4288,13 +4288,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.699947870366</v>
+        <v>46073.53328120371</v>
       </c>
       <c r="C47" s="8">
-        <v>46132.57863260417</v>
+        <v>46132.4119659375</v>
       </c>
       <c r="D47" s="8">
-        <v>46132.57863447917</v>
+        <v>46132.4119678125</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4349,13 +4349,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46076.881105196764</v>
+        <v>46076.71443853009</v>
       </c>
       <c r="C48" s="5">
-        <v>46112.48812652778</v>
+        <v>46112.32145986111</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.54788491898</v>
+        <v>46139.38121825231</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4414,13 +4414,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46076.88918239583</v>
+        <v>46076.72251572917</v>
       </c>
       <c r="C49" s="8">
-        <v>46112.49184642361</v>
+        <v>46112.32517975694</v>
       </c>
       <c r="D49" s="8">
-        <v>46112.491848171296</v>
+        <v>46112.325181504624</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4469,13 +4469,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46076.88930991898</v>
+        <v>46076.72264325232</v>
       </c>
       <c r="C50" s="5">
-        <v>46112.50604163195</v>
+        <v>46112.339374965275</v>
       </c>
       <c r="D50" s="5">
-        <v>46112.50608989583</v>
+        <v>46112.33942322917</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4524,13 +4524,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.579487986106</v>
+        <v>46077.41282131945</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.83738681713</v>
+        <v>46191.67072015046</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.83738863426</v>
+        <v>46191.67072196759</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4589,13 +4589,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.5872287963</v>
+        <v>46077.42056212963</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.68337204861</v>
+        <v>46182.516705381946</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.68337341435</v>
+        <v>46182.51670674769</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4644,13 +4644,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.58741234954</v>
+        <v>46077.42074568287</v>
       </c>
       <c r="C53" s="8">
-        <v>46182.69210525463</v>
+        <v>46182.52543858797</v>
       </c>
       <c r="D53" s="8">
-        <v>46182.69210671296</v>
+        <v>46182.525440046295</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -4699,13 +4699,13 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.57954119213</v>
+        <v>46077.412874525464</v>
       </c>
       <c r="C54" s="5">
-        <v>46174.65185637731</v>
+        <v>46174.48518971065</v>
       </c>
       <c r="D54" s="5">
-        <v>46174.6518578588</v>
+        <v>46174.48519119213</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4764,13 +4764,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.587555833336</v>
+        <v>46077.420889166664</v>
       </c>
       <c r="C55" s="8">
-        <v>46094.7587408449</v>
+        <v>46094.59207417824</v>
       </c>
       <c r="D55" s="8">
-        <v>46169.8399244676</v>
+        <v>46169.673257800925</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>110</v>
@@ -4819,13 +4819,13 @@
         <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.5876627199</v>
+        <v>46077.42099605324</v>
       </c>
       <c r="C56" s="5">
-        <v>46174.65173</v>
+        <v>46174.48506333333</v>
       </c>
       <c r="D56" s="5">
-        <v>46174.651731377315</v>
+        <v>46174.48506471065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -4874,13 +4874,13 @@
         <v>197</v>
       </c>
       <c r="B57" s="8">
-        <v>46139.543413900465</v>
+        <v>46139.37674723379</v>
       </c>
       <c r="C57" s="8">
-        <v>46191.840089791665</v>
+        <v>46191.673423125</v>
       </c>
       <c r="D57" s="8">
-        <v>46205.80892784722</v>
+        <v>46205.642261180554</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4939,13 +4939,13 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46139.543700821756</v>
+        <v>46139.37703415509</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.839869421296</v>
+        <v>46191.67320275463</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.83987099537</v>
+        <v>46191.673204328705</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -4994,13 +4994,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46139.54378479166</v>
+        <v>46139.377118125005</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.83995417824</v>
+        <v>46191.67328751157</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.83995613426</v>
+        <v>46191.673289467595</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5049,11 +5049,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46205.80892462963</v>
+        <v>46205.64225796296</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46210.86168509259</v>
+        <v>46210.695018425926</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5100,11 +5100,11 @@
         <v>211</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.69994815972</v>
+        <v>46073.53328149306</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46129.586425601854</v>
+        <v>46129.41975893518</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>212</v>
@@ -5147,13 +5147,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.6999484375</v>
+        <v>46073.53328177083</v>
       </c>
       <c r="C62" s="5">
-        <v>46099.54242106482</v>
+        <v>46099.37575439815</v>
       </c>
       <c r="D62" s="5">
-        <v>46099.54242268519</v>
+        <v>46099.37575601852</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5212,13 +5212,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.699946249995</v>
+        <v>46073.53327958334</v>
       </c>
       <c r="C63" s="8">
-        <v>46129.586253912035</v>
+        <v>46129.41958724537</v>
       </c>
       <c r="D63" s="8">
-        <v>46129.58626813657</v>
+        <v>46129.41960146991</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5277,13 +5277,13 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.494241736116</v>
+        <v>46092.327575069445</v>
       </c>
       <c r="C64" s="5">
-        <v>46129.58641790509</v>
+        <v>46129.41975123843</v>
       </c>
       <c r="D64" s="5">
-        <v>46210.861392569444</v>
+        <v>46210.69472590278</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>115</v>
@@ -5340,11 +5340,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="8">
-        <v>46092.49428590278</v>
+        <v>46092.32761923611</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46154.16811805556</v>
+        <v>46154.00145138889</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>227</v>
@@ -5403,11 +5403,11 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.69994662037</v>
+        <v>46073.5332799537</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46210.858702094905</v>
+        <v>46210.69203542824</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>233</v>
@@ -5450,13 +5450,13 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.69994689815</v>
+        <v>46073.53328023148</v>
       </c>
       <c r="C67" s="8">
-        <v>46210.858693472226</v>
+        <v>46210.692026805555</v>
       </c>
       <c r="D67" s="8">
-        <v>46210.85869597222</v>
+        <v>46210.69202930556</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5515,13 +5515,13 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.69994719907</v>
+        <v>46073.53328053241</v>
       </c>
       <c r="C68" s="5">
-        <v>46206.53745016204</v>
+        <v>46206.37078349537</v>
       </c>
       <c r="D68" s="5">
-        <v>46210.86139240741</v>
+        <v>46210.694725740745</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5580,11 +5580,11 @@
         <v>242</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.699948865746</v>
+        <v>46073.533282199074</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.604225717594</v>
+        <v>46195.43755905093</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>233</v>
@@ -5627,11 +5627,11 @@
         <v>244</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.69995097222</v>
+        <v>46073.53328430555</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.830143969906</v>
+        <v>46199.66347730324</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>245</v>
@@ -5690,11 +5690,11 @@
         <v>247</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.69994640046</v>
+        <v>46073.5332797338</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46121.187778182866</v>
+        <v>46121.0211115162</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>56</v>
@@ -5753,11 +5753,11 @@
         <v>249</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.699946782406</v>
+        <v>46073.53328011574</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46199.82646660879</v>
+        <v>46199.65979994213</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>250</v>
@@ -5816,13 +5816,13 @@
         <v>252</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.69994708333</v>
+        <v>46073.53328041667</v>
       </c>
       <c r="C73" s="8">
-        <v>46195.603957824074</v>
+        <v>46195.4372911574</v>
       </c>
       <c r="D73" s="8">
-        <v>46195.603959687505</v>
+        <v>46195.437293020834</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>253</v>
@@ -5881,13 +5881,13 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46076.88127923611</v>
+        <v>46076.71461256944</v>
       </c>
       <c r="C74" s="5">
-        <v>46195.60421921297</v>
+        <v>46195.4375525463</v>
       </c>
       <c r="D74" s="5">
-        <v>46195.60422127315</v>
+        <v>46195.437554606484</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -5946,13 +5946,13 @@
         <v>258</v>
       </c>
       <c r="B75" s="8">
-        <v>46077.57961084491</v>
+        <v>46077.41294417824</v>
       </c>
       <c r="C75" s="8">
-        <v>46195.60466336805</v>
+        <v>46195.43799670139</v>
       </c>
       <c r="D75" s="8">
-        <v>46195.60466490741</v>
+        <v>46195.43799824074</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>259</v>
@@ -6011,11 +6011,11 @@
         <v>261</v>
       </c>
       <c r="B76" s="5">
-        <v>46077.57965403935</v>
+        <v>46077.412987372685</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46182.692112696765</v>
+        <v>46182.52544603009</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>188</v>
@@ -6074,11 +6074,11 @@
         <v>262</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.69994733796</v>
+        <v>46073.5332806713</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46078.621237141204</v>
+        <v>46078.45457047454</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>263</v>
@@ -6121,11 +6121,11 @@
         <v>265</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.69994759259</v>
+        <v>46073.53328092593</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46210.861684930554</v>
+        <v>46210.69501826389</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>210</v>
@@ -6184,11 +6184,11 @@
         <v>268</v>
       </c>
       <c r="B79" s="8">
-        <v>46073.69994784722</v>
+        <v>46073.53328118056</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.59349042824</v>
+        <v>46198.426823761576</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>
@@ -6247,11 +6247,11 @@
         <v>272</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.69994813658</v>
+        <v>46073.53328146991</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.592367060184</v>
+        <v>46198.42570039352</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>273</v>
@@ -6310,11 +6310,11 @@
         <v>275</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.699948368056</v>
+        <v>46073.533281701384</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46198.59272494213</v>
+        <v>46198.426058275465</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>
@@ -6373,11 +6373,11 @@
         <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46076.88137268518</v>
+        <v>46076.71470601852</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.60422616898</v>
+        <v>46195.437559502316</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>280</v>
@@ -6436,11 +6436,11 @@
         <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.69994864584</v>
+        <v>46073.533281979166</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46153.16811694445</v>
+        <v>46153.00145027778</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>230</v>
@@ -6499,11 +6499,11 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.699948912035</v>
+        <v>46073.53328224537</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46154.16785564815</v>
+        <v>46154.00118898148</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6562,11 +6562,11 @@
         <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46073.69994572917</v>
+        <v>46073.533279062496</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46077.638347245374</v>
+        <v>46077.4716805787</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6609,11 +6609,11 @@
         <v>292</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.699946099536</v>
+        <v>46073.53327943287</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46210.60325569444</v>
+        <v>46210.43658902778</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>293</v>
@@ -6672,11 +6672,11 @@
         <v>297</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.69994638889</v>
+        <v>46073.53327972222</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.604670092594</v>
+        <v>46195.43800342592</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>260</v>
@@ -6735,11 +6735,11 @@
         <v>300</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.69994668981</v>
+        <v>46073.53328002315</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46161.25032122685</v>
+        <v>46161.083654560185</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>301</v>
@@ -6798,11 +6798,11 @@
         <v>305</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.69994695602</v>
+        <v>46073.53328028935</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46162.25040996527</v>
+        <v>46162.083743298615</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>306</v>
@@ -6861,11 +6861,11 @@
         <v>308</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.699947245375</v>
+        <v>46073.533280578704</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46077.6387968287</v>
+        <v>46077.47213016204</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>309</v>
@@ -6908,11 +6908,11 @@
         <v>311</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.699947500005</v>
+        <v>46073.53328083333</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46174.16833755787</v>
+        <v>46174.0016708912</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>312</v>
@@ -6971,11 +6971,11 @@
         <v>315</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.699947789355</v>
+        <v>46073.53328112268</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46174.168340185184</v>
+        <v>46174.00167351852</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>316</v>
@@ -7034,11 +7034,11 @@
         <v>318</v>
       </c>
       <c r="B93" s="8">
-        <v>46092.48971385417</v>
+        <v>46092.3230471875</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46092.497058946756</v>
+        <v>46092.33039228009</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>319</v>
@@ -7087,11 +7087,11 @@
         <v>321</v>
       </c>
       <c r="B94" s="5">
-        <v>46092.49161491898</v>
+        <v>46092.32494825231</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46171.168742951384</v>
+        <v>46171.00207628473</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>322</v>
@@ -7150,11 +7150,11 @@
         <v>324</v>
       </c>
       <c r="B95" s="8">
-        <v>46092.491661747685</v>
+        <v>46092.32499508101</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46181.16820616898</v>
+        <v>46181.001539502315</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>325</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1615,13 +1615,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.53327969907</v>
+        <v>46073.69994636574</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55202717593</v>
+        <v>46092.71869384259</v>
       </c>
       <c r="D4" s="5">
-        <v>46118.61572028935</v>
+        <v>46118.78238695602</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1664,13 +1664,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.53328005787</v>
+        <v>46073.69994672453</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55211712963</v>
+        <v>46092.7187837963</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55213513889</v>
+        <v>46092.71880180556</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1729,13 +1729,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.53328034723</v>
+        <v>46073.69994701388</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55214392361</v>
+        <v>46092.718810590275</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55215846065</v>
+        <v>46092.71882512732</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1794,13 +1794,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.53328063658</v>
+        <v>46073.69994730324</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.552157488426</v>
+        <v>46092.71882415509</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.552175069446</v>
+        <v>46092.71884173611</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1859,13 +1859,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.53328091435</v>
+        <v>46073.699947581015</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55216664352</v>
+        <v>46092.71883331018</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.58784101852</v>
+        <v>46093.75450768518</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1924,13 +1924,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55218392361</v>
+        <v>46092.718850590274</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.552198634265</v>
+        <v>46092.71886530092</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1989,11 +1989,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.53328145834</v>
+        <v>46073.699948124995</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.72635736111</v>
+        <v>46127.89302402778</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2036,13 +2036,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.53328171297</v>
+        <v>46073.699948379624</v>
       </c>
       <c r="C11" s="8">
-        <v>46093.69488967593</v>
+        <v>46093.86155634259</v>
       </c>
       <c r="D11" s="8">
-        <v>46093.694909328704</v>
+        <v>46093.86157599537</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2101,11 +2101,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46134.52718547454</v>
+        <v>46134.69385214121</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2164,13 +2164,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C13" s="8">
-        <v>46093.58815574074</v>
+        <v>46093.75482240741</v>
       </c>
       <c r="D13" s="8">
-        <v>46093.58816989583</v>
+        <v>46093.7548365625</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>60</v>
@@ -2217,13 +2217,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.533279560186</v>
+        <v>46073.69994622685</v>
       </c>
       <c r="C14" s="5">
-        <v>46093.58800283565</v>
+        <v>46093.75466950232</v>
       </c>
       <c r="D14" s="5">
-        <v>46093.58802418981</v>
+        <v>46093.754690856484</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2282,13 +2282,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.53327989583</v>
+        <v>46073.6999465625</v>
       </c>
       <c r="C15" s="8">
-        <v>46093.58801493056</v>
+        <v>46093.754681597224</v>
       </c>
       <c r="D15" s="8">
-        <v>46093.588031527775</v>
+        <v>46093.75469819445</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2347,13 +2347,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.533280185184</v>
+        <v>46073.69994685185</v>
       </c>
       <c r="C16" s="5">
-        <v>46093.58802552083</v>
+        <v>46093.754692187504</v>
       </c>
       <c r="D16" s="5">
-        <v>46093.58804537037</v>
+        <v>46093.75471203704</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2412,13 +2412,13 @@
         <v>73</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.53328045139</v>
+        <v>46073.69994711806</v>
       </c>
       <c r="C17" s="8">
-        <v>46093.58803587963</v>
+        <v>46093.7547025463</v>
       </c>
       <c r="D17" s="8">
-        <v>46093.58805561342</v>
+        <v>46093.75472228009</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>74</v>
@@ -2477,13 +2477,13 @@
         <v>76</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.41097503473</v>
+        <v>46077.577641701384</v>
       </c>
       <c r="C18" s="5">
-        <v>46093.58804545139</v>
+        <v>46093.754712118054</v>
       </c>
       <c r="D18" s="5">
-        <v>46093.588064895834</v>
+        <v>46093.7547315625</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>77</v>
@@ -2542,13 +2542,13 @@
         <v>79</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.41106642361</v>
+        <v>46077.57773309028</v>
       </c>
       <c r="C19" s="8">
-        <v>46093.58805770833</v>
+        <v>46093.754724375</v>
       </c>
       <c r="D19" s="8">
-        <v>46093.588074803236</v>
+        <v>46093.75474146991</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>80</v>
@@ -2607,13 +2607,13 @@
         <v>82</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.53328070602</v>
+        <v>46073.69994737269</v>
       </c>
       <c r="C20" s="5">
-        <v>46093.588138356485</v>
+        <v>46093.75480502315</v>
       </c>
       <c r="D20" s="5">
-        <v>46093.588156875005</v>
+        <v>46093.75482354166</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>83</v>
@@ -2672,13 +2672,13 @@
         <v>86</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.533280972224</v>
+        <v>46073.69994763889</v>
       </c>
       <c r="C21" s="8">
-        <v>46093.70787949074</v>
+        <v>46093.87454615741</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.37611355324</v>
+        <v>46139.54278021991</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>87</v>
@@ -2725,13 +2725,13 @@
         <v>89</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.53328150463</v>
+        <v>46073.6999481713</v>
       </c>
       <c r="C22" s="5">
-        <v>46093.58810327546</v>
+        <v>46093.75476994213</v>
       </c>
       <c r="D22" s="5">
-        <v>46093.58811964121</v>
+        <v>46093.754786307865</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>
@@ -2790,13 +2790,13 @@
         <v>92</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.53328122685</v>
+        <v>46073.69994789352</v>
       </c>
       <c r="C23" s="8">
-        <v>46093.588114375</v>
+        <v>46093.754781041665</v>
       </c>
       <c r="D23" s="8">
-        <v>46093.5881318287</v>
+        <v>46093.75479849537</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>93</v>
@@ -2855,13 +2855,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.533281875</v>
+        <v>46073.69994854167</v>
       </c>
       <c r="C24" s="5">
-        <v>46093.707863171294</v>
+        <v>46093.874529837965</v>
       </c>
       <c r="D24" s="5">
-        <v>46093.707880625</v>
+        <v>46093.87454729166</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2920,13 +2920,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.53328215278</v>
+        <v>46073.69994881944</v>
       </c>
       <c r="C25" s="8">
-        <v>46093.588160694446</v>
+        <v>46093.75482736111</v>
       </c>
       <c r="D25" s="8">
-        <v>46093.5881780787</v>
+        <v>46093.754844745374</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2985,13 +2985,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.53327965278</v>
+        <v>46073.699946319444</v>
       </c>
       <c r="C26" s="5">
-        <v>46093.588169571754</v>
+        <v>46093.754836238426</v>
       </c>
       <c r="D26" s="5">
-        <v>46093.58818924769</v>
+        <v>46093.75485591435</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -3050,13 +3050,13 @@
         <v>104</v>
       </c>
       <c r="B27" s="8">
-        <v>46076.71435710648</v>
+        <v>46076.88102377315</v>
       </c>
       <c r="C27" s="8">
-        <v>46093.58817870371</v>
+        <v>46093.75484537037</v>
       </c>
       <c r="D27" s="8">
-        <v>46093.58820009259</v>
+        <v>46093.754866759264</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>105</v>
@@ -3115,13 +3115,13 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.41262609954</v>
+        <v>46077.579292766204</v>
       </c>
       <c r="C28" s="5">
-        <v>46093.5881874537</v>
+        <v>46093.75485412037</v>
       </c>
       <c r="D28" s="5">
-        <v>46093.5882078588</v>
+        <v>46093.75487452546</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>78</v>
@@ -3180,13 +3180,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46077.4126985301</v>
+        <v>46077.579365196754</v>
       </c>
       <c r="C29" s="8">
-        <v>46093.58819627315</v>
+        <v>46093.754862939815</v>
       </c>
       <c r="D29" s="8">
-        <v>46093.58821469908</v>
+        <v>46093.75488136574</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>81</v>
@@ -3245,13 +3245,13 @@
         <v>111</v>
       </c>
       <c r="B30" s="5">
-        <v>46139.37604528935</v>
+        <v>46139.54271195602</v>
       </c>
       <c r="C30" s="5">
-        <v>46139.37662927083</v>
+        <v>46139.5432959375</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.3815103125</v>
+        <v>46139.548176979166</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3310,11 +3310,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.533280081014</v>
+        <v>46073.699946747685</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46191.67268866899</v>
+        <v>46191.83935533564</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3357,13 +3357,13 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.53328038195</v>
+        <v>46073.69994704861</v>
       </c>
       <c r="C32" s="5">
-        <v>46191.67268192129</v>
+        <v>46191.839348587964</v>
       </c>
       <c r="D32" s="5">
-        <v>46191.67268393519</v>
+        <v>46191.83935060185</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3422,13 +3422,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.53328071759</v>
+        <v>46073.69994738426</v>
       </c>
       <c r="C33" s="8">
-        <v>46182.516964062495</v>
+        <v>46182.68363072917</v>
       </c>
       <c r="D33" s="8">
-        <v>46182.51746700231</v>
+        <v>46182.68413366898</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3483,13 +3483,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.53328103009</v>
+        <v>46073.69994769676</v>
       </c>
       <c r="C34" s="5">
-        <v>46191.670885370375</v>
+        <v>46191.83755203703</v>
       </c>
       <c r="D34" s="5">
-        <v>46191.670886921296</v>
+        <v>46191.83755358796</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3544,11 +3544,11 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.533281365744</v>
+        <v>46073.69994803241</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.48607194444</v>
+        <v>46174.65273861111</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3607,13 +3607,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.53328166666</v>
+        <v>46073.699948333335</v>
       </c>
       <c r="C36" s="5">
-        <v>46174.48606336805</v>
+        <v>46174.65273003472</v>
       </c>
       <c r="D36" s="5">
-        <v>46174.48606505787</v>
+        <v>46174.652731724535</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3668,11 +3668,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.53328195601</v>
+        <v>46073.699948622685</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46174.48607142361</v>
+        <v>46174.65273809028</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3727,13 +3727,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.53328225695</v>
+        <v>46073.69994892361</v>
       </c>
       <c r="C38" s="5">
-        <v>46191.67004607639</v>
+        <v>46191.836712743054</v>
       </c>
       <c r="D38" s="5">
-        <v>46191.670048622684</v>
+        <v>46191.83671528935</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3792,13 +3792,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.53328253472</v>
+        <v>46073.699949201386</v>
       </c>
       <c r="C39" s="8">
-        <v>46174.482631631945</v>
+        <v>46174.64929829861</v>
       </c>
       <c r="D39" s="8">
-        <v>46174.48263331018</v>
+        <v>46174.64929997685</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3853,13 +3853,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.53327918981</v>
+        <v>46073.69994585648</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.50899928241</v>
+        <v>46182.67566594908</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.50900143519</v>
+        <v>46182.67566810185</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3914,13 +3914,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.53327961806</v>
+        <v>46073.69994628472</v>
       </c>
       <c r="C41" s="8">
-        <v>46127.61676586806</v>
+        <v>46127.78343253472</v>
       </c>
       <c r="D41" s="8">
-        <v>46127.61677946759</v>
+        <v>46127.78344613426</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3979,13 +3979,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.53327987269</v>
+        <v>46073.69994653935</v>
       </c>
       <c r="C42" s="5">
-        <v>46120.52588439814</v>
+        <v>46120.692551064814</v>
       </c>
       <c r="D42" s="5">
-        <v>46120.52588638889</v>
+        <v>46120.69255305556</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4040,13 +4040,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.53328013889</v>
+        <v>46073.69994680556</v>
       </c>
       <c r="C43" s="8">
-        <v>46127.616739375</v>
+        <v>46127.783406041664</v>
       </c>
       <c r="D43" s="8">
-        <v>46127.61674059028</v>
+        <v>46127.783407256946</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4101,13 +4101,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46073.53328040509</v>
+        <v>46073.69994707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46127.616750057874</v>
+        <v>46127.78341672454</v>
       </c>
       <c r="D44" s="5">
-        <v>46127.616751388894</v>
+        <v>46127.78341805555</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4162,13 +4162,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C45" s="8">
-        <v>46112.323915127316</v>
+        <v>46112.49058179398</v>
       </c>
       <c r="D45" s="8">
-        <v>46139.38124505787</v>
+        <v>46139.54791172454</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4227,13 +4227,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C46" s="5">
-        <v>46104.66087769676</v>
+        <v>46104.82754436343</v>
       </c>
       <c r="D46" s="5">
-        <v>46104.66087959491</v>
+        <v>46104.82754626157</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4288,13 +4288,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.53328120371</v>
+        <v>46073.699947870366</v>
       </c>
       <c r="C47" s="8">
-        <v>46132.4119659375</v>
+        <v>46132.57863260417</v>
       </c>
       <c r="D47" s="8">
-        <v>46132.4119678125</v>
+        <v>46132.57863447917</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4349,13 +4349,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46076.71443853009</v>
+        <v>46076.881105196764</v>
       </c>
       <c r="C48" s="5">
-        <v>46112.32145986111</v>
+        <v>46112.48812652778</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.38121825231</v>
+        <v>46139.54788491898</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4414,13 +4414,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46076.72251572917</v>
+        <v>46076.88918239583</v>
       </c>
       <c r="C49" s="8">
-        <v>46112.32517975694</v>
+        <v>46112.49184642361</v>
       </c>
       <c r="D49" s="8">
-        <v>46112.325181504624</v>
+        <v>46112.491848171296</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4469,13 +4469,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46076.72264325232</v>
+        <v>46076.88930991898</v>
       </c>
       <c r="C50" s="5">
-        <v>46112.339374965275</v>
+        <v>46112.50604163195</v>
       </c>
       <c r="D50" s="5">
-        <v>46112.33942322917</v>
+        <v>46112.50608989583</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4524,13 +4524,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.41282131945</v>
+        <v>46077.579487986106</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.67072015046</v>
+        <v>46191.83738681713</v>
       </c>
       <c r="D51" s="8">
-        <v>46191.67072196759</v>
+        <v>46191.83738863426</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4589,13 +4589,13 @@
         <v>184</v>
       </c>
       <c r="B52" s="5">
-        <v>46077.42056212963</v>
+        <v>46077.5872287963</v>
       </c>
       <c r="C52" s="5">
-        <v>46182.516705381946</v>
+        <v>46182.68337204861</v>
       </c>
       <c r="D52" s="5">
-        <v>46182.51670674769</v>
+        <v>46182.68337341435</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4644,13 +4644,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46077.42074568287</v>
+        <v>46077.58741234954</v>
       </c>
       <c r="C53" s="8">
-        <v>46182.52543858797</v>
+        <v>46182.69210525463</v>
       </c>
       <c r="D53" s="8">
-        <v>46182.525440046295</v>
+        <v>46182.69210671296</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -4699,13 +4699,13 @@
         <v>189</v>
       </c>
       <c r="B54" s="5">
-        <v>46077.412874525464</v>
+        <v>46077.57954119213</v>
       </c>
       <c r="C54" s="5">
-        <v>46174.48518971065</v>
+        <v>46174.65185637731</v>
       </c>
       <c r="D54" s="5">
-        <v>46174.48519119213</v>
+        <v>46174.6518578588</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4764,13 +4764,13 @@
         <v>192</v>
       </c>
       <c r="B55" s="8">
-        <v>46077.420889166664</v>
+        <v>46077.587555833336</v>
       </c>
       <c r="C55" s="8">
-        <v>46094.59207417824</v>
+        <v>46094.7587408449</v>
       </c>
       <c r="D55" s="8">
-        <v>46169.673257800925</v>
+        <v>46169.8399244676</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>110</v>
@@ -4819,13 +4819,13 @@
         <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46077.42099605324</v>
+        <v>46077.5876627199</v>
       </c>
       <c r="C56" s="5">
-        <v>46174.48506333333</v>
+        <v>46174.65173</v>
       </c>
       <c r="D56" s="5">
-        <v>46174.48506471065</v>
+        <v>46174.651731377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>195</v>
@@ -4874,13 +4874,13 @@
         <v>197</v>
       </c>
       <c r="B57" s="8">
-        <v>46139.37674723379</v>
+        <v>46139.543413900465</v>
       </c>
       <c r="C57" s="8">
-        <v>46191.673423125</v>
+        <v>46191.840089791665</v>
       </c>
       <c r="D57" s="8">
-        <v>46205.642261180554</v>
+        <v>46205.80892784722</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>198</v>
@@ -4939,13 +4939,13 @@
         <v>202</v>
       </c>
       <c r="B58" s="5">
-        <v>46139.37703415509</v>
+        <v>46139.543700821756</v>
       </c>
       <c r="C58" s="5">
-        <v>46191.67320275463</v>
+        <v>46191.839869421296</v>
       </c>
       <c r="D58" s="5">
-        <v>46191.673204328705</v>
+        <v>46191.83987099537</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -4994,13 +4994,13 @@
         <v>204</v>
       </c>
       <c r="B59" s="8">
-        <v>46139.377118125005</v>
+        <v>46139.54378479166</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.67328751157</v>
+        <v>46191.83995417824</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.673289467595</v>
+        <v>46191.83995613426</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>205</v>
@@ -5049,11 +5049,11 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46205.64225796296</v>
+        <v>46205.80892462963</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46210.695018425926</v>
+        <v>46210.86168509259</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5100,11 +5100,11 @@
         <v>211</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.53328149306</v>
+        <v>46073.69994815972</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46129.41975893518</v>
+        <v>46129.586425601854</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>212</v>
@@ -5147,13 +5147,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.53328177083</v>
+        <v>46073.6999484375</v>
       </c>
       <c r="C62" s="5">
-        <v>46099.37575439815</v>
+        <v>46099.54242106482</v>
       </c>
       <c r="D62" s="5">
-        <v>46099.37575601852</v>
+        <v>46099.54242268519</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5212,13 +5212,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.53327958334</v>
+        <v>46073.699946249995</v>
       </c>
       <c r="C63" s="8">
-        <v>46129.41958724537</v>
+        <v>46129.586253912035</v>
       </c>
       <c r="D63" s="8">
-        <v>46129.41960146991</v>
+        <v>46129.58626813657</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>218</v>
@@ -5277,13 +5277,13 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46092.327575069445</v>
+        <v>46092.494241736116</v>
       </c>
       <c r="C64" s="5">
-        <v>46129.41975123843</v>
+        <v>46129.58641790509</v>
       </c>
       <c r="D64" s="5">
-        <v>46210.69472590278</v>
+        <v>46210.861392569444</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>115</v>
@@ -5340,11 +5340,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="8">
-        <v>46092.32761923611</v>
+        <v>46092.49428590278</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46154.00145138889</v>
+        <v>46154.16811805556</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>227</v>
@@ -5403,11 +5403,11 @@
         <v>232</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.5332799537</v>
+        <v>46073.69994662037</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46210.69203542824</v>
+        <v>46210.858702094905</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>233</v>
@@ -5450,13 +5450,13 @@
         <v>235</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.53328023148</v>
+        <v>46073.69994689815</v>
       </c>
       <c r="C67" s="8">
-        <v>46210.692026805555</v>
+        <v>46210.858693472226</v>
       </c>
       <c r="D67" s="8">
-        <v>46210.69202930556</v>
+        <v>46210.85869597222</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>236</v>
@@ -5515,13 +5515,13 @@
         <v>240</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.53328053241</v>
+        <v>46073.69994719907</v>
       </c>
       <c r="C68" s="5">
-        <v>46206.37078349537</v>
+        <v>46206.53745016204</v>
       </c>
       <c r="D68" s="5">
-        <v>46210.694725740745</v>
+        <v>46210.86139240741</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>241</v>
@@ -5580,11 +5580,11 @@
         <v>242</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.533282199074</v>
+        <v>46073.699948865746</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.43755905093</v>
+        <v>46195.604225717594</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>233</v>
@@ -5627,11 +5627,11 @@
         <v>244</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.53328430555</v>
+        <v>46073.69995097222</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.66347730324</v>
+        <v>46199.830143969906</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>245</v>
@@ -5690,11 +5690,11 @@
         <v>247</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.5332797338</v>
+        <v>46073.69994640046</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46121.0211115162</v>
+        <v>46121.187778182866</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>56</v>
@@ -5753,11 +5753,11 @@
         <v>249</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.53328011574</v>
+        <v>46073.699946782406</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46199.65979994213</v>
+        <v>46199.82646660879</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>250</v>
@@ -5816,13 +5816,13 @@
         <v>252</v>
       </c>
       <c r="B73" s="8">
-        <v>46073.53328041667</v>
+        <v>46073.69994708333</v>
       </c>
       <c r="C73" s="8">
-        <v>46195.4372911574</v>
+        <v>46195.603957824074</v>
       </c>
       <c r="D73" s="8">
-        <v>46195.437293020834</v>
+        <v>46195.603959687505</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>253</v>
@@ -5881,13 +5881,13 @@
         <v>255</v>
       </c>
       <c r="B74" s="5">
-        <v>46076.71461256944</v>
+        <v>46076.88127923611</v>
       </c>
       <c r="C74" s="5">
-        <v>46195.4375525463</v>
+        <v>46195.60421921297</v>
       </c>
       <c r="D74" s="5">
-        <v>46195.437554606484</v>
+        <v>46195.60422127315</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>256</v>
@@ -5946,13 +5946,13 @@
         <v>258</v>
       </c>
       <c r="B75" s="8">
-        <v>46077.41294417824</v>
+        <v>46077.57961084491</v>
       </c>
       <c r="C75" s="8">
-        <v>46195.43799670139</v>
+        <v>46195.60466336805</v>
       </c>
       <c r="D75" s="8">
-        <v>46195.43799824074</v>
+        <v>46195.60466490741</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>259</v>
@@ -6011,11 +6011,11 @@
         <v>261</v>
       </c>
       <c r="B76" s="5">
-        <v>46077.412987372685</v>
+        <v>46077.57965403935</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46182.52544603009</v>
+        <v>46182.692112696765</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>188</v>
@@ -6074,11 +6074,11 @@
         <v>262</v>
       </c>
       <c r="B77" s="8">
-        <v>46073.5332806713</v>
+        <v>46073.69994733796</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46078.45457047454</v>
+        <v>46078.621237141204</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>263</v>
@@ -6121,11 +6121,11 @@
         <v>265</v>
       </c>
       <c r="B78" s="5">
-        <v>46073.53328092593</v>
+        <v>46073.69994759259</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46210.69501826389</v>
+        <v>46210.861684930554</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>210</v>
@@ -6184,11 +6184,11 @@
         <v>268</v>
       </c>
       <c r="B79" s="8">
-        <v>46073.53328118056</v>
+        <v>46073.69994784722</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.426823761576</v>
+        <v>46198.59349042824</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>
@@ -6247,11 +6247,11 @@
         <v>272</v>
       </c>
       <c r="B80" s="5">
-        <v>46073.53328146991</v>
+        <v>46073.69994813658</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.42570039352</v>
+        <v>46198.592367060184</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>273</v>
@@ -6310,11 +6310,11 @@
         <v>275</v>
       </c>
       <c r="B81" s="8">
-        <v>46073.533281701384</v>
+        <v>46073.699948368056</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46198.426058275465</v>
+        <v>46198.59272494213</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>
@@ -6373,11 +6373,11 @@
         <v>279</v>
       </c>
       <c r="B82" s="5">
-        <v>46076.71470601852</v>
+        <v>46076.88137268518</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.437559502316</v>
+        <v>46195.60422616898</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>280</v>
@@ -6436,11 +6436,11 @@
         <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46073.533281979166</v>
+        <v>46073.69994864584</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46153.00145027778</v>
+        <v>46153.16811694445</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>230</v>
@@ -6499,11 +6499,11 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46073.53328224537</v>
+        <v>46073.699948912035</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46154.00118898148</v>
+        <v>46154.16785564815</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6562,11 +6562,11 @@
         <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46073.533279062496</v>
+        <v>46073.69994572917</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46077.4716805787</v>
+        <v>46077.638347245374</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6609,11 +6609,11 @@
         <v>292</v>
       </c>
       <c r="B86" s="5">
-        <v>46073.53327943287</v>
+        <v>46073.699946099536</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46210.43658902778</v>
+        <v>46210.60325569444</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>293</v>
@@ -6672,11 +6672,11 @@
         <v>297</v>
       </c>
       <c r="B87" s="8">
-        <v>46073.53327972222</v>
+        <v>46073.69994638889</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.43800342592</v>
+        <v>46195.604670092594</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>260</v>
@@ -6735,11 +6735,11 @@
         <v>300</v>
       </c>
       <c r="B88" s="5">
-        <v>46073.53328002315</v>
+        <v>46073.69994668981</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46161.083654560185</v>
+        <v>46161.25032122685</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>301</v>
@@ -6798,11 +6798,11 @@
         <v>305</v>
       </c>
       <c r="B89" s="8">
-        <v>46073.53328028935</v>
+        <v>46073.69994695602</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46162.083743298615</v>
+        <v>46162.25040996527</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>306</v>
@@ -6861,11 +6861,11 @@
         <v>308</v>
       </c>
       <c r="B90" s="5">
-        <v>46073.533280578704</v>
+        <v>46073.699947245375</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46077.47213016204</v>
+        <v>46077.6387968287</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>309</v>
@@ -6908,11 +6908,11 @@
         <v>311</v>
       </c>
       <c r="B91" s="8">
-        <v>46073.53328083333</v>
+        <v>46073.699947500005</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46174.0016708912</v>
+        <v>46174.16833755787</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>312</v>
@@ -6971,11 +6971,11 @@
         <v>315</v>
       </c>
       <c r="B92" s="5">
-        <v>46073.53328112268</v>
+        <v>46073.699947789355</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46174.00167351852</v>
+        <v>46174.168340185184</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>316</v>
@@ -7034,11 +7034,11 @@
         <v>318</v>
       </c>
       <c r="B93" s="8">
-        <v>46092.3230471875</v>
+        <v>46092.48971385417</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46092.33039228009</v>
+        <v>46092.497058946756</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>319</v>
@@ -7087,11 +7087,11 @@
         <v>321</v>
       </c>
       <c r="B94" s="5">
-        <v>46092.32494825231</v>
+        <v>46092.49161491898</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46171.00207628473</v>
+        <v>46171.168742951384</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>322</v>
@@ -7150,11 +7150,11 @@
         <v>324</v>
       </c>
       <c r="B95" s="8">
-        <v>46092.32499508101</v>
+        <v>46092.491661747685</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46181.001539502315</v>
+        <v>46181.16820616898</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>325</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5053,7 +5053,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46210.86168509259</v>
+        <v>46212.84863678241</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5584,7 +5584,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46195.604225717594</v>
+        <v>46213.56641354167</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>233</v>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.830143969906</v>
+        <v>46213.56641027778</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>245</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46198.59272494213</v>
+        <v>46213.56641375</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="327">
   <si>
     <t xml:space="preserve">50001490-ZITRON PERU METRO DE LIMA PV04-PV05 </t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>Definicion Tecnica de componentes principales</t>
+  </si>
+  <si>
+    <t>ZVR-1-22-90/6 (W22 Carcasa de Hierro Gris) MOTOR (2) 90 KW – 06 POLOS – 380 V -60 HZ- 1000 msnm. Resistente al fuego 250°C / 2 horas Sentido de giro bidireccional Frame: 250 Forma constructiva: B3T Protección: IP55 Refrigeración: TEFC Calentamiento: CLASE B Servicio: S1 Factor de Servicio: 1,15 Rendimiento: IE1 Aislamiento: clase H Arranque: VDF Caja de bornes en el exterior del ventilador Sondas: Sondas de temperatura PTC en los devanados Sondas de temperatura PTC 100 en cojinetes Sonda Stall (anti-bombeo) (Directo e inverso) Sonda de caudal (Directo e inverso) Sonda de vibraciones Sonda de rodamientos PT100 PT100 de temperatura de aire ZVRv-1-22-90/6 (W22 Carcasa de Hierro Gris) MOTOR (2) 90 KW – 06 POLOS – 380 V -60 HZ- 1000 msnm. Resistente al fuego 250°C / 2 horas Sentido de giro bidireccional Frame: 250 Forma constructiva: B3T Protección: IP55.</t>
   </si>
   <si>
     <t>Ingenieria electrica,Ingenieria Basica Motor,Ingenieria Basica Alabes,Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Damper , Ingenieria basica atenuador</t>
@@ -1865,7 +1868,7 @@
         <v>46092.71883331018</v>
       </c>
       <c r="D8" s="5">
-        <v>46093.75450768518</v>
+        <v>46213.75870287037</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1889,7 +1892,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -1901,7 +1904,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q8" s="5">
         <v>45993</v>
@@ -1921,7 +1924,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="8">
         <v>46073.69994784722</v>
@@ -1933,7 +1936,7 @@
         <v>46092.71886530092</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>26</v>
@@ -1986,7 +1989,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="5">
         <v>46073.699948124995</v>
@@ -1996,7 +1999,7 @@
         <v>46127.89302402778</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -2020,7 +2023,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2033,7 +2036,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="8">
         <v>46073.699948379624</v>
@@ -2045,16 +2048,16 @@
         <v>46093.86157599537</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I11" s="8">
         <v>45994</v>
@@ -2072,13 +2075,13 @@
         <v>26</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="8">
         <v>45994</v>
@@ -2098,7 +2101,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="5">
         <v>46073.69994864584</v>
@@ -2108,16 +2111,16 @@
         <v>46134.69385214121</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I12" s="5">
         <v>46121</v>
@@ -2135,13 +2138,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q12" s="5">
         <v>46121</v>
@@ -2156,12 +2159,12 @@
         <v>0</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="8">
         <v>46073.69994892361</v>
@@ -2173,7 +2176,7 @@
         <v>46093.7548365625</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2197,7 +2200,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2214,7 +2217,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46073.69994622685</v>
@@ -2226,16 +2229,16 @@
         <v>46093.754690856484</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" s="5">
         <v>45994</v>
@@ -2253,13 +2256,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q14" s="5">
         <v>45994</v>
@@ -2279,7 +2282,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="8">
         <v>46073.6999465625</v>
@@ -2291,16 +2294,16 @@
         <v>46093.75469819445</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I15" s="8">
         <v>45994</v>
@@ -2318,13 +2321,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q15" s="8">
         <v>45994</v>
@@ -2344,7 +2347,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
         <v>46073.69994685185</v>
@@ -2356,16 +2359,16 @@
         <v>46093.75471203704</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I16" s="5">
         <v>45994</v>
@@ -2383,13 +2386,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q16" s="5">
         <v>45994</v>
@@ -2409,7 +2412,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="8">
         <v>46073.69994711806</v>
@@ -2421,16 +2424,16 @@
         <v>46093.75472228009</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I17" s="8">
         <v>45994</v>
@@ -2448,13 +2451,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="8">
         <v>45994</v>
@@ -2474,7 +2477,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" s="5">
         <v>46077.577641701384</v>
@@ -2486,16 +2489,16 @@
         <v>46093.7547315625</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="5">
         <v>45994</v>
@@ -2513,13 +2516,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>45994</v>
@@ -2539,7 +2542,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8">
         <v>46077.57773309028</v>
@@ -2551,16 +2554,16 @@
         <v>46093.75474146991</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I19" s="8">
         <v>45994</v>
@@ -2578,13 +2581,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="8">
         <v>45994</v>
@@ -2604,7 +2607,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46073.69994737269</v>
@@ -2616,16 +2619,16 @@
         <v>46093.75482354166</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I20" s="5">
         <v>45994</v>
@@ -2643,13 +2646,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>45994</v>
@@ -2669,7 +2672,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" s="8">
         <v>46073.69994763889</v>
@@ -2681,7 +2684,7 @@
         <v>46139.54278021991</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>25</v>
@@ -2705,7 +2708,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P21" s="9" t="s">
         <v>26</v>
@@ -2722,7 +2725,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46073.6999481713</v>
@@ -2734,16 +2737,16 @@
         <v>46093.754786307865</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I22" s="5">
         <v>45996</v>
@@ -2761,13 +2764,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q22" s="5">
         <v>45996</v>
@@ -2787,7 +2790,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="8">
         <v>46073.69994789352</v>
@@ -2799,16 +2802,16 @@
         <v>46093.75479849537</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I23" s="8">
         <v>46003</v>
@@ -2826,13 +2829,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="8">
         <v>46003</v>
@@ -2852,7 +2855,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46073.69994854167</v>
@@ -2864,16 +2867,16 @@
         <v>46093.87454729166</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I24" s="5">
         <v>45999</v>
@@ -2891,13 +2894,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>45999</v>
@@ -2917,7 +2920,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="8">
         <v>46073.69994881944</v>
@@ -2929,16 +2932,16 @@
         <v>46093.754844745374</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I25" s="8">
         <v>46003</v>
@@ -2956,13 +2959,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q25" s="8">
         <v>46003</v>
@@ -2982,7 +2985,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46073.699946319444</v>
@@ -2994,16 +2997,16 @@
         <v>46093.75485591435</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I26" s="5">
         <v>46003</v>
@@ -3021,13 +3024,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q26" s="5">
         <v>46003</v>
@@ -3047,7 +3050,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46076.88102377315</v>
@@ -3059,16 +3062,16 @@
         <v>46093.754866759264</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I27" s="8">
         <v>46003</v>
@@ -3086,13 +3089,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="8">
         <v>46003</v>
@@ -3112,7 +3115,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46077.579292766204</v>
@@ -3124,16 +3127,16 @@
         <v>46093.75487452546</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I28" s="5">
         <v>46003</v>
@@ -3151,13 +3154,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q28" s="5">
         <v>46003</v>
@@ -3177,7 +3180,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46077.579365196754</v>
@@ -3189,16 +3192,16 @@
         <v>46093.75488136574</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I29" s="8">
         <v>46003</v>
@@ -3216,13 +3219,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q29" s="8">
         <v>46003</v>
@@ -3242,7 +3245,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5">
         <v>46139.54271195602</v>
@@ -3254,16 +3257,16 @@
         <v>46139.548176979166</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I30" s="5">
         <v>46136</v>
@@ -3281,13 +3284,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="5">
         <v>46136</v>
@@ -3307,7 +3310,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46073.699946747685</v>
@@ -3317,7 +3320,7 @@
         <v>46191.83935533564</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3341,7 +3344,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3354,7 +3357,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46073.69994704861</v>
@@ -3366,16 +3369,16 @@
         <v>46191.83935060185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I32" s="5">
         <v>46014</v>
@@ -3393,13 +3396,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q32" s="5">
         <v>46014</v>
@@ -3414,12 +3417,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46073.69994738426</v>
@@ -3431,16 +3434,16 @@
         <v>46182.68413366898</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" s="8">
         <v>46014</v>
@@ -3458,29 +3461,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46073.69994769676</v>
@@ -3492,16 +3495,16 @@
         <v>46191.83755358796</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I34" s="5">
         <v>46017</v>
@@ -3519,29 +3522,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46073.69994803241</v>
@@ -3551,16 +3554,16 @@
         <v>46174.65273861111</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I35" s="8">
         <v>46008</v>
@@ -3578,13 +3581,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q35" s="8">
         <v>46008</v>
@@ -3599,12 +3602,12 @@
         <v>0.5</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46073.699948333335</v>
@@ -3616,16 +3619,16 @@
         <v>46174.652731724535</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I36" s="5">
         <v>46008</v>
@@ -3643,29 +3646,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46073.699948622685</v>
@@ -3675,16 +3678,16 @@
         <v>46174.65273809028</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I37" s="8">
         <v>46020</v>
@@ -3702,29 +3705,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46073.69994892361</v>
@@ -3736,16 +3739,16 @@
         <v>46191.83671528935</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I38" s="5">
         <v>46014</v>
@@ -3763,13 +3766,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q38" s="5">
         <v>46014</v>
@@ -3784,12 +3787,12 @@
         <v>0</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46073.699949201386</v>
@@ -3801,16 +3804,16 @@
         <v>46174.64929997685</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I39" s="8">
         <v>46014</v>
@@ -3828,29 +3831,29 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46073.69994585648</v>
@@ -3862,16 +3865,16 @@
         <v>46182.67566810185</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I40" s="5">
         <v>46017</v>
@@ -3889,29 +3892,29 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46073.69994628472</v>
@@ -3923,16 +3926,16 @@
         <v>46127.78344613426</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I41" s="8">
         <v>46000</v>
@@ -3950,13 +3953,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q41" s="8">
         <v>46000</v>
@@ -3965,7 +3968,7 @@
         <v>46147</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3976,7 +3979,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46073.69994653935</v>
@@ -3988,16 +3991,16 @@
         <v>46120.69255305556</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I42" s="5">
         <v>46000</v>
@@ -4015,29 +4018,29 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46073.69994680556</v>
@@ -4049,16 +4052,16 @@
         <v>46127.783407256946</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I43" s="8">
         <v>46020</v>
@@ -4076,29 +4079,29 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
       <c r="S43" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46073.69994707176</v>
@@ -4110,16 +4113,16 @@
         <v>46127.78341805555</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I44" s="5">
         <v>46020</v>
@@ -4137,29 +4140,29 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46073.69994733796</v>
@@ -4171,16 +4174,16 @@
         <v>46139.54791172454</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I45" s="8">
         <v>46014</v>
@@ -4198,13 +4201,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q45" s="8">
         <v>46014</v>
@@ -4224,7 +4227,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46073.69994759259</v>
@@ -4236,16 +4239,16 @@
         <v>46104.82754626157</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46014</v>
@@ -4263,29 +4266,29 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46073.699947870366</v>
@@ -4297,16 +4300,16 @@
         <v>46132.57863447917</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I47" s="8">
         <v>46035</v>
@@ -4324,29 +4327,29 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
       <c r="S47" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46076.881105196764</v>
@@ -4358,16 +4361,16 @@
         <v>46139.54788491898</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I48" s="5">
         <v>46014</v>
@@ -4385,13 +4388,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q48" s="5">
         <v>46014</v>
@@ -4411,7 +4414,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8">
         <v>46076.88918239583</v>
@@ -4423,16 +4426,16 @@
         <v>46112.491848171296</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I49" s="8">
         <v>46014</v>
@@ -4450,13 +4453,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4466,7 +4469,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46076.88930991898</v>
@@ -4478,16 +4481,16 @@
         <v>46112.50608989583</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I50" s="5">
         <v>46043</v>
@@ -4505,13 +4508,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4521,7 +4524,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B51" s="8">
         <v>46077.579487986106</v>
@@ -4533,16 +4536,16 @@
         <v>46191.83738863426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I51" s="8">
         <v>46014</v>
@@ -4560,10 +4563,10 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>26</v>
@@ -4581,12 +4584,12 @@
         <v>0</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B52" s="5">
         <v>46077.5872287963</v>
@@ -4598,16 +4601,16 @@
         <v>46182.68337341435</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I52" s="5">
         <v>46014</v>
@@ -4625,13 +4628,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4641,7 +4644,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46077.58741234954</v>
@@ -4653,16 +4656,16 @@
         <v>46182.69210671296</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I53" s="8">
         <v>46017</v>
@@ -4680,13 +4683,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4696,7 +4699,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5">
         <v>46077.57954119213</v>
@@ -4708,16 +4711,16 @@
         <v>46174.6518578588</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I54" s="5">
         <v>46014</v>
@@ -4735,10 +4738,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4756,12 +4759,12 @@
         <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46077.587555833336</v>
@@ -4773,16 +4776,16 @@
         <v>46169.8399244676</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I55" s="8">
         <v>46014</v>
@@ -4800,13 +4803,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4816,7 +4819,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46077.5876627199</v>
@@ -4828,16 +4831,16 @@
         <v>46174.651731377315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I56" s="5">
         <v>46017</v>
@@ -4855,13 +4858,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4871,7 +4874,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46139.543413900465</v>
@@ -4883,16 +4886,16 @@
         <v>46205.80892784722</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I57" s="8">
         <v>46139</v>
@@ -4910,10 +4913,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4925,18 +4928,18 @@
         <v>46177</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46139.543700821756</v>
@@ -4948,16 +4951,16 @@
         <v>46191.83987099537</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46139</v>
@@ -4975,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4991,7 +4994,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>46139.54378479166</v>
@@ -5003,16 +5006,16 @@
         <v>46191.83995613426</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I59" s="8">
         <v>46149</v>
@@ -5030,10 +5033,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5046,7 +5049,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B60" s="5">
         <v>46205.80892462963</v>
@@ -5056,16 +5059,16 @@
         <v>46212.84863678241</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5081,13 +5084,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5097,7 +5100,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46073.69994815972</v>
@@ -5107,7 +5110,7 @@
         <v>46129.586425601854</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5131,7 +5134,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5144,7 +5147,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46073.6999484375</v>
@@ -5156,16 +5159,16 @@
         <v>46099.54242268519</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I62" s="5">
         <v>46003</v>
@@ -5183,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q62" s="5">
         <v>46003</v>
@@ -5209,7 +5212,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46073.699946249995</v>
@@ -5221,16 +5224,16 @@
         <v>46129.58626813657</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I63" s="8">
         <v>46058</v>
@@ -5248,13 +5251,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q63" s="8">
         <v>46058</v>
@@ -5274,7 +5277,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46092.494241736116</v>
@@ -5286,16 +5289,16 @@
         <v>46210.861392569444</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5311,13 +5314,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="5">
         <v>46065</v>
@@ -5337,7 +5340,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46092.49428590278</v>
@@ -5347,16 +5350,16 @@
         <v>46154.16811805556</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I65" s="8">
         <v>46154</v>
@@ -5374,13 +5377,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="8">
         <v>46154</v>
@@ -5389,18 +5392,18 @@
         <v>46154</v>
       </c>
       <c r="S65" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46073.69994662037</v>
@@ -5410,7 +5413,7 @@
         <v>46210.858702094905</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5434,7 +5437,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5447,7 +5450,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B67" s="8">
         <v>46073.69994689815</v>
@@ -5459,16 +5462,16 @@
         <v>46210.85869597222</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I67" s="8">
         <v>46063</v>
@@ -5486,13 +5489,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q67" s="8">
         <v>46063</v>
@@ -5507,12 +5510,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46073.69994719907</v>
@@ -5524,16 +5527,16 @@
         <v>46210.86139240741</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46065</v>
@@ -5551,13 +5554,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="5">
         <v>46065</v>
@@ -5572,12 +5575,12 @@
         <v>0</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B69" s="8">
         <v>46073.699948865746</v>
@@ -5587,7 +5590,7 @@
         <v>46213.56641354167</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5611,7 +5614,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5624,7 +5627,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B70" s="5">
         <v>46073.69995097222</v>
@@ -5634,16 +5637,16 @@
         <v>46213.56641027778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I70" s="5">
         <v>46097</v>
@@ -5661,13 +5664,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q70" s="5">
         <v>46097</v>
@@ -5682,12 +5685,12 @@
         <v>0</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B71" s="8">
         <v>46073.69994640046</v>
@@ -5697,16 +5700,16 @@
         <v>46121.187778182866</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I71" s="8">
         <v>46119</v>
@@ -5724,13 +5727,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q71" s="8">
         <v>46119</v>
@@ -5745,12 +5748,12 @@
         <v>0</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B72" s="5">
         <v>46073.699946782406</v>
@@ -5760,16 +5763,16 @@
         <v>46199.82646660879</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I72" s="5">
         <v>46132</v>
@@ -5787,13 +5790,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q72" s="5">
         <v>46132</v>
@@ -5808,12 +5811,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B73" s="8">
         <v>46073.69994708333</v>
@@ -5825,16 +5828,16 @@
         <v>46195.603959687505</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I73" s="8">
         <v>46147</v>
@@ -5852,13 +5855,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q73" s="8">
         <v>46147</v>
@@ -5867,18 +5870,18 @@
         <v>46148</v>
       </c>
       <c r="S73" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T73" s="9">
         <v>0</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B74" s="5">
         <v>46076.88127923611</v>
@@ -5890,16 +5893,16 @@
         <v>46195.60422127315</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I74" s="5">
         <v>46121</v>
@@ -5917,13 +5920,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46121</v>
@@ -5938,12 +5941,12 @@
         <v>0</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B75" s="8">
         <v>46077.57961084491</v>
@@ -5955,16 +5958,16 @@
         <v>46195.60466490741</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I75" s="8">
         <v>46104</v>
@@ -5982,13 +5985,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q75" s="8">
         <v>46104</v>
@@ -6003,12 +6006,12 @@
         <v>0</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46077.57965403935</v>
@@ -6018,16 +6021,16 @@
         <v>46182.692112696765</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I76" s="5">
         <v>46098</v>
@@ -6045,13 +6048,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q76" s="5">
         <v>46098</v>
@@ -6066,12 +6069,12 @@
         <v>0</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B77" s="8">
         <v>46073.69994733796</v>
@@ -6081,7 +6084,7 @@
         <v>46078.621237141204</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6105,7 +6108,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6118,7 +6121,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B78" s="5">
         <v>46073.69994759259</v>
@@ -6128,16 +6131,16 @@
         <v>46210.861684930554</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I78" s="5">
         <v>46111</v>
@@ -6155,13 +6158,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q78" s="5">
         <v>46111</v>
@@ -6176,12 +6179,12 @@
         <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B79" s="8">
         <v>46073.69994784722</v>
@@ -6191,16 +6194,16 @@
         <v>46198.59349042824</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I79" s="8">
         <v>46149</v>
@@ -6218,13 +6221,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q79" s="8">
         <v>46149</v>
@@ -6233,18 +6236,18 @@
         <v>46150</v>
       </c>
       <c r="S79" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T79" s="9">
         <v>0</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B80" s="5">
         <v>46073.69994813658</v>
@@ -6254,16 +6257,16 @@
         <v>46198.592367060184</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I80" s="5">
         <v>46134</v>
@@ -6281,13 +6284,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q80" s="5">
         <v>46134</v>
@@ -6302,12 +6305,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="8">
         <v>46073.699948368056</v>
@@ -6317,16 +6320,16 @@
         <v>46213.56641375</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I81" s="8">
         <v>46136</v>
@@ -6344,13 +6347,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q81" s="8">
         <v>46136</v>
@@ -6359,18 +6362,18 @@
         <v>46139</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="T81" s="9">
         <v>0.5</v>
       </c>
       <c r="U81" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="5">
         <v>46076.88137268518</v>
@@ -6380,16 +6383,16 @@
         <v>46195.60422616898</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I82" s="5">
         <v>46129</v>
@@ -6407,13 +6410,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q82" s="5">
         <v>46129</v>
@@ -6428,12 +6431,12 @@
         <v>0</v>
       </c>
       <c r="U82" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B83" s="8">
         <v>46073.69994864584</v>
@@ -6443,16 +6446,16 @@
         <v>46153.16811694445</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I83" s="8">
         <v>46153</v>
@@ -6470,13 +6473,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q83" s="8">
         <v>46153</v>
@@ -6485,18 +6488,18 @@
         <v>46153</v>
       </c>
       <c r="S83" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T83" s="9">
         <v>0</v>
       </c>
       <c r="U83" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B84" s="5">
         <v>46073.699948912035</v>
@@ -6506,16 +6509,16 @@
         <v>46154.16785564815</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I84" s="5">
         <v>46154</v>
@@ -6533,13 +6536,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q84" s="5">
         <v>46154</v>
@@ -6548,18 +6551,18 @@
         <v>46154</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B85" s="8">
         <v>46073.69994572917</v>
@@ -6569,7 +6572,7 @@
         <v>46077.638347245374</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6593,7 +6596,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6606,7 +6609,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B86" s="5">
         <v>46073.699946099536</v>
@@ -6616,16 +6619,16 @@
         <v>46210.60325569444</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I86" s="5">
         <v>46155</v>
@@ -6643,13 +6646,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q86" s="5">
         <v>46155</v>
@@ -6658,18 +6661,18 @@
         <v>46155</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B87" s="8">
         <v>46073.69994638889</v>
@@ -6679,16 +6682,16 @@
         <v>46195.604670092594</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I87" s="8">
         <v>46156</v>
@@ -6706,13 +6709,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q87" s="8">
         <v>46156</v>
@@ -6721,18 +6724,18 @@
         <v>46160</v>
       </c>
       <c r="S87" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
       </c>
       <c r="U87" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B88" s="5">
         <v>46073.69994668981</v>
@@ -6742,16 +6745,16 @@
         <v>46161.25032122685</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I88" s="5">
         <v>46161</v>
@@ -6769,13 +6772,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q88" s="5">
         <v>46161</v>
@@ -6784,18 +6787,18 @@
         <v>46161</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B89" s="8">
         <v>46073.69994695602</v>
@@ -6805,16 +6808,16 @@
         <v>46162.25040996527</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I89" s="8">
         <v>46162</v>
@@ -6832,13 +6835,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q89" s="8">
         <v>46162</v>
@@ -6847,18 +6850,18 @@
         <v>46162</v>
       </c>
       <c r="S89" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
       </c>
       <c r="U89" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B90" s="5">
         <v>46073.699947245375</v>
@@ -6868,7 +6871,7 @@
         <v>46077.6387968287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6892,7 +6895,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6905,7 +6908,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B91" s="8">
         <v>46073.699947500005</v>
@@ -6915,16 +6918,16 @@
         <v>46174.16833755787</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I91" s="8">
         <v>46164</v>
@@ -6942,13 +6945,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q91" s="8">
         <v>46164</v>
@@ -6957,18 +6960,18 @@
         <v>46174</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
       </c>
       <c r="U91" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B92" s="5">
         <v>46073.699947789355</v>
@@ -6978,16 +6981,16 @@
         <v>46174.168340185184</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I92" s="5">
         <v>46164</v>
@@ -7005,13 +7008,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q92" s="5">
         <v>46164</v>
@@ -7020,18 +7023,18 @@
         <v>46174</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T92" s="6">
         <v>0</v>
       </c>
       <c r="U92" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B93" s="8">
         <v>46092.48971385417</v>
@@ -7041,7 +7044,7 @@
         <v>46092.497058946756</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -7065,7 +7068,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>26</v>
@@ -7073,18 +7076,18 @@
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
       <c r="S93" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T93" s="9">
         <v>0</v>
       </c>
       <c r="U93" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B94" s="5">
         <v>46092.49161491898</v>
@@ -7094,16 +7097,16 @@
         <v>46171.168742951384</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I94" s="5">
         <v>46164</v>
@@ -7121,13 +7124,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q94" s="5">
         <v>46164</v>
@@ -7136,18 +7139,18 @@
         <v>46171</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B95" s="8">
         <v>46092.491661747685</v>
@@ -7157,16 +7160,16 @@
         <v>46181.16820616898</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I95" s="8">
         <v>46174</v>
@@ -7184,13 +7187,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q95" s="8">
         <v>46174</v>
@@ -7199,13 +7202,13 @@
         <v>46181</v>
       </c>
       <c r="S95" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T95" s="9">
         <v>0</v>
       </c>
       <c r="U95" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46212.84863678241</v>
+        <v>46213.85753734954</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>208</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46174.65273861111</v>
+        <v>46217.58160621527</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46213.85753734954</v>
+        <v>46217.57588326389</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>208</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46217.58160621527</v>
+        <v>46218.59376659722</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>134</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46217.57588326389</v>
+        <v>46218.58775554398</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>208</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="324">
   <si>
     <t xml:space="preserve">50001490-ZITRON PERU METRO DE LIMA PV04-PV05 </t>
   </si>
@@ -355,12 +355,6 @@
     <t xml:space="preserve">Propuesta Fabricacion externa </t>
   </si>
   <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
     <t>Check Planos</t>
   </si>
   <si>
@@ -812,9 +806,6 @@
   </si>
   <si>
     <t>1213380177588315</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
   </si>
   <si>
     <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:,Montaje Sensor</t>
@@ -3263,11 +3254,9 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>115</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H30" s="6"/>
       <c r="I30" s="5">
         <v>46136</v>
       </c>
@@ -3287,10 +3276,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="5">
         <v>46136</v>
@@ -3310,7 +3299,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46073.699946747685</v>
@@ -3320,7 +3309,7 @@
         <v>46191.83935533564</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3344,7 +3333,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3357,7 +3346,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B32" s="5">
         <v>46073.69994704861</v>
@@ -3369,16 +3358,16 @@
         <v>46191.83935060185</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I32" s="5">
         <v>46014</v>
@@ -3396,13 +3385,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q32" s="5">
         <v>46014</v>
@@ -3422,7 +3411,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46073.69994738426</v>
@@ -3434,16 +3423,16 @@
         <v>46182.68413366898</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I33" s="8">
         <v>46014</v>
@@ -3461,18 +3450,18 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>94</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
@@ -3483,7 +3472,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46073.69994769676</v>
@@ -3495,16 +3484,16 @@
         <v>46191.83755358796</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I34" s="5">
         <v>46017</v>
@@ -3522,18 +3511,18 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3544,7 +3533,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46073.69994803241</v>
@@ -3554,16 +3543,16 @@
         <v>46218.59376659722</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I35" s="8">
         <v>46008</v>
@@ -3581,13 +3570,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q35" s="8">
         <v>46008</v>
@@ -3607,7 +3596,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46073.699948333335</v>
@@ -3619,16 +3608,16 @@
         <v>46174.652731724535</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I36" s="5">
         <v>46008</v>
@@ -3646,18 +3635,18 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3668,7 +3657,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46073.699948622685</v>
@@ -3678,16 +3667,16 @@
         <v>46174.65273809028</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I37" s="8">
         <v>46020</v>
@@ -3705,18 +3694,18 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
@@ -3727,7 +3716,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46073.69994892361</v>
@@ -3739,16 +3728,16 @@
         <v>46191.83671528935</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I38" s="5">
         <v>46014</v>
@@ -3766,13 +3755,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q38" s="5">
         <v>46014</v>
@@ -3792,7 +3781,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46073.699949201386</v>
@@ -3804,16 +3793,16 @@
         <v>46174.64929997685</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I39" s="8">
         <v>46014</v>
@@ -3831,18 +3820,18 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>100</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
@@ -3853,7 +3842,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46073.69994585648</v>
@@ -3865,16 +3854,16 @@
         <v>46182.67566810185</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I40" s="5">
         <v>46017</v>
@@ -3892,18 +3881,18 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
@@ -3914,7 +3903,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46073.69994628472</v>
@@ -3926,16 +3915,16 @@
         <v>46127.78344613426</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I41" s="8">
         <v>46000</v>
@@ -3953,13 +3942,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q41" s="8">
         <v>46000</v>
@@ -3968,7 +3957,7 @@
         <v>46147</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3979,7 +3968,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46073.69994653935</v>
@@ -3991,16 +3980,16 @@
         <v>46120.69255305556</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I42" s="5">
         <v>46000</v>
@@ -4018,18 +4007,18 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
@@ -4040,7 +4029,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46073.69994680556</v>
@@ -4052,16 +4041,16 @@
         <v>46127.783407256946</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I43" s="8">
         <v>46020</v>
@@ -4079,18 +4068,18 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
       <c r="S43" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
@@ -4101,7 +4090,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46073.69994707176</v>
@@ -4113,16 +4102,16 @@
         <v>46127.78341805555</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I44" s="5">
         <v>46020</v>
@@ -4140,18 +4129,18 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -4162,7 +4151,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B45" s="8">
         <v>46073.69994733796</v>
@@ -4174,16 +4163,16 @@
         <v>46139.54791172454</v>
       </c>
       <c r="E45" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I45" s="8">
         <v>46014</v>
@@ -4201,13 +4190,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q45" s="8">
         <v>46014</v>
@@ -4227,7 +4216,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46073.69994759259</v>
@@ -4239,16 +4228,16 @@
         <v>46104.82754626157</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I46" s="5">
         <v>46014</v>
@@ -4266,18 +4255,18 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4288,7 +4277,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46073.699947870366</v>
@@ -4300,16 +4289,16 @@
         <v>46132.57863447917</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I47" s="8">
         <v>46035</v>
@@ -4327,18 +4316,18 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
       <c r="S47" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4349,7 +4338,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46076.881105196764</v>
@@ -4361,16 +4350,16 @@
         <v>46139.54788491898</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I48" s="5">
         <v>46014</v>
@@ -4388,13 +4377,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q48" s="5">
         <v>46014</v>
@@ -4414,7 +4403,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46076.88918239583</v>
@@ -4426,16 +4415,16 @@
         <v>46112.491848171296</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I49" s="8">
         <v>46014</v>
@@ -4453,13 +4442,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>106</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4469,7 +4458,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B50" s="5">
         <v>46076.88930991898</v>
@@ -4481,16 +4470,16 @@
         <v>46112.50608989583</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I50" s="5">
         <v>46043</v>
@@ -4508,13 +4497,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4524,7 +4513,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B51" s="8">
         <v>46077.579487986106</v>
@@ -4536,16 +4525,16 @@
         <v>46191.83738863426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I51" s="8">
         <v>46014</v>
@@ -4563,7 +4552,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>109</v>
@@ -4589,7 +4578,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B52" s="5">
         <v>46077.5872287963</v>
@@ -4607,10 +4596,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I52" s="5">
         <v>46014</v>
@@ -4628,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4644,7 +4633,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46077.58741234954</v>
@@ -4656,16 +4645,16 @@
         <v>46182.69210671296</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I53" s="8">
         <v>46017</v>
@@ -4683,13 +4672,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>109</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4699,7 +4688,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46077.57954119213</v>
@@ -4711,16 +4700,16 @@
         <v>46174.6518578588</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I54" s="5">
         <v>46014</v>
@@ -4738,10 +4727,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4764,7 +4753,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46077.587555833336</v>
@@ -4782,10 +4771,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I55" s="8">
         <v>46014</v>
@@ -4803,13 +4792,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4819,7 +4808,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46077.5876627199</v>
@@ -4831,16 +4820,16 @@
         <v>46174.651731377315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I56" s="5">
         <v>46017</v>
@@ -4858,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4874,7 +4863,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B57" s="8">
         <v>46139.543413900465</v>
@@ -4886,16 +4875,16 @@
         <v>46205.80892784722</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="I57" s="8">
         <v>46139</v>
@@ -4913,10 +4902,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4928,18 +4917,18 @@
         <v>46177</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46139.543700821756</v>
@@ -4951,16 +4940,16 @@
         <v>46191.83987099537</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I58" s="5">
         <v>46139</v>
@@ -4978,13 +4967,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4994,7 +4983,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46139.54378479166</v>
@@ -5006,16 +4995,16 @@
         <v>46191.83995613426</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I59" s="8">
         <v>46149</v>
@@ -5033,10 +5022,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5049,7 +5038,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46205.80892462963</v>
@@ -5059,16 +5048,16 @@
         <v>46218.58775554398</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5084,13 +5073,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5100,7 +5089,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B61" s="8">
         <v>46073.69994815972</v>
@@ -5110,7 +5099,7 @@
         <v>46129.586425601854</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5134,7 +5123,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5147,7 +5136,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
         <v>46073.6999484375</v>
@@ -5159,16 +5148,16 @@
         <v>46099.54242268519</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="I62" s="5">
         <v>46003</v>
@@ -5186,13 +5175,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q62" s="5">
         <v>46003</v>
@@ -5212,7 +5201,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B63" s="8">
         <v>46073.699946249995</v>
@@ -5224,16 +5213,16 @@
         <v>46129.58626813657</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>221</v>
-      </c>
       <c r="H63" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46058</v>
@@ -5251,13 +5240,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Q63" s="8">
         <v>46058</v>
@@ -5277,7 +5266,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46092.494241736116</v>
@@ -5289,16 +5278,16 @@
         <v>46210.861392569444</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5314,13 +5303,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="5">
         <v>46065</v>
@@ -5340,7 +5329,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46092.49428590278</v>
@@ -5350,16 +5339,16 @@
         <v>46154.16811805556</v>
       </c>
       <c r="E65" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="I65" s="8">
         <v>46154</v>
@@ -5377,13 +5366,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="8">
         <v>46154</v>
@@ -5392,7 +5381,7 @@
         <v>46154</v>
       </c>
       <c r="S65" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
@@ -5403,7 +5392,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46073.69994662037</v>
@@ -5413,7 +5402,7 @@
         <v>46210.858702094905</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5437,7 +5426,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5450,7 +5439,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B67" s="8">
         <v>46073.69994689815</v>
@@ -5462,16 +5451,16 @@
         <v>46210.85869597222</v>
       </c>
       <c r="E67" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>239</v>
       </c>
       <c r="I67" s="8">
         <v>46063</v>
@@ -5489,13 +5478,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q67" s="8">
         <v>46063</v>
@@ -5510,12 +5499,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B68" s="5">
         <v>46073.69994719907</v>
@@ -5527,16 +5516,16 @@
         <v>46210.86139240741</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I68" s="5">
         <v>46065</v>
@@ -5554,13 +5543,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="5">
         <v>46065</v>
@@ -5580,7 +5569,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B69" s="8">
         <v>46073.699948865746</v>
@@ -5590,7 +5579,7 @@
         <v>46213.56641354167</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5614,7 +5603,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5627,7 +5616,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B70" s="5">
         <v>46073.69995097222</v>
@@ -5637,16 +5626,16 @@
         <v>46213.56641027778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46097</v>
@@ -5664,13 +5653,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Q70" s="5">
         <v>46097</v>
@@ -5690,7 +5679,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B71" s="8">
         <v>46073.69994640046</v>
@@ -5706,10 +5695,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I71" s="8">
         <v>46119</v>
@@ -5727,13 +5716,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q71" s="8">
         <v>46119</v>
@@ -5753,7 +5742,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B72" s="5">
         <v>46073.699946782406</v>
@@ -5763,16 +5752,16 @@
         <v>46199.82646660879</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I72" s="5">
         <v>46132</v>
@@ -5790,13 +5779,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="Q72" s="5">
         <v>46132</v>
@@ -5816,7 +5805,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B73" s="8">
         <v>46073.69994708333</v>
@@ -5828,16 +5817,16 @@
         <v>46195.603959687505</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I73" s="8">
         <v>46147</v>
@@ -5855,13 +5844,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q73" s="8">
         <v>46147</v>
@@ -5870,18 +5859,18 @@
         <v>46148</v>
       </c>
       <c r="S73" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T73" s="9">
         <v>0</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B74" s="5">
         <v>46076.88127923611</v>
@@ -5893,16 +5882,16 @@
         <v>46195.60422127315</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I74" s="5">
         <v>46121</v>
@@ -5920,13 +5909,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q74" s="5">
         <v>46121</v>
@@ -5941,12 +5930,12 @@
         <v>0</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B75" s="8">
         <v>46077.57961084491</v>
@@ -5958,16 +5947,16 @@
         <v>46195.60466490741</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I75" s="8">
         <v>46104</v>
@@ -5985,13 +5974,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q75" s="8">
         <v>46104</v>
@@ -6011,7 +6000,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B76" s="5">
         <v>46077.57965403935</v>
@@ -6021,16 +6010,16 @@
         <v>46182.692112696765</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I76" s="5">
         <v>46098</v>
@@ -6048,13 +6037,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Q76" s="5">
         <v>46098</v>
@@ -6074,7 +6063,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B77" s="8">
         <v>46073.69994733796</v>
@@ -6084,7 +6073,7 @@
         <v>46078.621237141204</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6108,7 +6097,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6121,7 +6110,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B78" s="5">
         <v>46073.69994759259</v>
@@ -6131,17 +6120,15 @@
         <v>46210.861684930554</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>267</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H78" s="6"/>
       <c r="I78" s="5">
         <v>46111</v>
       </c>
@@ -6158,13 +6145,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Q78" s="5">
         <v>46111</v>
@@ -6184,7 +6171,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B79" s="8">
         <v>46073.69994784722</v>
@@ -6194,17 +6181,15 @@
         <v>46198.59349042824</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>267</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="9"/>
       <c r="I79" s="8">
         <v>46149</v>
       </c>
@@ -6221,13 +6206,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q79" s="8">
         <v>46149</v>
@@ -6236,7 +6221,7 @@
         <v>46150</v>
       </c>
       <c r="S79" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T79" s="9">
         <v>0</v>
@@ -6247,7 +6232,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B80" s="5">
         <v>46073.69994813658</v>
@@ -6257,17 +6242,15 @@
         <v>46198.592367060184</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>267</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
       <c r="I80" s="5">
         <v>46134</v>
       </c>
@@ -6284,13 +6267,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q80" s="5">
         <v>46134</v>
@@ -6310,7 +6293,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B81" s="8">
         <v>46073.699948368056</v>
@@ -6320,17 +6303,15 @@
         <v>46213.56641375</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>267</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H81" s="9"/>
       <c r="I81" s="8">
         <v>46136</v>
       </c>
@@ -6347,13 +6328,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q81" s="8">
         <v>46136</v>
@@ -6362,7 +6343,7 @@
         <v>46139</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="T81" s="9">
         <v>0.5</v>
@@ -6373,7 +6354,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B82" s="5">
         <v>46076.88137268518</v>
@@ -6383,17 +6364,15 @@
         <v>46195.60422616898</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>267</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="5">
         <v>46129</v>
       </c>
@@ -6410,13 +6389,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Q82" s="5">
         <v>46129</v>
@@ -6436,7 +6415,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46073.69994864584</v>
@@ -6446,17 +6425,15 @@
         <v>46153.16811694445</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>267</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="9"/>
       <c r="I83" s="8">
         <v>46153</v>
       </c>
@@ -6473,13 +6450,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="Q83" s="8">
         <v>46153</v>
@@ -6488,7 +6465,7 @@
         <v>46153</v>
       </c>
       <c r="S83" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T83" s="9">
         <v>0</v>
@@ -6499,7 +6476,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46073.699948912035</v>
@@ -6509,17 +6486,15 @@
         <v>46154.16785564815</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>267</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
       <c r="I84" s="5">
         <v>46154</v>
       </c>
@@ -6536,13 +6511,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="Q84" s="5">
         <v>46154</v>
@@ -6551,7 +6526,7 @@
         <v>46154</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6562,7 +6537,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B85" s="8">
         <v>46073.69994572917</v>
@@ -6572,7 +6547,7 @@
         <v>46077.638347245374</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6596,7 +6571,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6609,7 +6584,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B86" s="5">
         <v>46073.699946099536</v>
@@ -6619,16 +6594,16 @@
         <v>46210.60325569444</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I86" s="5">
         <v>46155</v>
@@ -6646,13 +6621,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Q86" s="5">
         <v>46155</v>
@@ -6661,7 +6636,7 @@
         <v>46155</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6672,7 +6647,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B87" s="8">
         <v>46073.69994638889</v>
@@ -6682,17 +6657,15 @@
         <v>46195.604670092594</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>267</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="9"/>
       <c r="I87" s="8">
         <v>46156</v>
       </c>
@@ -6709,13 +6682,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Q87" s="8">
         <v>46156</v>
@@ -6724,7 +6697,7 @@
         <v>46160</v>
       </c>
       <c r="S87" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
@@ -6735,7 +6708,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B88" s="5">
         <v>46073.69994668981</v>
@@ -6745,16 +6718,16 @@
         <v>46161.25032122685</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I88" s="5">
         <v>46161</v>
@@ -6772,13 +6745,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="Q88" s="5">
         <v>46161</v>
@@ -6787,7 +6760,7 @@
         <v>46161</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6798,7 +6771,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B89" s="8">
         <v>46073.69994695602</v>
@@ -6808,16 +6781,16 @@
         <v>46162.25040996527</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="I89" s="8">
         <v>46162</v>
@@ -6835,13 +6808,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q89" s="8">
         <v>46162</v>
@@ -6850,7 +6823,7 @@
         <v>46162</v>
       </c>
       <c r="S89" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
@@ -6861,7 +6834,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B90" s="5">
         <v>46073.699947245375</v>
@@ -6871,7 +6844,7 @@
         <v>46077.6387968287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6895,7 +6868,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6908,7 +6881,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B91" s="8">
         <v>46073.699947500005</v>
@@ -6918,16 +6891,16 @@
         <v>46174.16833755787</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I91" s="8">
         <v>46164</v>
@@ -6945,13 +6918,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O91" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="P91" s="9" t="s">
         <v>307</v>
-      </c>
-      <c r="P91" s="9" t="s">
-        <v>310</v>
       </c>
       <c r="Q91" s="8">
         <v>46164</v>
@@ -6960,7 +6933,7 @@
         <v>46174</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -6971,7 +6944,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B92" s="5">
         <v>46073.699947789355</v>
@@ -6981,16 +6954,16 @@
         <v>46174.168340185184</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I92" s="5">
         <v>46164</v>
@@ -7008,13 +6981,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Q92" s="5">
         <v>46164</v>
@@ -7023,7 +6996,7 @@
         <v>46174</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T92" s="6">
         <v>0</v>
@@ -7034,7 +7007,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B93" s="8">
         <v>46092.48971385417</v>
@@ -7044,7 +7017,7 @@
         <v>46092.497058946756</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -7068,7 +7041,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>26</v>
@@ -7076,7 +7049,7 @@
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
       <c r="S93" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T93" s="9">
         <v>0</v>
@@ -7087,7 +7060,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B94" s="5">
         <v>46092.49161491898</v>
@@ -7097,7 +7070,7 @@
         <v>46171.168742951384</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7124,13 +7097,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Q94" s="5">
         <v>46164</v>
@@ -7139,7 +7112,7 @@
         <v>46171</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7150,7 +7123,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B95" s="8">
         <v>46092.491661747685</v>
@@ -7160,7 +7133,7 @@
         <v>46181.16820616898</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7187,13 +7160,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="O95" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="O95" s="9" t="s">
-        <v>323</v>
-      </c>
       <c r="P95" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="Q95" s="8">
         <v>46174</v>
@@ -7202,7 +7175,7 @@
         <v>46181</v>
       </c>
       <c r="S95" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T95" s="9">
         <v>0</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="325">
   <si>
     <t xml:space="preserve">50001490-ZITRON PERU METRO DE LIMA PV04-PV05 </t>
   </si>
@@ -806,6 +806,9 @@
   </si>
   <si>
     <t>1213380177588315</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:,Montaje Sensor</t>
@@ -6117,7 +6120,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46210.861684930554</v>
+        <v>46223.819611666666</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>209</v>
@@ -6126,9 +6129,11 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
+        <v>265</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>265</v>
+      </c>
       <c r="I78" s="5">
         <v>46111</v>
       </c>
@@ -6151,7 +6156,7 @@
         <v>206</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q78" s="5">
         <v>46111</v>
@@ -6171,25 +6176,27 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B79" s="8">
         <v>46073.69994784722</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46198.59349042824</v>
+        <v>46223.819611087965</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
+        <v>265</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>265</v>
+      </c>
       <c r="I79" s="8">
         <v>46149</v>
       </c>
@@ -6209,10 +6216,10 @@
         <v>262</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q79" s="8">
         <v>46149</v>
@@ -6232,25 +6239,27 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B80" s="5">
         <v>46073.69994813658</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.592367060184</v>
+        <v>46223.81961050926</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
+        <v>265</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>265</v>
+      </c>
       <c r="I80" s="5">
         <v>46134</v>
       </c>
@@ -6270,10 +6279,10 @@
         <v>262</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q80" s="5">
         <v>46134</v>
@@ -6293,25 +6302,27 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B81" s="8">
         <v>46073.699948368056</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46213.56641375</v>
+        <v>46223.81960986111</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="9"/>
+        <v>265</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>265</v>
+      </c>
       <c r="I81" s="8">
         <v>46136</v>
       </c>
@@ -6331,10 +6342,10 @@
         <v>262</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q81" s="8">
         <v>46136</v>
@@ -6343,7 +6354,7 @@
         <v>46139</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T81" s="9">
         <v>0.5</v>
@@ -6354,25 +6365,27 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5">
         <v>46076.88137268518</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46195.60422616898</v>
+        <v>46223.819609293976</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>265</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>265</v>
+      </c>
       <c r="I82" s="5">
         <v>46129</v>
       </c>
@@ -6392,10 +6405,10 @@
         <v>262</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q82" s="5">
         <v>46129</v>
@@ -6415,14 +6428,14 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46073.69994864584</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46153.16811694445</v>
+        <v>46223.81960872685</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>229</v>
@@ -6431,9 +6444,11 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="9"/>
+        <v>265</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>265</v>
+      </c>
       <c r="I83" s="8">
         <v>46153</v>
       </c>
@@ -6453,10 +6468,10 @@
         <v>262</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83" s="8">
         <v>46153</v>
@@ -6476,25 +6491,27 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46073.699948912035</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46154.16785564815</v>
+        <v>46223.819608148144</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>265</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>265</v>
+      </c>
       <c r="I84" s="5">
         <v>46154</v>
       </c>
@@ -6517,7 +6534,7 @@
         <v>226</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q84" s="5">
         <v>46154</v>
@@ -6537,7 +6554,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B85" s="8">
         <v>46073.69994572917</v>
@@ -6547,7 +6564,7 @@
         <v>46077.638347245374</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6571,7 +6588,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6584,7 +6601,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46073.699946099536</v>
@@ -6594,16 +6611,16 @@
         <v>46210.60325569444</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I86" s="5">
         <v>46155</v>
@@ -6621,13 +6638,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q86" s="5">
         <v>46155</v>
@@ -6647,7 +6664,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B87" s="8">
         <v>46073.69994638889</v>
@@ -6682,13 +6699,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q87" s="8">
         <v>46156</v>
@@ -6708,7 +6725,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B88" s="5">
         <v>46073.69994668981</v>
@@ -6718,16 +6735,16 @@
         <v>46161.25032122685</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I88" s="5">
         <v>46161</v>
@@ -6745,13 +6762,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>259</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q88" s="5">
         <v>46161</v>
@@ -6771,7 +6788,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B89" s="8">
         <v>46073.69994695602</v>
@@ -6781,16 +6798,16 @@
         <v>46162.25040996527</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I89" s="8">
         <v>46162</v>
@@ -6808,13 +6825,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q89" s="8">
         <v>46162</v>
@@ -6834,7 +6851,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B90" s="5">
         <v>46073.699947245375</v>
@@ -6844,7 +6861,7 @@
         <v>46077.6387968287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6868,7 +6885,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6881,7 +6898,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B91" s="8">
         <v>46073.699947500005</v>
@@ -6891,16 +6908,16 @@
         <v>46174.16833755787</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I91" s="8">
         <v>46164</v>
@@ -6918,13 +6935,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q91" s="8">
         <v>46164</v>
@@ -6944,7 +6961,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B92" s="5">
         <v>46073.699947789355</v>
@@ -6954,16 +6971,16 @@
         <v>46174.168340185184</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I92" s="5">
         <v>46164</v>
@@ -6981,13 +6998,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q92" s="5">
         <v>46164</v>
@@ -7007,7 +7024,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B93" s="8">
         <v>46092.48971385417</v>
@@ -7017,7 +7034,7 @@
         <v>46092.497058946756</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -7041,7 +7058,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>26</v>
@@ -7060,7 +7077,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B94" s="5">
         <v>46092.49161491898</v>
@@ -7070,7 +7087,7 @@
         <v>46171.168742951384</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7097,13 +7114,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q94" s="5">
         <v>46164</v>
@@ -7123,7 +7140,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B95" s="8">
         <v>46092.491661747685</v>
@@ -7133,7 +7150,7 @@
         <v>46181.16820616898</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7160,13 +7177,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q95" s="8">
         <v>46174</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="325">
   <si>
     <t xml:space="preserve">50001490-ZITRON PERU METRO DE LIMA PV04-PV05 </t>
   </si>
@@ -355,6 +355,9 @@
     <t xml:space="preserve">Propuesta Fabricacion externa </t>
   </si>
   <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
     <t>Check Planos</t>
   </si>
   <si>
@@ -806,9 +809,6 @@
   </si>
   <si>
     <t>1213380177588315</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje:,Montaje Sensor</t>
@@ -3248,7 +3248,7 @@
         <v>46139.5432959375</v>
       </c>
       <c r="D30" s="5">
-        <v>46139.548176979166</v>
+        <v>46223.83401435185</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -3257,9 +3257,11 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>114</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="I30" s="5">
         <v>46136</v>
       </c>
@@ -3279,10 +3281,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q30" s="5">
         <v>46136</v>
@@ -3302,7 +3304,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46073.699946747685</v>
@@ -3312,7 +3314,7 @@
         <v>46191.83935533564</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3336,7 +3338,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3349,7 +3351,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46073.69994704861</v>
@@ -3361,16 +3363,16 @@
         <v>46191.83935060185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I32" s="5">
         <v>46014</v>
@@ -3388,13 +3390,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q32" s="5">
         <v>46014</v>
@@ -3414,7 +3416,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46073.69994738426</v>
@@ -3426,16 +3428,16 @@
         <v>46182.68413366898</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I33" s="8">
         <v>46014</v>
@@ -3453,18 +3455,18 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>94</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
@@ -3475,7 +3477,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46073.69994769676</v>
@@ -3487,16 +3489,16 @@
         <v>46191.83755358796</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I34" s="5">
         <v>46017</v>
@@ -3514,18 +3516,18 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3536,7 +3538,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46073.69994803241</v>
@@ -3546,16 +3548,16 @@
         <v>46218.59376659722</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I35" s="8">
         <v>46008</v>
@@ -3573,13 +3575,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q35" s="8">
         <v>46008</v>
@@ -3599,7 +3601,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46073.699948333335</v>
@@ -3611,16 +3613,16 @@
         <v>46174.652731724535</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I36" s="5">
         <v>46008</v>
@@ -3638,18 +3640,18 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3660,7 +3662,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46073.699948622685</v>
@@ -3670,16 +3672,16 @@
         <v>46174.65273809028</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I37" s="8">
         <v>46020</v>
@@ -3697,18 +3699,18 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
@@ -3719,7 +3721,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46073.69994892361</v>
@@ -3731,16 +3733,16 @@
         <v>46191.83671528935</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I38" s="5">
         <v>46014</v>
@@ -3758,13 +3760,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q38" s="5">
         <v>46014</v>
@@ -3784,7 +3786,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46073.699949201386</v>
@@ -3796,16 +3798,16 @@
         <v>46174.64929997685</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I39" s="8">
         <v>46014</v>
@@ -3823,18 +3825,18 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>100</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
@@ -3845,7 +3847,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46073.69994585648</v>
@@ -3857,16 +3859,16 @@
         <v>46182.67566810185</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I40" s="5">
         <v>46017</v>
@@ -3884,18 +3886,18 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
@@ -3906,7 +3908,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46073.69994628472</v>
@@ -3918,16 +3920,16 @@
         <v>46127.78344613426</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I41" s="8">
         <v>46000</v>
@@ -3945,13 +3947,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q41" s="8">
         <v>46000</v>
@@ -3960,7 +3962,7 @@
         <v>46147</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3971,7 +3973,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46073.69994653935</v>
@@ -3983,16 +3985,16 @@
         <v>46120.69255305556</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I42" s="5">
         <v>46000</v>
@@ -4010,18 +4012,18 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
@@ -4032,7 +4034,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46073.69994680556</v>
@@ -4044,16 +4046,16 @@
         <v>46127.783407256946</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I43" s="8">
         <v>46020</v>
@@ -4071,18 +4073,18 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
       <c r="S43" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
@@ -4093,7 +4095,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46073.69994707176</v>
@@ -4105,16 +4107,16 @@
         <v>46127.78341805555</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I44" s="5">
         <v>46020</v>
@@ -4132,18 +4134,18 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -4154,7 +4156,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46073.69994733796</v>
@@ -4166,16 +4168,16 @@
         <v>46139.54791172454</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I45" s="8">
         <v>46014</v>
@@ -4193,13 +4195,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q45" s="8">
         <v>46014</v>
@@ -4219,7 +4221,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46073.69994759259</v>
@@ -4231,16 +4233,16 @@
         <v>46104.82754626157</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46014</v>
@@ -4258,18 +4260,18 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4280,7 +4282,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46073.699947870366</v>
@@ -4292,16 +4294,16 @@
         <v>46132.57863447917</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46035</v>
@@ -4319,18 +4321,18 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
       <c r="S47" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4341,7 +4343,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46076.881105196764</v>
@@ -4353,16 +4355,16 @@
         <v>46139.54788491898</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46014</v>
@@ -4380,13 +4382,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q48" s="5">
         <v>46014</v>
@@ -4406,7 +4408,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46076.88918239583</v>
@@ -4418,16 +4420,16 @@
         <v>46112.491848171296</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46014</v>
@@ -4445,13 +4447,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>106</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4461,7 +4463,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B50" s="5">
         <v>46076.88930991898</v>
@@ -4473,16 +4475,16 @@
         <v>46112.50608989583</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46043</v>
@@ -4500,13 +4502,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4516,7 +4518,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B51" s="8">
         <v>46077.579487986106</v>
@@ -4528,16 +4530,16 @@
         <v>46191.83738863426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I51" s="8">
         <v>46014</v>
@@ -4555,7 +4557,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>109</v>
@@ -4581,7 +4583,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B52" s="5">
         <v>46077.5872287963</v>
@@ -4599,10 +4601,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I52" s="5">
         <v>46014</v>
@@ -4620,13 +4622,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4636,7 +4638,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46077.58741234954</v>
@@ -4648,16 +4650,16 @@
         <v>46182.69210671296</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I53" s="8">
         <v>46017</v>
@@ -4675,13 +4677,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>109</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4691,7 +4693,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46077.57954119213</v>
@@ -4703,16 +4705,16 @@
         <v>46174.6518578588</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I54" s="5">
         <v>46014</v>
@@ -4730,10 +4732,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4756,7 +4758,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46077.587555833336</v>
@@ -4774,10 +4776,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I55" s="8">
         <v>46014</v>
@@ -4795,13 +4797,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4811,7 +4813,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46077.5876627199</v>
@@ -4823,16 +4825,16 @@
         <v>46174.651731377315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I56" s="5">
         <v>46017</v>
@@ -4850,13 +4852,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4866,7 +4868,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46139.543413900465</v>
@@ -4878,16 +4880,16 @@
         <v>46205.80892784722</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I57" s="8">
         <v>46139</v>
@@ -4905,10 +4907,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4920,18 +4922,18 @@
         <v>46177</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B58" s="5">
         <v>46139.543700821756</v>
@@ -4943,16 +4945,16 @@
         <v>46191.83987099537</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46139</v>
@@ -4970,13 +4972,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4986,7 +4988,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46139.54378479166</v>
@@ -4998,16 +5000,16 @@
         <v>46191.83995613426</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I59" s="8">
         <v>46149</v>
@@ -5025,10 +5027,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5041,7 +5043,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B60" s="5">
         <v>46205.80892462963</v>
@@ -5051,16 +5053,16 @@
         <v>46218.58775554398</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5076,13 +5078,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5092,7 +5094,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B61" s="8">
         <v>46073.69994815972</v>
@@ -5102,7 +5104,7 @@
         <v>46129.586425601854</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5126,7 +5128,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5139,7 +5141,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46073.6999484375</v>
@@ -5151,16 +5153,16 @@
         <v>46099.54242268519</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I62" s="5">
         <v>46003</v>
@@ -5178,13 +5180,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q62" s="5">
         <v>46003</v>
@@ -5204,7 +5206,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B63" s="8">
         <v>46073.699946249995</v>
@@ -5216,16 +5218,16 @@
         <v>46129.58626813657</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I63" s="8">
         <v>46058</v>
@@ -5243,13 +5245,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q63" s="8">
         <v>46058</v>
@@ -5269,7 +5271,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46092.494241736116</v>
@@ -5281,16 +5283,16 @@
         <v>46210.861392569444</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5306,13 +5308,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="5">
         <v>46065</v>
@@ -5332,7 +5334,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="8">
         <v>46092.49428590278</v>
@@ -5342,16 +5344,16 @@
         <v>46154.16811805556</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I65" s="8">
         <v>46154</v>
@@ -5369,13 +5371,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q65" s="8">
         <v>46154</v>
@@ -5384,7 +5386,7 @@
         <v>46154</v>
       </c>
       <c r="S65" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
@@ -5395,7 +5397,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46073.69994662037</v>
@@ -5405,7 +5407,7 @@
         <v>46210.858702094905</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5429,7 +5431,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5442,7 +5444,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B67" s="8">
         <v>46073.69994689815</v>
@@ -5454,16 +5456,16 @@
         <v>46210.85869597222</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I67" s="8">
         <v>46063</v>
@@ -5481,13 +5483,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q67" s="8">
         <v>46063</v>
@@ -5502,12 +5504,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
         <v>46073.69994719907</v>
@@ -5519,16 +5521,16 @@
         <v>46210.86139240741</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I68" s="5">
         <v>46065</v>
@@ -5546,13 +5548,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="5">
         <v>46065</v>
@@ -5572,7 +5574,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B69" s="8">
         <v>46073.699948865746</v>
@@ -5582,7 +5584,7 @@
         <v>46213.56641354167</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5606,7 +5608,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5619,7 +5621,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B70" s="5">
         <v>46073.69995097222</v>
@@ -5629,16 +5631,16 @@
         <v>46213.56641027778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I70" s="5">
         <v>46097</v>
@@ -5656,13 +5658,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q70" s="5">
         <v>46097</v>
@@ -5682,7 +5684,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B71" s="8">
         <v>46073.69994640046</v>
@@ -5698,10 +5700,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I71" s="8">
         <v>46119</v>
@@ -5719,13 +5721,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q71" s="8">
         <v>46119</v>
@@ -5745,7 +5747,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B72" s="5">
         <v>46073.699946782406</v>
@@ -5755,16 +5757,16 @@
         <v>46199.82646660879</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I72" s="5">
         <v>46132</v>
@@ -5782,13 +5784,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q72" s="5">
         <v>46132</v>
@@ -5808,7 +5810,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B73" s="8">
         <v>46073.69994708333</v>
@@ -5820,16 +5822,16 @@
         <v>46195.603959687505</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I73" s="8">
         <v>46147</v>
@@ -5847,13 +5849,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q73" s="8">
         <v>46147</v>
@@ -5862,18 +5864,18 @@
         <v>46148</v>
       </c>
       <c r="S73" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T73" s="9">
         <v>0</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B74" s="5">
         <v>46076.88127923611</v>
@@ -5885,16 +5887,16 @@
         <v>46195.60422127315</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I74" s="5">
         <v>46121</v>
@@ -5912,13 +5914,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q74" s="5">
         <v>46121</v>
@@ -5933,12 +5935,12 @@
         <v>0</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B75" s="8">
         <v>46077.57961084491</v>
@@ -5950,16 +5952,16 @@
         <v>46195.60466490741</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I75" s="8">
         <v>46104</v>
@@ -5977,13 +5979,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q75" s="8">
         <v>46104</v>
@@ -6003,7 +6005,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B76" s="5">
         <v>46077.57965403935</v>
@@ -6013,16 +6015,16 @@
         <v>46182.692112696765</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I76" s="5">
         <v>46098</v>
@@ -6040,13 +6042,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q76" s="5">
         <v>46098</v>
@@ -6066,7 +6068,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B77" s="8">
         <v>46073.69994733796</v>
@@ -6076,7 +6078,7 @@
         <v>46078.621237141204</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6100,7 +6102,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6113,7 +6115,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B78" s="5">
         <v>46073.69994759259</v>
@@ -6123,16 +6125,16 @@
         <v>46223.819611666666</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="I78" s="5">
         <v>46111</v>
@@ -6150,10 +6152,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>266</v>
@@ -6192,10 +6194,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="I79" s="8">
         <v>46149</v>
@@ -6213,7 +6215,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>269</v>
@@ -6228,7 +6230,7 @@
         <v>46150</v>
       </c>
       <c r="S79" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T79" s="9">
         <v>0</v>
@@ -6255,10 +6257,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="I80" s="5">
         <v>46134</v>
@@ -6276,7 +6278,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>273</v>
@@ -6318,10 +6320,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="I81" s="8">
         <v>46136</v>
@@ -6339,7 +6341,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>276</v>
@@ -6381,10 +6383,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="I82" s="5">
         <v>46129</v>
@@ -6402,7 +6404,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>280</v>
@@ -6438,16 +6440,16 @@
         <v>46223.81960872685</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="I83" s="8">
         <v>46153</v>
@@ -6465,7 +6467,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>283</v>
@@ -6480,7 +6482,7 @@
         <v>46153</v>
       </c>
       <c r="S83" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T83" s="9">
         <v>0</v>
@@ -6507,10 +6509,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>265</v>
+        <v>114</v>
       </c>
       <c r="I84" s="5">
         <v>46154</v>
@@ -6528,10 +6530,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>287</v>
@@ -6543,7 +6545,7 @@
         <v>46154</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6653,7 +6655,7 @@
         <v>46155</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6671,18 +6673,20 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46195.604670092594</v>
+        <v>46223.83412716435</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="9"/>
+        <v>114</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="I87" s="8">
         <v>46156</v>
       </c>
@@ -6714,7 +6718,7 @@
         <v>46160</v>
       </c>
       <c r="S87" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
@@ -6765,7 +6769,7 @@
         <v>289</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>303</v>
@@ -6777,7 +6781,7 @@
         <v>46161</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6840,7 +6844,7 @@
         <v>46162</v>
       </c>
       <c r="S89" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
@@ -6950,7 +6954,7 @@
         <v>46174</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -7013,7 +7017,7 @@
         <v>46174</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T92" s="6">
         <v>0</v>
@@ -7066,7 +7070,7 @@
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
       <c r="S93" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T93" s="9">
         <v>0</v>
@@ -7129,7 +7133,7 @@
         <v>46171</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7192,7 +7196,7 @@
         <v>46181</v>
       </c>
       <c r="S95" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T95" s="9">
         <v>0</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="326">
   <si>
     <t xml:space="preserve">50001490-ZITRON PERU METRO DE LIMA PV04-PV05 </t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t xml:space="preserve">Propuesta Fabricacion externa </t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -3260,7 +3263,7 @@
         <v>114</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I30" s="5">
         <v>46136</v>
@@ -3281,10 +3284,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="5">
         <v>46136</v>
@@ -3304,7 +3307,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46073.699946747685</v>
@@ -3314,7 +3317,7 @@
         <v>46191.83935533564</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3338,7 +3341,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3351,7 +3354,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46073.69994704861</v>
@@ -3363,16 +3366,16 @@
         <v>46191.83935060185</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I32" s="5">
         <v>46014</v>
@@ -3390,13 +3393,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q32" s="5">
         <v>46014</v>
@@ -3416,7 +3419,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46073.69994738426</v>
@@ -3428,16 +3431,16 @@
         <v>46182.68413366898</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" s="8">
         <v>46014</v>
@@ -3455,18 +3458,18 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>94</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
@@ -3477,7 +3480,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46073.69994769676</v>
@@ -3489,16 +3492,16 @@
         <v>46191.83755358796</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I34" s="5">
         <v>46017</v>
@@ -3516,18 +3519,18 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3538,7 +3541,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46073.69994803241</v>
@@ -3548,16 +3551,16 @@
         <v>46218.59376659722</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I35" s="8">
         <v>46008</v>
@@ -3575,13 +3578,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q35" s="8">
         <v>46008</v>
@@ -3601,7 +3604,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46073.699948333335</v>
@@ -3613,16 +3616,16 @@
         <v>46174.652731724535</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I36" s="5">
         <v>46008</v>
@@ -3640,18 +3643,18 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3662,7 +3665,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46073.699948622685</v>
@@ -3672,16 +3675,16 @@
         <v>46174.65273809028</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I37" s="8">
         <v>46020</v>
@@ -3699,18 +3702,18 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
@@ -3721,7 +3724,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46073.69994892361</v>
@@ -3733,16 +3736,16 @@
         <v>46191.83671528935</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I38" s="5">
         <v>46014</v>
@@ -3760,13 +3763,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q38" s="5">
         <v>46014</v>
@@ -3786,7 +3789,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46073.699949201386</v>
@@ -3798,16 +3801,16 @@
         <v>46174.64929997685</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I39" s="8">
         <v>46014</v>
@@ -3825,18 +3828,18 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>100</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
@@ -3847,7 +3850,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46073.69994585648</v>
@@ -3859,16 +3862,16 @@
         <v>46182.67566810185</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I40" s="5">
         <v>46017</v>
@@ -3886,18 +3889,18 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
@@ -3908,7 +3911,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46073.69994628472</v>
@@ -3920,16 +3923,16 @@
         <v>46127.78344613426</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I41" s="8">
         <v>46000</v>
@@ -3947,13 +3950,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q41" s="8">
         <v>46000</v>
@@ -3962,7 +3965,7 @@
         <v>46147</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -3973,7 +3976,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46073.69994653935</v>
@@ -3985,16 +3988,16 @@
         <v>46120.69255305556</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I42" s="5">
         <v>46000</v>
@@ -4012,18 +4015,18 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
@@ -4034,7 +4037,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46073.69994680556</v>
@@ -4046,16 +4049,16 @@
         <v>46127.783407256946</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I43" s="8">
         <v>46020</v>
@@ -4073,18 +4076,18 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
       <c r="S43" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T43" s="9">
         <v>0</v>
@@ -4095,7 +4098,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46073.69994707176</v>
@@ -4107,16 +4110,16 @@
         <v>46127.78341805555</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I44" s="5">
         <v>46020</v>
@@ -4134,18 +4137,18 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -4156,7 +4159,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46073.69994733796</v>
@@ -4168,16 +4171,16 @@
         <v>46139.54791172454</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I45" s="8">
         <v>46014</v>
@@ -4195,13 +4198,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q45" s="8">
         <v>46014</v>
@@ -4221,7 +4224,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46073.69994759259</v>
@@ -4233,16 +4236,16 @@
         <v>46104.82754626157</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46014</v>
@@ -4260,18 +4263,18 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
       <c r="S46" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4282,7 +4285,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46073.699947870366</v>
@@ -4294,16 +4297,16 @@
         <v>46132.57863447917</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I47" s="8">
         <v>46035</v>
@@ -4321,18 +4324,18 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
       <c r="S47" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4343,7 +4346,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B48" s="5">
         <v>46076.881105196764</v>
@@ -4355,16 +4358,16 @@
         <v>46139.54788491898</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I48" s="5">
         <v>46014</v>
@@ -4382,13 +4385,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q48" s="5">
         <v>46014</v>
@@ -4408,7 +4411,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8">
         <v>46076.88918239583</v>
@@ -4420,16 +4423,16 @@
         <v>46112.491848171296</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I49" s="8">
         <v>46014</v>
@@ -4447,13 +4450,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>106</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4463,7 +4466,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46076.88930991898</v>
@@ -4475,16 +4478,16 @@
         <v>46112.50608989583</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I50" s="5">
         <v>46043</v>
@@ -4502,13 +4505,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4518,7 +4521,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B51" s="8">
         <v>46077.579487986106</v>
@@ -4530,16 +4533,16 @@
         <v>46191.83738863426</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I51" s="8">
         <v>46014</v>
@@ -4557,7 +4560,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>109</v>
@@ -4583,7 +4586,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B52" s="5">
         <v>46077.5872287963</v>
@@ -4601,10 +4604,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I52" s="5">
         <v>46014</v>
@@ -4622,13 +4625,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>79</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4638,7 +4641,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46077.58741234954</v>
@@ -4650,16 +4653,16 @@
         <v>46182.69210671296</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I53" s="8">
         <v>46017</v>
@@ -4677,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>109</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4693,7 +4696,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5">
         <v>46077.57954119213</v>
@@ -4705,16 +4708,16 @@
         <v>46174.6518578588</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I54" s="5">
         <v>46014</v>
@@ -4732,10 +4735,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4758,7 +4761,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46077.587555833336</v>
@@ -4776,10 +4779,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I55" s="8">
         <v>46014</v>
@@ -4797,13 +4800,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4813,7 +4816,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46077.5876627199</v>
@@ -4825,16 +4828,16 @@
         <v>46174.651731377315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I56" s="5">
         <v>46017</v>
@@ -4852,13 +4855,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4868,7 +4871,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46139.543413900465</v>
@@ -4880,16 +4883,16 @@
         <v>46205.80892784722</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I57" s="8">
         <v>46139</v>
@@ -4907,10 +4910,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4922,18 +4925,18 @@
         <v>46177</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B58" s="5">
         <v>46139.543700821756</v>
@@ -4945,16 +4948,16 @@
         <v>46191.83987099537</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I58" s="5">
         <v>46139</v>
@@ -4972,13 +4975,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>113</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4988,7 +4991,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>46139.54378479166</v>
@@ -5000,16 +5003,16 @@
         <v>46191.83995613426</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I59" s="8">
         <v>46149</v>
@@ -5027,10 +5030,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5043,7 +5046,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B60" s="5">
         <v>46205.80892462963</v>
@@ -5053,16 +5056,16 @@
         <v>46218.58775554398</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5078,13 +5081,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5094,7 +5097,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46073.69994815972</v>
@@ -5104,7 +5107,7 @@
         <v>46129.586425601854</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5128,7 +5131,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5141,7 +5144,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46073.6999484375</v>
@@ -5153,16 +5156,16 @@
         <v>46099.54242268519</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I62" s="5">
         <v>46003</v>
@@ -5180,13 +5183,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q62" s="5">
         <v>46003</v>
@@ -5206,7 +5209,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B63" s="8">
         <v>46073.699946249995</v>
@@ -5218,16 +5221,16 @@
         <v>46129.58626813657</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I63" s="8">
         <v>46058</v>
@@ -5245,13 +5248,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q63" s="8">
         <v>46058</v>
@@ -5271,7 +5274,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46092.494241736116</v>
@@ -5283,16 +5286,16 @@
         <v>46210.861392569444</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5308,13 +5311,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="5">
         <v>46065</v>
@@ -5334,7 +5337,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B65" s="8">
         <v>46092.49428590278</v>
@@ -5344,16 +5347,16 @@
         <v>46154.16811805556</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I65" s="8">
         <v>46154</v>
@@ -5371,13 +5374,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="8">
         <v>46154</v>
@@ -5386,7 +5389,7 @@
         <v>46154</v>
       </c>
       <c r="S65" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T65" s="9">
         <v>0</v>
@@ -5397,7 +5400,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46073.69994662037</v>
@@ -5407,7 +5410,7 @@
         <v>46210.858702094905</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5431,7 +5434,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5444,7 +5447,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B67" s="8">
         <v>46073.69994689815</v>
@@ -5456,16 +5459,16 @@
         <v>46210.85869597222</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I67" s="8">
         <v>46063</v>
@@ -5483,13 +5486,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q67" s="8">
         <v>46063</v>
@@ -5504,12 +5507,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46073.69994719907</v>
@@ -5521,16 +5524,16 @@
         <v>46210.86139240741</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46065</v>
@@ -5548,13 +5551,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="5">
         <v>46065</v>
@@ -5574,7 +5577,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B69" s="8">
         <v>46073.699948865746</v>
@@ -5584,7 +5587,7 @@
         <v>46213.56641354167</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5608,7 +5611,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5621,7 +5624,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B70" s="5">
         <v>46073.69995097222</v>
@@ -5631,16 +5634,16 @@
         <v>46213.56641027778</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I70" s="5">
         <v>46097</v>
@@ -5658,13 +5661,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q70" s="5">
         <v>46097</v>
@@ -5684,7 +5687,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B71" s="8">
         <v>46073.69994640046</v>
@@ -5700,10 +5703,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I71" s="8">
         <v>46119</v>
@@ -5721,13 +5724,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q71" s="8">
         <v>46119</v>
@@ -5747,7 +5750,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B72" s="5">
         <v>46073.699946782406</v>
@@ -5757,16 +5760,16 @@
         <v>46199.82646660879</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I72" s="5">
         <v>46132</v>
@@ -5784,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q72" s="5">
         <v>46132</v>
@@ -5810,7 +5813,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B73" s="8">
         <v>46073.69994708333</v>
@@ -5822,16 +5825,16 @@
         <v>46195.603959687505</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I73" s="8">
         <v>46147</v>
@@ -5849,13 +5852,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q73" s="8">
         <v>46147</v>
@@ -5864,18 +5867,18 @@
         <v>46148</v>
       </c>
       <c r="S73" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T73" s="9">
         <v>0</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B74" s="5">
         <v>46076.88127923611</v>
@@ -5887,16 +5890,16 @@
         <v>46195.60422127315</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I74" s="5">
         <v>46121</v>
@@ -5914,13 +5917,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q74" s="5">
         <v>46121</v>
@@ -5935,12 +5938,12 @@
         <v>0</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B75" s="8">
         <v>46077.57961084491</v>
@@ -5952,16 +5955,16 @@
         <v>46195.60466490741</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I75" s="8">
         <v>46104</v>
@@ -5979,13 +5982,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q75" s="8">
         <v>46104</v>
@@ -6005,7 +6008,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B76" s="5">
         <v>46077.57965403935</v>
@@ -6015,16 +6018,16 @@
         <v>46182.692112696765</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I76" s="5">
         <v>46098</v>
@@ -6042,13 +6045,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q76" s="5">
         <v>46098</v>
@@ -6068,7 +6071,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B77" s="8">
         <v>46073.69994733796</v>
@@ -6078,7 +6081,7 @@
         <v>46078.621237141204</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6102,7 +6105,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6115,7 +6118,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B78" s="5">
         <v>46073.69994759259</v>
@@ -6125,7 +6128,7 @@
         <v>46223.819611666666</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6134,7 +6137,7 @@
         <v>114</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I78" s="5">
         <v>46111</v>
@@ -6152,13 +6155,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q78" s="5">
         <v>46111</v>
@@ -6178,7 +6181,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B79" s="8">
         <v>46073.69994784722</v>
@@ -6188,7 +6191,7 @@
         <v>46223.819611087965</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6197,7 +6200,7 @@
         <v>114</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I79" s="8">
         <v>46149</v>
@@ -6215,13 +6218,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q79" s="8">
         <v>46149</v>
@@ -6230,7 +6233,7 @@
         <v>46150</v>
       </c>
       <c r="S79" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T79" s="9">
         <v>0</v>
@@ -6241,7 +6244,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B80" s="5">
         <v>46073.69994813658</v>
@@ -6251,7 +6254,7 @@
         <v>46223.81961050926</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6260,7 +6263,7 @@
         <v>114</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I80" s="5">
         <v>46134</v>
@@ -6278,13 +6281,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q80" s="5">
         <v>46134</v>
@@ -6304,7 +6307,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B81" s="8">
         <v>46073.699948368056</v>
@@ -6314,7 +6317,7 @@
         <v>46223.81960986111</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6323,7 +6326,7 @@
         <v>114</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I81" s="8">
         <v>46136</v>
@@ -6341,13 +6344,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q81" s="8">
         <v>46136</v>
@@ -6356,7 +6359,7 @@
         <v>46139</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T81" s="9">
         <v>0.5</v>
@@ -6367,7 +6370,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46076.88137268518</v>
@@ -6377,7 +6380,7 @@
         <v>46223.819609293976</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6386,7 +6389,7 @@
         <v>114</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I82" s="5">
         <v>46129</v>
@@ -6404,13 +6407,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q82" s="5">
         <v>46129</v>
@@ -6430,7 +6433,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" s="8">
         <v>46073.69994864584</v>
@@ -6440,7 +6443,7 @@
         <v>46223.81960872685</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6449,7 +6452,7 @@
         <v>114</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I83" s="8">
         <v>46153</v>
@@ -6467,13 +6470,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q83" s="8">
         <v>46153</v>
@@ -6482,7 +6485,7 @@
         <v>46153</v>
       </c>
       <c r="S83" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T83" s="9">
         <v>0</v>
@@ -6493,7 +6496,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B84" s="5">
         <v>46073.699948912035</v>
@@ -6503,7 +6506,7 @@
         <v>46223.819608148144</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6512,7 +6515,7 @@
         <v>114</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I84" s="5">
         <v>46154</v>
@@ -6530,13 +6533,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q84" s="5">
         <v>46154</v>
@@ -6545,7 +6548,7 @@
         <v>46154</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6556,7 +6559,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B85" s="8">
         <v>46073.69994572917</v>
@@ -6566,7 +6569,7 @@
         <v>46077.638347245374</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>25</v>
@@ -6590,7 +6593,7 @@
         <v>26</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6603,7 +6606,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B86" s="5">
         <v>46073.699946099536</v>
@@ -6613,16 +6616,16 @@
         <v>46210.60325569444</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I86" s="5">
         <v>46155</v>
@@ -6640,13 +6643,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q86" s="5">
         <v>46155</v>
@@ -6655,7 +6658,7 @@
         <v>46155</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
@@ -6666,7 +6669,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B87" s="8">
         <v>46073.69994638889</v>
@@ -6676,7 +6679,7 @@
         <v>46223.83412716435</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6685,7 +6688,7 @@
         <v>114</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I87" s="8">
         <v>46156</v>
@@ -6703,13 +6706,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q87" s="8">
         <v>46156</v>
@@ -6718,7 +6721,7 @@
         <v>46160</v>
       </c>
       <c r="S87" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
@@ -6729,7 +6732,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B88" s="5">
         <v>46073.69994668981</v>
@@ -6739,16 +6742,16 @@
         <v>46161.25032122685</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I88" s="5">
         <v>46161</v>
@@ -6766,13 +6769,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q88" s="5">
         <v>46161</v>
@@ -6781,7 +6784,7 @@
         <v>46161</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6792,7 +6795,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B89" s="8">
         <v>46073.69994695602</v>
@@ -6802,16 +6805,16 @@
         <v>46162.25040996527</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I89" s="8">
         <v>46162</v>
@@ -6829,13 +6832,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q89" s="8">
         <v>46162</v>
@@ -6844,7 +6847,7 @@
         <v>46162</v>
       </c>
       <c r="S89" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
@@ -6855,7 +6858,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B90" s="5">
         <v>46073.699947245375</v>
@@ -6865,7 +6868,7 @@
         <v>46077.6387968287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6889,7 +6892,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6902,7 +6905,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B91" s="8">
         <v>46073.699947500005</v>
@@ -6912,16 +6915,16 @@
         <v>46174.16833755787</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I91" s="8">
         <v>46164</v>
@@ -6939,13 +6942,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q91" s="8">
         <v>46164</v>
@@ -6954,7 +6957,7 @@
         <v>46174</v>
       </c>
       <c r="S91" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T91" s="9">
         <v>0</v>
@@ -6965,7 +6968,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B92" s="5">
         <v>46073.699947789355</v>
@@ -6975,16 +6978,16 @@
         <v>46174.168340185184</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I92" s="5">
         <v>46164</v>
@@ -7002,13 +7005,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q92" s="5">
         <v>46164</v>
@@ -7017,7 +7020,7 @@
         <v>46174</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T92" s="6">
         <v>0</v>
@@ -7028,7 +7031,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B93" s="8">
         <v>46092.48971385417</v>
@@ -7038,7 +7041,7 @@
         <v>46092.497058946756</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -7062,7 +7065,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>26</v>
@@ -7070,7 +7073,7 @@
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
       <c r="S93" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T93" s="9">
         <v>0</v>
@@ -7081,7 +7084,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B94" s="5">
         <v>46092.49161491898</v>
@@ -7091,7 +7094,7 @@
         <v>46171.168742951384</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7118,13 +7121,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q94" s="5">
         <v>46164</v>
@@ -7133,7 +7136,7 @@
         <v>46171</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7144,7 +7147,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B95" s="8">
         <v>46092.491661747685</v>
@@ -7154,7 +7157,7 @@
         <v>46181.16820616898</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7181,13 +7184,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q95" s="8">
         <v>46174</v>
@@ -7196,7 +7199,7 @@
         <v>46181</v>
       </c>
       <c r="S95" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T95" s="9">
         <v>0</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -1993,7 +1993,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46127.89302402778</v>
+        <v>46228.72469505787</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -2678,7 +2678,7 @@
         <v>46093.87454615741</v>
       </c>
       <c r="D21" s="8">
-        <v>46139.54278021991</v>
+        <v>46235.71759233796</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>88</v>
@@ -4880,7 +4880,7 @@
         <v>46191.840089791665</v>
       </c>
       <c r="D57" s="8">
-        <v>46205.80892784722</v>
+        <v>46235.717934444445</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>199</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46078.621237141204</v>
+        <v>46237.55411403935</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>264</v>
@@ -6123,9 +6123,11 @@
       <c r="B78" s="5">
         <v>46073.69994759259</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46237.55410504629</v>
+      </c>
       <c r="D78" s="5">
-        <v>46223.819611666666</v>
+        <v>46237.55410664352</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>211</v>
@@ -6175,8 +6177,8 @@
       <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="U78" s="10" t="s">
-        <v>59</v>
+      <c r="U78" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6188,7 +6190,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46223.819611087965</v>
+        <v>46237.55411162037</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>
@@ -6238,8 +6240,8 @@
       <c r="T79" s="9">
         <v>0</v>
       </c>
-      <c r="U79" s="10" t="s">
-        <v>59</v>
+      <c r="U79" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6249,9 +6251,11 @@
       <c r="B80" s="5">
         <v>46073.69994813658</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46237.554038807866</v>
+      </c>
       <c r="D80" s="5">
-        <v>46223.81961050926</v>
+        <v>46237.55411311342</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>273</v>
@@ -6301,8 +6305,8 @@
       <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="U80" s="10" t="s">
-        <v>59</v>
+      <c r="U80" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6314,7 +6318,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46223.81960986111</v>
+        <v>46237.5541136574</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>
@@ -6364,8 +6368,8 @@
       <c r="T81" s="9">
         <v>0.5</v>
       </c>
-      <c r="U81" s="10" t="s">
-        <v>59</v>
+      <c r="U81" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6377,7 +6381,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46223.819609293976</v>
+        <v>46237.554114976854</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>280</v>
@@ -6427,8 +6431,8 @@
       <c r="T82" s="6">
         <v>0</v>
       </c>
-      <c r="U82" s="10" t="s">
-        <v>59</v>
+      <c r="U82" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6440,7 +6444,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46223.81960872685</v>
+        <v>46237.55404603009</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>231</v>
@@ -6490,8 +6494,8 @@
       <c r="T83" s="9">
         <v>0</v>
       </c>
-      <c r="U83" s="10" t="s">
-        <v>59</v>
+      <c r="U83" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6676,7 +6680,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46223.83412716435</v>
+        <v>46237.53257923611</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>261</v>
@@ -6726,8 +6730,8 @@
       <c r="T87" s="9">
         <v>0</v>
       </c>
-      <c r="U87" s="10" t="s">
-        <v>59</v>
+      <c r="U87" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="318">
   <si>
     <t xml:space="preserve">50001490-ZITRON PERU METRO DE LIMA PV04-PV05 </t>
   </si>
@@ -934,7 +934,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Gestion,Costos,Logistica:,Instalación componentes</t>
+    <t>Gestion,Costos,Logistica:</t>
   </si>
   <si>
     <t>1213380177588326</t>
@@ -965,30 +965,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213598288999620</t>
-  </si>
-  <si>
-    <t>Puesta en marcha Servicios</t>
-  </si>
-  <si>
-    <t>Instalación componentes,Pruebas instalacion componente</t>
-  </si>
-  <si>
-    <t>1213598288999622</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t>Pruebas instalacion componente,Puesta en marcha Servicios</t>
-  </si>
-  <si>
-    <t>1213598288999624</t>
-  </si>
-  <si>
-    <t>Pruebas instalacion componente</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U95"/>
+  <dimension ref="A1:U92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -6806,7 +6782,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46162.25040996527</v>
+        <v>46240.72176880787</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>306</v>
@@ -7030,185 +7006,6 @@
         <v>0</v>
       </c>
       <c r="U92" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B93" s="8">
-        <v>46092.48971385417</v>
-      </c>
-      <c r="C93" s="9"/>
-      <c r="D93" s="8">
-        <v>46092.497058946756</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
-      <c r="I93" s="9"/>
-      <c r="J93" s="9"/>
-      <c r="K93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M93" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O93" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
-      <c r="S93" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="T93" s="9">
-        <v>0</v>
-      </c>
-      <c r="U93" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B94" s="5">
-        <v>46092.49161491898</v>
-      </c>
-      <c r="C94" s="6"/>
-      <c r="D94" s="5">
-        <v>46171.168742951384</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I94" s="5">
-        <v>46164</v>
-      </c>
-      <c r="J94" s="5">
-        <v>46171</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q94" s="5">
-        <v>46164</v>
-      </c>
-      <c r="R94" s="5">
-        <v>46171</v>
-      </c>
-      <c r="S94" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="T94" s="6">
-        <v>0</v>
-      </c>
-      <c r="U94" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="B95" s="8">
-        <v>46092.491661747685</v>
-      </c>
-      <c r="C95" s="9"/>
-      <c r="D95" s="8">
-        <v>46181.16820616898</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I95" s="8">
-        <v>46174</v>
-      </c>
-      <c r="J95" s="8">
-        <v>46181</v>
-      </c>
-      <c r="K95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N95" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q95" s="8">
-        <v>46174</v>
-      </c>
-      <c r="R95" s="8">
-        <v>46181</v>
-      </c>
-      <c r="S95" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="T95" s="9">
-        <v>0</v>
-      </c>
-      <c r="U95" s="10" t="s">
         <v>59</v>
       </c>
     </row>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5381,9 +5381,11 @@
       <c r="B66" s="5">
         <v>46073.69994662037</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46245.666245659726</v>
+      </c>
       <c r="D66" s="5">
-        <v>46210.858702094905</v>
+        <v>46245.666247685185</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>234</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -6056,7 +6056,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46237.55411403935</v>
+        <v>46247.53022914352</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>264</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46154.16811805556</v>
+        <v>46247.851415428246</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>228</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46237.55411162037</v>
+        <v>46260.56856410879</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -6056,7 +6056,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46247.53022914352</v>
+        <v>46262.80759832176</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>264</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46260.56856410879</v>
+        <v>46262.808263865736</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>
@@ -6218,8 +6218,8 @@
       <c r="T79" s="9">
         <v>0</v>
       </c>
-      <c r="U79" s="12" t="s">
-        <v>202</v>
+      <c r="U79" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46237.5541136574</v>
+        <v>46262.80775383102</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>
@@ -6346,8 +6346,8 @@
       <c r="T81" s="9">
         <v>0.5</v>
       </c>
-      <c r="U81" s="12" t="s">
-        <v>202</v>
+      <c r="U81" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6357,9 +6357,11 @@
       <c r="B82" s="5">
         <v>46076.88137268518</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46262.80759297454</v>
+      </c>
       <c r="D82" s="5">
-        <v>46237.554114976854</v>
+        <v>46262.80759458333</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>280</v>
@@ -6409,8 +6411,8 @@
       <c r="T82" s="6">
         <v>0</v>
       </c>
-      <c r="U82" s="12" t="s">
-        <v>202</v>
+      <c r="U82" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6422,7 +6424,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46237.55404603009</v>
+        <v>46262.80759803241</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>231</v>
@@ -6548,7 +6550,7 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46077.638347245374</v>
+        <v>46262.80754692129</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6719,9 +6721,11 @@
       <c r="B88" s="5">
         <v>46073.69994668981</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46262.80753832176</v>
+      </c>
       <c r="D88" s="5">
-        <v>46161.25032122685</v>
+        <v>46262.807540567126</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>301</v>
@@ -6771,8 +6775,8 @@
       <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="U88" s="10" t="s">
-        <v>59</v>
+      <c r="U88" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6784,7 +6788,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46240.72176880787</v>
+        <v>46262.80754540509</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>306</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46213.56641354167</v>
+        <v>46265.58197266204</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>234</v>
@@ -5607,9 +5607,11 @@
       <c r="B70" s="5">
         <v>46073.69995097222</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46265.581966122685</v>
+      </c>
       <c r="D70" s="5">
-        <v>46213.56641027778</v>
+        <v>46265.58196802084</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>246</v>
@@ -5733,9 +5735,11 @@
       <c r="B72" s="5">
         <v>46073.699946782406</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46265.58195543982</v>
+      </c>
       <c r="D72" s="5">
-        <v>46199.82646660879</v>
+        <v>46265.58195854167</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>251</v>
@@ -6056,7 +6060,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46262.80759832176</v>
+        <v>46265.58240835648</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>264</v>
@@ -6166,9 +6170,11 @@
       <c r="B79" s="8">
         <v>46073.69994784722</v>
       </c>
-      <c r="C79" s="9"/>
+      <c r="C79" s="8">
+        <v>46265.58239951389</v>
+      </c>
       <c r="D79" s="8">
-        <v>46262.808263865736</v>
+        <v>46265.582400960644</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>269</v>
@@ -6233,7 +6239,7 @@
         <v>46237.554038807866</v>
       </c>
       <c r="D80" s="5">
-        <v>46237.55411311342</v>
+        <v>46265.58196423611</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>273</v>
@@ -6294,9 +6300,11 @@
       <c r="B81" s="8">
         <v>46073.699948368056</v>
       </c>
-      <c r="C81" s="9"/>
+      <c r="C81" s="8">
+        <v>46265.5822203125</v>
+      </c>
       <c r="D81" s="8">
-        <v>46262.80775383102</v>
+        <v>46265.58222244213</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>276</v>
@@ -6424,7 +6432,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46262.80759803241</v>
+        <v>46265.58240677083</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>231</v>

--- a/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
+++ b/data/50001490 - ZITRON PERU METRO LIMA PV04-PV05.xlsx
@@ -6558,7 +6558,7 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46262.80754692129</v>
+        <v>46268.828274328705</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>290</v>
@@ -6666,9 +6666,11 @@
       <c r="B87" s="8">
         <v>46073.69994638889</v>
       </c>
-      <c r="C87" s="9"/>
+      <c r="C87" s="8">
+        <v>46268.828154664356</v>
+      </c>
       <c r="D87" s="8">
-        <v>46237.53257923611</v>
+        <v>46268.82815729167</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>261</v>
@@ -6733,7 +6735,7 @@
         <v>46262.80753832176</v>
       </c>
       <c r="D88" s="5">
-        <v>46262.807540567126</v>
+        <v>46268.828162418984</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>301</v>
@@ -6794,9 +6796,11 @@
       <c r="B89" s="8">
         <v>46073.69994695602</v>
       </c>
-      <c r="C89" s="9"/>
+      <c r="C89" s="8">
+        <v>46268.82826504629</v>
+      </c>
       <c r="D89" s="8">
-        <v>46262.80754540509</v>
+        <v>46268.82826701389</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>306</v>
@@ -6906,7 +6910,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46174.16833755787</v>
+        <v>46268.82827175926</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>312</v>
@@ -6969,7 +6973,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46174.168340185184</v>
+        <v>46268.82827357639</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>316</v>
